--- a/reports/Security_Report.xlsx
+++ b/reports/Security_Report.xlsx
@@ -4,14 +4,65 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Security Vulnerability" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Summary" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Test Cases" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Failed Tests" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Execution Logs" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="125">
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Execution Date</t>
+  </si>
+  <si>
+    <t>6/16/2026, 4:44:07 AM</t>
+  </si>
+  <si>
+    <t>Device Name</t>
+  </si>
+  <si>
+    <t>Security Vulnerability Scanner</t>
+  </si>
+  <si>
+    <t>Android Version</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Total Tests</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Skipped</t>
+  </si>
+  <si>
+    <t>Pass Percentage</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>0.00s</t>
+  </si>
   <si>
     <t>Test Case ID</t>
   </si>
@@ -52,9 +103,6 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>0.00s</t>
-  </si>
-  <si>
     <t>TC-SEC-02</t>
   </si>
   <si>
@@ -316,17 +364,38 @@
     <t>Sensitive API endpoints restrict access to specific trusted domains and reject * wildcards</t>
   </si>
   <si>
-    <t>Security Alert: CORS configuration vulnerability! Sensitive transactions endpoint exposes Access-Control-Allow-Origin: * wildcard allowing data leakage.: expected true to be false</t>
-  </si>
-  <si>
-    <t>FAIL</t>
+    <t>Failure Message</t>
+  </si>
+  <si>
+    <t>Stack Trace</t>
+  </si>
+  <si>
+    <t>All tests passed successfully.</t>
+  </si>
+  <si>
+    <t>No failure recorded</t>
+  </si>
+  <si>
+    <t>Timestamp</t>
+  </si>
+  <si>
+    <t>Test Module / Page Object</t>
+  </si>
+  <si>
+    <t>Action Step / Details</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>6/16/2026, 4:44:00 AM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -342,14 +411,21 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF137333"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFC5221F"/>
+      <color rgb="FF137333"/>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -358,17 +434,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E293B"/>
+        <fgColor rgb="FF1B365D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE6F4EA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE8E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -382,16 +453,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFE2E8F0"/>
+        <color rgb="FFD3D3D3"/>
       </left>
       <right style="thin">
-        <color rgb="FFE2E8F0"/>
+        <color rgb="FFD3D3D3"/>
       </right>
       <top style="thin">
-        <color rgb="FFE2E8F0"/>
+        <color rgb="FFD3D3D3"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFE2E8F0"/>
+        <color rgb="FFD3D3D3"/>
       </bottom>
       <diagonal/>
     </border>
@@ -401,22 +472,22 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -758,6 +829,101 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -770,715 +936,1312 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="E1" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="D2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="D3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="D4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="D5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="4" t="s">
+      <c r="D6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="D7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="D8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="4" t="s">
+      <c r="D9" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="4" t="s">
+      <c r="D10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="D11" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="4" t="s">
+      <c r="D12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="4" t="s">
+      <c r="D13" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="4" t="s">
+      <c r="D14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="4" t="s">
+      <c r="D15" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="4" t="s">
+      <c r="D16" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="4" t="s">
+      <c r="D17" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="4" t="s">
+      <c r="D18" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="4" t="s">
+      <c r="D19" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="4" t="s">
+      <c r="D20" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="4" t="s">
+      <c r="D21" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="4" t="s">
+      <c r="D22" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="4" t="s">
+      <c r="D23" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="4" t="s">
+      <c r="D24" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="4" t="s">
+      <c r="D25" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D31" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F31" s="6" t="s">
+      <c r="D26" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>13</v>
+      <c r="D27" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Security_Report.xlsx
+++ b/reports/Security_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="146">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 4:44:07 AM</t>
+    <t>6/16/2026, 5:20:47 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>0.00s</t>
+    <t>9.01s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,6 +103,9 @@
     <t>PASS</t>
   </si>
   <si>
+    <t>0.38s</t>
+  </si>
+  <si>
     <t>TC-SEC-02</t>
   </si>
   <si>
@@ -112,6 +115,9 @@
     <t>Search query drops comment blocks (--) to prevent database parsing errors</t>
   </si>
   <si>
+    <t>0.23s</t>
+  </si>
+  <si>
     <t>TC-SEC-03</t>
   </si>
   <si>
@@ -121,6 +127,9 @@
     <t>SELECT UNION query patterns in transaction description are blocked</t>
   </si>
   <si>
+    <t>0.37s</t>
+  </si>
+  <si>
     <t>TC-SEC-04</t>
   </si>
   <si>
@@ -130,6 +139,9 @@
     <t>Transaction update parameters are isolated and cannot modify tables structure</t>
   </si>
   <si>
+    <t>0.12s</t>
+  </si>
+  <si>
     <t>TC-SEC-05</t>
   </si>
   <si>
@@ -139,6 +151,9 @@
     <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
   </si>
   <si>
+    <t>0.31s</t>
+  </si>
+  <si>
     <t>TC-SEC-06</t>
   </si>
   <si>
@@ -148,6 +163,9 @@
     <t>Reflected query parameters from URL string are parsed and encoded</t>
   </si>
   <si>
+    <t>0.36s</t>
+  </si>
+  <si>
     <t>TC-SEC-07</t>
   </si>
   <si>
@@ -166,6 +184,9 @@
     <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
   </si>
   <si>
+    <t>0.18s</t>
+  </si>
+  <si>
     <t>TC-SEC-09</t>
   </si>
   <si>
@@ -175,6 +196,9 @@
     <t>Forms submit payloads include active unique CSRF session hashes</t>
   </si>
   <si>
+    <t>0.26s</t>
+  </si>
+  <si>
     <t>TC-SEC-10</t>
   </si>
   <si>
@@ -184,6 +208,9 @@
     <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
   </si>
   <si>
+    <t>0.47s</t>
+  </si>
+  <si>
     <t>TC-SEC-11</t>
   </si>
   <si>
@@ -193,6 +220,9 @@
     <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
   </si>
   <si>
+    <t>0.16s</t>
+  </si>
+  <si>
     <t>TC-SEC-12</t>
   </si>
   <si>
@@ -202,6 +232,9 @@
     <t>JWT tokens with altered payload contents return invalid signature key errors</t>
   </si>
   <si>
+    <t>0.35s</t>
+  </si>
+  <si>
     <t>TC-SEC-13</t>
   </si>
   <si>
@@ -220,6 +253,9 @@
     <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
   </si>
   <si>
+    <t>0.45s</t>
+  </si>
+  <si>
     <t>TC-SEC-15</t>
   </si>
   <si>
@@ -229,6 +265,9 @@
     <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
   </si>
   <si>
+    <t>0.14s</t>
+  </si>
+  <si>
     <t>TC-SEC-16</t>
   </si>
   <si>
@@ -238,6 +277,9 @@
     <t>Inactivity over 15 minutes invalidates session token automatically</t>
   </si>
   <si>
+    <t>0.34s</t>
+  </si>
+  <si>
     <t>TC-SEC-17</t>
   </si>
   <si>
@@ -256,6 +298,9 @@
     <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
   </si>
   <si>
+    <t>0.28s</t>
+  </si>
+  <si>
     <t>TC-SEC-19</t>
   </si>
   <si>
@@ -274,6 +319,9 @@
     <t>Transaction form validates amount bounds and rejects negative entries</t>
   </si>
   <si>
+    <t>0.40s</t>
+  </si>
+  <si>
     <t>TC-SEC-21</t>
   </si>
   <si>
@@ -283,6 +331,9 @@
     <t>Dates set beyond maximum future bounds are rejected</t>
   </si>
   <si>
+    <t>0.43s</t>
+  </si>
+  <si>
     <t>TC-SEC-22</t>
   </si>
   <si>
@@ -310,6 +361,9 @@
     <t>Nosniff headers prevent browsers from executing script MIME type spoofing</t>
   </si>
   <si>
+    <t>0.19s</t>
+  </si>
+  <si>
     <t>TC-SEC-25</t>
   </si>
   <si>
@@ -319,6 +373,9 @@
     <t>Server returns HSTS headers forcing browser redirects to HTTPS protocol</t>
   </si>
   <si>
+    <t>0.22s</t>
+  </si>
+  <si>
     <t>TC-SEC-26</t>
   </si>
   <si>
@@ -328,6 +385,9 @@
     <t>API rate limit blocks traffic exceeding 100 requests per minute</t>
   </si>
   <si>
+    <t>0.42s</t>
+  </si>
+  <si>
     <t>TC-SEC-27</t>
   </si>
   <si>
@@ -337,6 +397,9 @@
     <t>Requests without valid Authorization tokens fail with 401 Unauthorized</t>
   </si>
   <si>
+    <t>0.25s</t>
+  </si>
+  <si>
     <t>TC-SEC-28</t>
   </si>
   <si>
@@ -388,7 +451,7 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>6/16/2026, 4:44:00 AM</t>
+    <t>6/16/2026, 5:20:46 AM</t>
   </si>
 </sst>
 </file>
@@ -977,21 +1040,21 @@
         <v>28</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>27</v>
@@ -1000,21 +1063,21 @@
         <v>28</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>27</v>
@@ -1023,21 +1086,21 @@
         <v>28</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>27</v>
@@ -1046,21 +1109,21 @@
         <v>28</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>27</v>
@@ -1069,21 +1132,21 @@
         <v>28</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>27</v>
@@ -1092,21 +1155,21 @@
         <v>28</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>27</v>
@@ -1115,21 +1178,21 @@
         <v>28</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1138,21 +1201,21 @@
         <v>28</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>27</v>
@@ -1161,21 +1224,21 @@
         <v>28</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
@@ -1184,21 +1247,21 @@
         <v>28</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>27</v>
@@ -1207,21 +1270,21 @@
         <v>28</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>27</v>
@@ -1230,44 +1293,44 @@
         <v>28</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>27</v>
@@ -1276,21 +1339,21 @@
         <v>28</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>27</v>
@@ -1299,21 +1362,21 @@
         <v>28</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>15</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>27</v>
@@ -1322,21 +1385,21 @@
         <v>28</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>27</v>
@@ -1345,21 +1408,21 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1368,21 +1431,21 @@
         <v>28</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>15</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>27</v>
@@ -1391,21 +1454,21 @@
         <v>28</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>27</v>
@@ -1414,21 +1477,21 @@
         <v>28</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>27</v>
@@ -1437,21 +1500,21 @@
         <v>28</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>15</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
@@ -1460,21 +1523,21 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>27</v>
@@ -1483,21 +1546,21 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>27</v>
@@ -1506,21 +1569,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1529,21 +1592,21 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>15</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>27</v>
@@ -1552,21 +1615,21 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
@@ -1575,21 +1638,21 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>27</v>
@@ -1598,21 +1661,21 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>27</v>
@@ -1621,21 +1684,21 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>27</v>
@@ -1644,7 +1707,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1676,10 +1739,10 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1690,10 +1753,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
@@ -1719,24 +1782,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>24</v>
@@ -1753,13 +1816,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>28</v>
@@ -1770,13 +1833,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>28</v>
@@ -1787,13 +1850,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>28</v>
@@ -1804,13 +1867,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>28</v>
@@ -1821,13 +1884,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>28</v>
@@ -1838,13 +1901,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
@@ -1855,13 +1918,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>28</v>
@@ -1872,13 +1935,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
@@ -1889,13 +1952,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>28</v>
@@ -1906,13 +1969,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
@@ -1923,13 +1986,13 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
@@ -1940,13 +2003,13 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>28</v>
@@ -1957,13 +2020,13 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
@@ -1974,13 +2037,13 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>28</v>
@@ -1991,13 +2054,13 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>28</v>
@@ -2008,13 +2071,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>28</v>
@@ -2025,13 +2088,13 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
@@ -2042,13 +2105,13 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
@@ -2059,13 +2122,13 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>28</v>
@@ -2076,13 +2139,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>28</v>
@@ -2093,13 +2156,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>28</v>
@@ -2110,13 +2173,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>28</v>
@@ -2127,13 +2190,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>28</v>
@@ -2144,13 +2207,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>28</v>
@@ -2161,13 +2224,13 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>28</v>
@@ -2178,13 +2241,13 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>28</v>
@@ -2195,13 +2258,13 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>
@@ -2212,13 +2275,13 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>28</v>
@@ -2229,13 +2292,13 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>28</v>

--- a/reports/Security_Report.xlsx
+++ b/reports/Security_Report.xlsx
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 5:20:47 AM</t>
+    <t>6/16/2026, 5:29:22 AM</t>
   </si>
   <si>
     <t>Device Name</t>

--- a/reports/Security_Report.xlsx
+++ b/reports/Security_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="144">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>16/6/2026, 11:35:06 am</t>
+    <t>6/16/2026, 6:07:10 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>8.98s</t>
+    <t>8.62s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,228 +103,225 @@
     <t>PASS</t>
   </si>
   <si>
+    <t>0.47s</t>
+  </si>
+  <si>
+    <t>TC-SEC-02</t>
+  </si>
+  <si>
+    <t>TC-SEC-02: Dashboard search box query sanitization check against inline comment characters</t>
+  </si>
+  <si>
+    <t>Search query drops comment blocks (--) to prevent database parsing errors</t>
+  </si>
+  <si>
+    <t>0.46s</t>
+  </si>
+  <si>
+    <t>TC-SEC-03</t>
+  </si>
+  <si>
+    <t>TC-SEC-03: Transaction Description parameter validator check against SELECT union query commands</t>
+  </si>
+  <si>
+    <t>SELECT UNION query patterns in transaction description are blocked</t>
+  </si>
+  <si>
+    <t>0.23s</t>
+  </si>
+  <si>
+    <t>TC-SEC-04</t>
+  </si>
+  <si>
+    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
+  </si>
+  <si>
+    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
+  </si>
+  <si>
+    <t>0.21s</t>
+  </si>
+  <si>
+    <t>TC-SEC-05</t>
+  </si>
+  <si>
+    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
+  </si>
+  <si>
+    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
+  </si>
+  <si>
+    <t>0.31s</t>
+  </si>
+  <si>
+    <t>TC-SEC-06</t>
+  </si>
+  <si>
+    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
+  </si>
+  <si>
+    <t>Reflected query parameters from URL string are parsed and encoded</t>
+  </si>
+  <si>
+    <t>TC-SEC-07</t>
+  </si>
+  <si>
+    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
+  </si>
+  <si>
+    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
+  </si>
+  <si>
+    <t>0.24s</t>
+  </si>
+  <si>
+    <t>TC-SEC-08</t>
+  </si>
+  <si>
+    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
+  </si>
+  <si>
+    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
+  </si>
+  <si>
+    <t>0.30s</t>
+  </si>
+  <si>
+    <t>TC-SEC-09</t>
+  </si>
+  <si>
+    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
+  </si>
+  <si>
+    <t>Forms submit payloads include active unique CSRF session hashes</t>
+  </si>
+  <si>
+    <t>0.28s</t>
+  </si>
+  <si>
+    <t>TC-SEC-10</t>
+  </si>
+  <si>
+    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
+  </si>
+  <si>
+    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
+  </si>
+  <si>
+    <t>0.32s</t>
+  </si>
+  <si>
+    <t>TC-SEC-11</t>
+  </si>
+  <si>
+    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
+  </si>
+  <si>
+    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
+  </si>
+  <si>
+    <t>0.13s</t>
+  </si>
+  <si>
+    <t>TC-SEC-12</t>
+  </si>
+  <si>
+    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
+  </si>
+  <si>
+    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
+  </si>
+  <si>
+    <t>0.39s</t>
+  </si>
+  <si>
+    <t>TC-SEC-13</t>
+  </si>
+  <si>
+    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
+  </si>
+  <si>
+    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
+  </si>
+  <si>
+    <t>TC-SEC-14</t>
+  </si>
+  <si>
+    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
+  </si>
+  <si>
+    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
+  </si>
+  <si>
+    <t>0.43s</t>
+  </si>
+  <si>
+    <t>TC-SEC-15</t>
+  </si>
+  <si>
+    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
+  </si>
+  <si>
+    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
+  </si>
+  <si>
+    <t>TC-SEC-16</t>
+  </si>
+  <si>
+    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
+  </si>
+  <si>
+    <t>Inactivity over 15 minutes invalidates session token automatically</t>
+  </si>
+  <si>
+    <t>0.12s</t>
+  </si>
+  <si>
+    <t>TC-SEC-17</t>
+  </si>
+  <si>
+    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
+  </si>
+  <si>
+    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
+  </si>
+  <si>
+    <t>TC-SEC-18</t>
+  </si>
+  <si>
+    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
+  </si>
+  <si>
+    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
+  </si>
+  <si>
+    <t>0.26s</t>
+  </si>
+  <si>
+    <t>TC-SEC-19</t>
+  </si>
+  <si>
+    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
+  </si>
+  <si>
+    <t>Incorrect email formatting does not match registration criteria</t>
+  </si>
+  <si>
     <t>0.15s</t>
   </si>
   <si>
-    <t>TC-SEC-02</t>
-  </si>
-  <si>
-    <t>TC-SEC-02: Dashboard search box query sanitization check against inline comment characters</t>
-  </si>
-  <si>
-    <t>Search query drops comment blocks (--) to prevent database parsing errors</t>
-  </si>
-  <si>
-    <t>0.28s</t>
-  </si>
-  <si>
-    <t>TC-SEC-03</t>
-  </si>
-  <si>
-    <t>TC-SEC-03: Transaction Description parameter validator check against SELECT union query commands</t>
-  </si>
-  <si>
-    <t>SELECT UNION query patterns in transaction description are blocked</t>
-  </si>
-  <si>
-    <t>0.45s</t>
-  </si>
-  <si>
-    <t>TC-SEC-04</t>
-  </si>
-  <si>
-    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
-  </si>
-  <si>
-    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
-  </si>
-  <si>
-    <t>0.21s</t>
-  </si>
-  <si>
-    <t>TC-SEC-05</t>
-  </si>
-  <si>
-    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
-  </si>
-  <si>
-    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
-  </si>
-  <si>
-    <t>0.40s</t>
-  </si>
-  <si>
-    <t>TC-SEC-06</t>
-  </si>
-  <si>
-    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
-  </si>
-  <si>
-    <t>Reflected query parameters from URL string are parsed and encoded</t>
-  </si>
-  <si>
-    <t>0.26s</t>
-  </si>
-  <si>
-    <t>TC-SEC-07</t>
-  </si>
-  <si>
-    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
-  </si>
-  <si>
-    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
-  </si>
-  <si>
-    <t>0.33s</t>
-  </si>
-  <si>
-    <t>TC-SEC-08</t>
-  </si>
-  <si>
-    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
-  </si>
-  <si>
-    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
-  </si>
-  <si>
-    <t>0.37s</t>
-  </si>
-  <si>
-    <t>TC-SEC-09</t>
-  </si>
-  <si>
-    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
-  </si>
-  <si>
-    <t>Forms submit payloads include active unique CSRF session hashes</t>
-  </si>
-  <si>
-    <t>0.41s</t>
-  </si>
-  <si>
-    <t>TC-SEC-10</t>
-  </si>
-  <si>
-    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
-  </si>
-  <si>
-    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
-  </si>
-  <si>
-    <t>0.13s</t>
-  </si>
-  <si>
-    <t>TC-SEC-11</t>
-  </si>
-  <si>
-    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
-  </si>
-  <si>
-    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
-  </si>
-  <si>
-    <t>0.32s</t>
-  </si>
-  <si>
-    <t>TC-SEC-12</t>
-  </si>
-  <si>
-    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
-  </si>
-  <si>
-    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
-  </si>
-  <si>
-    <t>0.18s</t>
-  </si>
-  <si>
-    <t>TC-SEC-13</t>
-  </si>
-  <si>
-    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
-  </si>
-  <si>
-    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
-  </si>
-  <si>
-    <t>0.48s</t>
-  </si>
-  <si>
-    <t>TC-SEC-14</t>
-  </si>
-  <si>
-    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
-  </si>
-  <si>
-    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
-  </si>
-  <si>
-    <t>TC-SEC-15</t>
-  </si>
-  <si>
-    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
-  </si>
-  <si>
-    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
+    <t>TC-SEC-20</t>
+  </si>
+  <si>
+    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
+  </si>
+  <si>
+    <t>Transaction form validates amount bounds and rejects negative entries</t>
   </si>
   <si>
     <t>0.14s</t>
   </si>
   <si>
-    <t>TC-SEC-16</t>
-  </si>
-  <si>
-    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
-  </si>
-  <si>
-    <t>Inactivity over 15 minutes invalidates session token automatically</t>
-  </si>
-  <si>
-    <t>TC-SEC-17</t>
-  </si>
-  <si>
-    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
-  </si>
-  <si>
-    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
-  </si>
-  <si>
-    <t>0.27s</t>
-  </si>
-  <si>
-    <t>TC-SEC-18</t>
-  </si>
-  <si>
-    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
-  </si>
-  <si>
-    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
-  </si>
-  <si>
-    <t>0.47s</t>
-  </si>
-  <si>
-    <t>TC-SEC-19</t>
-  </si>
-  <si>
-    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
-  </si>
-  <si>
-    <t>Incorrect email formatting does not match registration criteria</t>
-  </si>
-  <si>
-    <t>0.44s</t>
-  </si>
-  <si>
-    <t>TC-SEC-20</t>
-  </si>
-  <si>
-    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
-  </si>
-  <si>
-    <t>Transaction form validates amount bounds and rejects negative entries</t>
-  </si>
-  <si>
     <t>TC-SEC-21</t>
   </si>
   <si>
@@ -334,7 +331,7 @@
     <t>Dates set beyond maximum future bounds are rejected</t>
   </si>
   <si>
-    <t>0.46s</t>
+    <t>0.25s</t>
   </si>
   <si>
     <t>TC-SEC-22</t>
@@ -367,9 +364,6 @@
     <t>Nosniff headers prevent browsers from executing script MIME type spoofing</t>
   </si>
   <si>
-    <t>0.24s</t>
-  </si>
-  <si>
     <t>TC-SEC-25</t>
   </si>
   <si>
@@ -379,7 +373,7 @@
     <t>Server returns HSTS headers forcing browser redirects to HTTPS protocol</t>
   </si>
   <si>
-    <t>0.34s</t>
+    <t>0.42s</t>
   </si>
   <si>
     <t>TC-SEC-26</t>
@@ -391,6 +385,9 @@
     <t>API rate limit blocks traffic exceeding 100 requests per minute</t>
   </si>
   <si>
+    <t>0.35s</t>
+  </si>
+  <si>
     <t>TC-SEC-27</t>
   </si>
   <si>
@@ -407,9 +404,6 @@
   </si>
   <si>
     <t>Improperly formatted Authorization header formats fail schema checks</t>
-  </si>
-  <si>
-    <t>0.39s</t>
   </si>
   <si>
     <t>TC-SEC-29</t>
@@ -1155,160 +1149,160 @@
         <v>28</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>72</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
       </c>
@@ -1316,45 +1310,45 @@
         <v>28</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="E16" s="3" t="s">
         <v>27</v>
       </c>
@@ -1362,45 +1356,45 @@
         <v>28</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="E17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>86</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="E18" s="3" t="s">
         <v>27</v>
       </c>
@@ -1408,137 +1402,137 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="E19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="E20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="E21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>101</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="E24" s="3" t="s">
         <v>27</v>
       </c>
@@ -1546,22 +1540,22 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="E25" s="3" t="s">
         <v>27</v>
       </c>
@@ -1569,68 +1563,68 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>117</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="3" t="s">
+      <c r="E26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" s="5" t="s">
         <v>119</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="3" t="s">
+      <c r="E27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>123</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
       </c>
@@ -1638,22 +1632,22 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>130</v>
-      </c>
       <c r="E29" s="3" t="s">
         <v>27</v>
       </c>
@@ -1661,22 +1655,22 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>131</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="E30" s="3" t="s">
         <v>27</v>
       </c>
@@ -1684,22 +1678,22 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="E31" s="3" t="s">
         <v>27</v>
       </c>
@@ -1707,7 +1701,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1739,10 +1733,10 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1753,10 +1747,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
@@ -1782,19 +1776,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1907,7 +1901,7 @@
         <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
@@ -1924,7 +1918,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>28</v>
@@ -1941,7 +1935,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
@@ -1958,7 +1952,7 @@
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>28</v>
@@ -1975,7 +1969,7 @@
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
@@ -1992,7 +1986,7 @@
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
@@ -2009,7 +2003,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>28</v>
@@ -2026,7 +2020,7 @@
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
@@ -2043,7 +2037,7 @@
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>28</v>
@@ -2060,7 +2054,7 @@
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>28</v>
@@ -2077,7 +2071,7 @@
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>28</v>
@@ -2094,7 +2088,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
@@ -2111,7 +2105,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
@@ -2128,7 +2122,7 @@
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>28</v>
@@ -2145,7 +2139,7 @@
         <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>28</v>
@@ -2162,7 +2156,7 @@
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>28</v>
@@ -2179,7 +2173,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>28</v>
@@ -2196,7 +2190,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>28</v>
@@ -2213,7 +2207,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>28</v>
@@ -2230,7 +2224,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>28</v>
@@ -2247,7 +2241,7 @@
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>28</v>
@@ -2264,7 +2258,7 @@
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>
@@ -2281,7 +2275,7 @@
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>28</v>
@@ -2298,7 +2292,7 @@
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>28</v>

--- a/reports/Security_Report.xlsx
+++ b/reports/Security_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="146">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 6:07:10 AM</t>
+    <t>6/16/2026, 6:27:06 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>8.62s</t>
+    <t>8.95s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,7 +103,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>0.47s</t>
+    <t>0.19s</t>
   </si>
   <si>
     <t>TC-SEC-02</t>
@@ -115,286 +115,292 @@
     <t>Search query drops comment blocks (--) to prevent database parsing errors</t>
   </si>
   <si>
+    <t>0.26s</t>
+  </si>
+  <si>
+    <t>TC-SEC-03</t>
+  </si>
+  <si>
+    <t>TC-SEC-03: Transaction Description parameter validator check against SELECT union query commands</t>
+  </si>
+  <si>
+    <t>SELECT UNION query patterns in transaction description are blocked</t>
+  </si>
+  <si>
+    <t>0.14s</t>
+  </si>
+  <si>
+    <t>TC-SEC-04</t>
+  </si>
+  <si>
+    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
+  </si>
+  <si>
+    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
+  </si>
+  <si>
+    <t>0.39s</t>
+  </si>
+  <si>
+    <t>TC-SEC-05</t>
+  </si>
+  <si>
+    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
+  </si>
+  <si>
+    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
+  </si>
+  <si>
+    <t>0.33s</t>
+  </si>
+  <si>
+    <t>TC-SEC-06</t>
+  </si>
+  <si>
+    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
+  </si>
+  <si>
+    <t>Reflected query parameters from URL string are parsed and encoded</t>
+  </si>
+  <si>
+    <t>0.38s</t>
+  </si>
+  <si>
+    <t>TC-SEC-07</t>
+  </si>
+  <si>
+    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
+  </si>
+  <si>
+    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
+  </si>
+  <si>
     <t>0.46s</t>
   </si>
   <si>
-    <t>TC-SEC-03</t>
-  </si>
-  <si>
-    <t>TC-SEC-03: Transaction Description parameter validator check against SELECT union query commands</t>
-  </si>
-  <si>
-    <t>SELECT UNION query patterns in transaction description are blocked</t>
+    <t>TC-SEC-08</t>
+  </si>
+  <si>
+    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
+  </si>
+  <si>
+    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
+  </si>
+  <si>
+    <t>0.30s</t>
+  </si>
+  <si>
+    <t>TC-SEC-09</t>
+  </si>
+  <si>
+    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
+  </si>
+  <si>
+    <t>Forms submit payloads include active unique CSRF session hashes</t>
+  </si>
+  <si>
+    <t>TC-SEC-10</t>
+  </si>
+  <si>
+    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
+  </si>
+  <si>
+    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
+  </si>
+  <si>
+    <t>0.12s</t>
+  </si>
+  <si>
+    <t>TC-SEC-11</t>
+  </si>
+  <si>
+    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
+  </si>
+  <si>
+    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
+  </si>
+  <si>
+    <t>0.45s</t>
+  </si>
+  <si>
+    <t>TC-SEC-12</t>
+  </si>
+  <si>
+    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
+  </si>
+  <si>
+    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-13</t>
+  </si>
+  <si>
+    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
+  </si>
+  <si>
+    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
+  </si>
+  <si>
+    <t>0.37s</t>
+  </si>
+  <si>
+    <t>TC-SEC-14</t>
+  </si>
+  <si>
+    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
+  </si>
+  <si>
+    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
+  </si>
+  <si>
+    <t>0.17s</t>
+  </si>
+  <si>
+    <t>TC-SEC-15</t>
+  </si>
+  <si>
+    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
+  </si>
+  <si>
+    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
+  </si>
+  <si>
+    <t>TC-SEC-16</t>
+  </si>
+  <si>
+    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
+  </si>
+  <si>
+    <t>Inactivity over 15 minutes invalidates session token automatically</t>
+  </si>
+  <si>
+    <t>0.35s</t>
+  </si>
+  <si>
+    <t>TC-SEC-17</t>
+  </si>
+  <si>
+    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
+  </si>
+  <si>
+    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
+  </si>
+  <si>
+    <t>TC-SEC-18</t>
+  </si>
+  <si>
+    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
+  </si>
+  <si>
+    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
+  </si>
+  <si>
+    <t>0.34s</t>
+  </si>
+  <si>
+    <t>TC-SEC-19</t>
+  </si>
+  <si>
+    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
+  </si>
+  <si>
+    <t>Incorrect email formatting does not match registration criteria</t>
+  </si>
+  <si>
+    <t>0.27s</t>
+  </si>
+  <si>
+    <t>TC-SEC-20</t>
+  </si>
+  <si>
+    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
+  </si>
+  <si>
+    <t>Transaction form validates amount bounds and rejects negative entries</t>
   </si>
   <si>
     <t>0.23s</t>
   </si>
   <si>
-    <t>TC-SEC-04</t>
-  </si>
-  <si>
-    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
-  </si>
-  <si>
-    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
+    <t>TC-SEC-21</t>
+  </si>
+  <si>
+    <t>TC-SEC-21: Transaction Date limits and bounds range checks validation</t>
+  </si>
+  <si>
+    <t>Dates set beyond maximum future bounds are rejected</t>
+  </si>
+  <si>
+    <t>TC-SEC-22</t>
+  </si>
+  <si>
+    <t>TC-SEC-22: X-Frame-Options: DENY clickjacking headers verification check</t>
+  </si>
+  <si>
+    <t>Server returns X-Frame-Options: DENY or SAMEORIGIN header configurations</t>
+  </si>
+  <si>
+    <t>0.16s</t>
+  </si>
+  <si>
+    <t>TC-SEC-23</t>
+  </si>
+  <si>
+    <t>TC-SEC-23: Content-Security-Policy (CSP) headers verification check</t>
+  </si>
+  <si>
+    <t>CSP header blocks execution of external script elements</t>
+  </si>
+  <si>
+    <t>0.28s</t>
+  </si>
+  <si>
+    <t>TC-SEC-24</t>
+  </si>
+  <si>
+    <t>TC-SEC-24: X-Content-Type-Options: nosniff headers check</t>
+  </si>
+  <si>
+    <t>Nosniff headers prevent browsers from executing script MIME type spoofing</t>
+  </si>
+  <si>
+    <t>0.41s</t>
+  </si>
+  <si>
+    <t>TC-SEC-25</t>
+  </si>
+  <si>
+    <t>TC-SEC-25: Strict-Transport-Security (HSTS) headers verification check</t>
+  </si>
+  <si>
+    <t>Server returns HSTS headers forcing browser redirects to HTTPS protocol</t>
+  </si>
+  <si>
+    <t>0.24s</t>
+  </si>
+  <si>
+    <t>TC-SEC-26</t>
+  </si>
+  <si>
+    <t>TC-SEC-26: API keys and client access rate limiting checking</t>
+  </si>
+  <si>
+    <t>API rate limit blocks traffic exceeding 100 requests per minute</t>
+  </si>
+  <si>
+    <t>0.44s</t>
+  </si>
+  <si>
+    <t>TC-SEC-27</t>
+  </si>
+  <si>
+    <t>TC-SEC-27: Unauthenticated client requests blocks on private API endpoints</t>
+  </si>
+  <si>
+    <t>Requests without valid Authorization tokens fail with 401 Unauthorized</t>
   </si>
   <si>
     <t>0.21s</t>
-  </si>
-  <si>
-    <t>TC-SEC-05</t>
-  </si>
-  <si>
-    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
-  </si>
-  <si>
-    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
-  </si>
-  <si>
-    <t>0.31s</t>
-  </si>
-  <si>
-    <t>TC-SEC-06</t>
-  </si>
-  <si>
-    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
-  </si>
-  <si>
-    <t>Reflected query parameters from URL string are parsed and encoded</t>
-  </si>
-  <si>
-    <t>TC-SEC-07</t>
-  </si>
-  <si>
-    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
-  </si>
-  <si>
-    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
-  </si>
-  <si>
-    <t>0.24s</t>
-  </si>
-  <si>
-    <t>TC-SEC-08</t>
-  </si>
-  <si>
-    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
-  </si>
-  <si>
-    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
-  </si>
-  <si>
-    <t>0.30s</t>
-  </si>
-  <si>
-    <t>TC-SEC-09</t>
-  </si>
-  <si>
-    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
-  </si>
-  <si>
-    <t>Forms submit payloads include active unique CSRF session hashes</t>
-  </si>
-  <si>
-    <t>0.28s</t>
-  </si>
-  <si>
-    <t>TC-SEC-10</t>
-  </si>
-  <si>
-    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
-  </si>
-  <si>
-    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
-  </si>
-  <si>
-    <t>0.32s</t>
-  </si>
-  <si>
-    <t>TC-SEC-11</t>
-  </si>
-  <si>
-    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
-  </si>
-  <si>
-    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
-  </si>
-  <si>
-    <t>0.13s</t>
-  </si>
-  <si>
-    <t>TC-SEC-12</t>
-  </si>
-  <si>
-    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
-  </si>
-  <si>
-    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
-  </si>
-  <si>
-    <t>0.39s</t>
-  </si>
-  <si>
-    <t>TC-SEC-13</t>
-  </si>
-  <si>
-    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
-  </si>
-  <si>
-    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
-  </si>
-  <si>
-    <t>TC-SEC-14</t>
-  </si>
-  <si>
-    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
-  </si>
-  <si>
-    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
-  </si>
-  <si>
-    <t>0.43s</t>
-  </si>
-  <si>
-    <t>TC-SEC-15</t>
-  </si>
-  <si>
-    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
-  </si>
-  <si>
-    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
-  </si>
-  <si>
-    <t>TC-SEC-16</t>
-  </si>
-  <si>
-    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
-  </si>
-  <si>
-    <t>Inactivity over 15 minutes invalidates session token automatically</t>
-  </si>
-  <si>
-    <t>0.12s</t>
-  </si>
-  <si>
-    <t>TC-SEC-17</t>
-  </si>
-  <si>
-    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
-  </si>
-  <si>
-    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
-  </si>
-  <si>
-    <t>TC-SEC-18</t>
-  </si>
-  <si>
-    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
-  </si>
-  <si>
-    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
-  </si>
-  <si>
-    <t>0.26s</t>
-  </si>
-  <si>
-    <t>TC-SEC-19</t>
-  </si>
-  <si>
-    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
-  </si>
-  <si>
-    <t>Incorrect email formatting does not match registration criteria</t>
-  </si>
-  <si>
-    <t>0.15s</t>
-  </si>
-  <si>
-    <t>TC-SEC-20</t>
-  </si>
-  <si>
-    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
-  </si>
-  <si>
-    <t>Transaction form validates amount bounds and rejects negative entries</t>
-  </si>
-  <si>
-    <t>0.14s</t>
-  </si>
-  <si>
-    <t>TC-SEC-21</t>
-  </si>
-  <si>
-    <t>TC-SEC-21: Transaction Date limits and bounds range checks validation</t>
-  </si>
-  <si>
-    <t>Dates set beyond maximum future bounds are rejected</t>
-  </si>
-  <si>
-    <t>0.25s</t>
-  </si>
-  <si>
-    <t>TC-SEC-22</t>
-  </si>
-  <si>
-    <t>TC-SEC-22: X-Frame-Options: DENY clickjacking headers verification check</t>
-  </si>
-  <si>
-    <t>Server returns X-Frame-Options: DENY or SAMEORIGIN header configurations</t>
-  </si>
-  <si>
-    <t>0.20s</t>
-  </si>
-  <si>
-    <t>TC-SEC-23</t>
-  </si>
-  <si>
-    <t>TC-SEC-23: Content-Security-Policy (CSP) headers verification check</t>
-  </si>
-  <si>
-    <t>CSP header blocks execution of external script elements</t>
-  </si>
-  <si>
-    <t>TC-SEC-24</t>
-  </si>
-  <si>
-    <t>TC-SEC-24: X-Content-Type-Options: nosniff headers check</t>
-  </si>
-  <si>
-    <t>Nosniff headers prevent browsers from executing script MIME type spoofing</t>
-  </si>
-  <si>
-    <t>TC-SEC-25</t>
-  </si>
-  <si>
-    <t>TC-SEC-25: Strict-Transport-Security (HSTS) headers verification check</t>
-  </si>
-  <si>
-    <t>Server returns HSTS headers forcing browser redirects to HTTPS protocol</t>
-  </si>
-  <si>
-    <t>0.42s</t>
-  </si>
-  <si>
-    <t>TC-SEC-26</t>
-  </si>
-  <si>
-    <t>TC-SEC-26: API keys and client access rate limiting checking</t>
-  </si>
-  <si>
-    <t>API rate limit blocks traffic exceeding 100 requests per minute</t>
-  </si>
-  <si>
-    <t>0.35s</t>
-  </si>
-  <si>
-    <t>TC-SEC-27</t>
-  </si>
-  <si>
-    <t>TC-SEC-27: Unauthenticated client requests blocks on private API endpoints</t>
-  </si>
-  <si>
-    <t>Requests without valid Authorization tokens fail with 401 Unauthorized</t>
   </si>
   <si>
     <t>TC-SEC-28</t>
@@ -1149,21 +1155,21 @@
         <v>28</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>27</v>
@@ -1172,21 +1178,21 @@
         <v>28</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1195,21 +1201,21 @@
         <v>28</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>27</v>
@@ -1218,7 +1224,7 @@
         <v>28</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1287,30 +1293,30 @@
         <v>28</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1356,7 +1362,7 @@
         <v>28</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1402,7 +1408,7 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1494,53 +1500,53 @@
         <v>28</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1563,21 +1569,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>52</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1586,21 +1592,21 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>27</v>
@@ -1609,21 +1615,21 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
@@ -1632,21 +1638,21 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>72</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>27</v>
@@ -1655,21 +1661,21 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>27</v>
@@ -1683,16 +1689,16 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>27</v>
@@ -1701,7 +1707,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1733,10 +1739,10 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1747,10 +1753,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
@@ -1776,19 +1782,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1901,7 +1907,7 @@
         <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
@@ -1918,7 +1924,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>28</v>
@@ -1935,7 +1941,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
@@ -2003,7 +2009,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>28</v>
@@ -2156,7 +2162,7 @@
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>28</v>
@@ -2173,7 +2179,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>28</v>
@@ -2207,7 +2213,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>28</v>
@@ -2224,7 +2230,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>28</v>
@@ -2241,7 +2247,7 @@
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>28</v>
@@ -2258,7 +2264,7 @@
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>
@@ -2275,7 +2281,7 @@
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>28</v>
@@ -2292,7 +2298,7 @@
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>28</v>

--- a/reports/Security_Report.xlsx
+++ b/reports/Security_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="144">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 6:27:06 AM</t>
+    <t>6/16/2026, 6:39:20 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>8.95s</t>
+    <t>8.59s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,7 +103,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>0.19s</t>
+    <t>0.18s</t>
   </si>
   <si>
     <t>TC-SEC-02</t>
@@ -127,268 +127,262 @@
     <t>SELECT UNION query patterns in transaction description are blocked</t>
   </si>
   <si>
+    <t>0.40s</t>
+  </si>
+  <si>
+    <t>TC-SEC-04</t>
+  </si>
+  <si>
+    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
+  </si>
+  <si>
+    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
+  </si>
+  <si>
+    <t>0.31s</t>
+  </si>
+  <si>
+    <t>TC-SEC-05</t>
+  </si>
+  <si>
+    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
+  </si>
+  <si>
+    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
+  </si>
+  <si>
+    <t>0.46s</t>
+  </si>
+  <si>
+    <t>TC-SEC-06</t>
+  </si>
+  <si>
+    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
+  </si>
+  <si>
+    <t>Reflected query parameters from URL string are parsed and encoded</t>
+  </si>
+  <si>
+    <t>0.28s</t>
+  </si>
+  <si>
+    <t>TC-SEC-07</t>
+  </si>
+  <si>
+    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
+  </si>
+  <si>
+    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
+  </si>
+  <si>
+    <t>TC-SEC-08</t>
+  </si>
+  <si>
+    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
+  </si>
+  <si>
+    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
+  </si>
+  <si>
+    <t>0.33s</t>
+  </si>
+  <si>
+    <t>TC-SEC-09</t>
+  </si>
+  <si>
+    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
+  </si>
+  <si>
+    <t>Forms submit payloads include active unique CSRF session hashes</t>
+  </si>
+  <si>
+    <t>0.29s</t>
+  </si>
+  <si>
+    <t>TC-SEC-10</t>
+  </si>
+  <si>
+    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
+  </si>
+  <si>
+    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
+  </si>
+  <si>
+    <t>0.15s</t>
+  </si>
+  <si>
+    <t>TC-SEC-11</t>
+  </si>
+  <si>
+    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
+  </si>
+  <si>
+    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
+  </si>
+  <si>
+    <t>TC-SEC-12</t>
+  </si>
+  <si>
+    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
+  </si>
+  <si>
+    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
+  </si>
+  <si>
+    <t>0.24s</t>
+  </si>
+  <si>
+    <t>TC-SEC-13</t>
+  </si>
+  <si>
+    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
+  </si>
+  <si>
+    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
+  </si>
+  <si>
+    <t>TC-SEC-14</t>
+  </si>
+  <si>
+    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
+  </si>
+  <si>
+    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
+  </si>
+  <si>
     <t>0.14s</t>
   </si>
   <si>
-    <t>TC-SEC-04</t>
-  </si>
-  <si>
-    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
-  </si>
-  <si>
-    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
+    <t>TC-SEC-15</t>
+  </si>
+  <si>
+    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
+  </si>
+  <si>
+    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
+  </si>
+  <si>
+    <t>0.37s</t>
+  </si>
+  <si>
+    <t>TC-SEC-16</t>
+  </si>
+  <si>
+    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
+  </si>
+  <si>
+    <t>Inactivity over 15 minutes invalidates session token automatically</t>
+  </si>
+  <si>
+    <t>0.34s</t>
+  </si>
+  <si>
+    <t>TC-SEC-17</t>
+  </si>
+  <si>
+    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
+  </si>
+  <si>
+    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
+  </si>
+  <si>
+    <t>0.42s</t>
+  </si>
+  <si>
+    <t>TC-SEC-18</t>
+  </si>
+  <si>
+    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
+  </si>
+  <si>
+    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
   </si>
   <si>
     <t>0.39s</t>
   </si>
   <si>
-    <t>TC-SEC-05</t>
-  </si>
-  <si>
-    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
-  </si>
-  <si>
-    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
-  </si>
-  <si>
-    <t>0.33s</t>
-  </si>
-  <si>
-    <t>TC-SEC-06</t>
-  </si>
-  <si>
-    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
-  </si>
-  <si>
-    <t>Reflected query parameters from URL string are parsed and encoded</t>
-  </si>
-  <si>
-    <t>0.38s</t>
-  </si>
-  <si>
-    <t>TC-SEC-07</t>
-  </si>
-  <si>
-    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
-  </si>
-  <si>
-    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
-  </si>
-  <si>
-    <t>0.46s</t>
-  </si>
-  <si>
-    <t>TC-SEC-08</t>
-  </si>
-  <si>
-    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
-  </si>
-  <si>
-    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
-  </si>
-  <si>
-    <t>0.30s</t>
-  </si>
-  <si>
-    <t>TC-SEC-09</t>
-  </si>
-  <si>
-    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
-  </si>
-  <si>
-    <t>Forms submit payloads include active unique CSRF session hashes</t>
-  </si>
-  <si>
-    <t>TC-SEC-10</t>
-  </si>
-  <si>
-    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
-  </si>
-  <si>
-    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
+    <t>TC-SEC-19</t>
+  </si>
+  <si>
+    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
+  </si>
+  <si>
+    <t>Incorrect email formatting does not match registration criteria</t>
+  </si>
+  <si>
+    <t>TC-SEC-20</t>
+  </si>
+  <si>
+    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
+  </si>
+  <si>
+    <t>Transaction form validates amount bounds and rejects negative entries</t>
+  </si>
+  <si>
+    <t>0.25s</t>
+  </si>
+  <si>
+    <t>TC-SEC-21</t>
+  </si>
+  <si>
+    <t>TC-SEC-21: Transaction Date limits and bounds range checks validation</t>
+  </si>
+  <si>
+    <t>Dates set beyond maximum future bounds are rejected</t>
+  </si>
+  <si>
+    <t>TC-SEC-22</t>
+  </si>
+  <si>
+    <t>TC-SEC-22: X-Frame-Options: DENY clickjacking headers verification check</t>
+  </si>
+  <si>
+    <t>Server returns X-Frame-Options: DENY or SAMEORIGIN header configurations</t>
+  </si>
+  <si>
+    <t>TC-SEC-23</t>
+  </si>
+  <si>
+    <t>TC-SEC-23: Content-Security-Policy (CSP) headers verification check</t>
+  </si>
+  <si>
+    <t>CSP header blocks execution of external script elements</t>
+  </si>
+  <si>
+    <t>0.17s</t>
+  </si>
+  <si>
+    <t>TC-SEC-24</t>
+  </si>
+  <si>
+    <t>TC-SEC-24: X-Content-Type-Options: nosniff headers check</t>
+  </si>
+  <si>
+    <t>Nosniff headers prevent browsers from executing script MIME type spoofing</t>
+  </si>
+  <si>
+    <t>0.35s</t>
+  </si>
+  <si>
+    <t>TC-SEC-25</t>
+  </si>
+  <si>
+    <t>TC-SEC-25: Strict-Transport-Security (HSTS) headers verification check</t>
+  </si>
+  <si>
+    <t>Server returns HSTS headers forcing browser redirects to HTTPS protocol</t>
+  </si>
+  <si>
+    <t>TC-SEC-26</t>
+  </si>
+  <si>
+    <t>TC-SEC-26: API keys and client access rate limiting checking</t>
+  </si>
+  <si>
+    <t>API rate limit blocks traffic exceeding 100 requests per minute</t>
   </si>
   <si>
     <t>0.12s</t>
-  </si>
-  <si>
-    <t>TC-SEC-11</t>
-  </si>
-  <si>
-    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
-  </si>
-  <si>
-    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
-  </si>
-  <si>
-    <t>0.45s</t>
-  </si>
-  <si>
-    <t>TC-SEC-12</t>
-  </si>
-  <si>
-    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
-  </si>
-  <si>
-    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-13</t>
-  </si>
-  <si>
-    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
-  </si>
-  <si>
-    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
-  </si>
-  <si>
-    <t>0.37s</t>
-  </si>
-  <si>
-    <t>TC-SEC-14</t>
-  </si>
-  <si>
-    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
-  </si>
-  <si>
-    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
-  </si>
-  <si>
-    <t>0.17s</t>
-  </si>
-  <si>
-    <t>TC-SEC-15</t>
-  </si>
-  <si>
-    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
-  </si>
-  <si>
-    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
-  </si>
-  <si>
-    <t>TC-SEC-16</t>
-  </si>
-  <si>
-    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
-  </si>
-  <si>
-    <t>Inactivity over 15 minutes invalidates session token automatically</t>
-  </si>
-  <si>
-    <t>0.35s</t>
-  </si>
-  <si>
-    <t>TC-SEC-17</t>
-  </si>
-  <si>
-    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
-  </si>
-  <si>
-    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
-  </si>
-  <si>
-    <t>TC-SEC-18</t>
-  </si>
-  <si>
-    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
-  </si>
-  <si>
-    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
-  </si>
-  <si>
-    <t>0.34s</t>
-  </si>
-  <si>
-    <t>TC-SEC-19</t>
-  </si>
-  <si>
-    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
-  </si>
-  <si>
-    <t>Incorrect email formatting does not match registration criteria</t>
-  </si>
-  <si>
-    <t>0.27s</t>
-  </si>
-  <si>
-    <t>TC-SEC-20</t>
-  </si>
-  <si>
-    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
-  </si>
-  <si>
-    <t>Transaction form validates amount bounds and rejects negative entries</t>
-  </si>
-  <si>
-    <t>0.23s</t>
-  </si>
-  <si>
-    <t>TC-SEC-21</t>
-  </si>
-  <si>
-    <t>TC-SEC-21: Transaction Date limits and bounds range checks validation</t>
-  </si>
-  <si>
-    <t>Dates set beyond maximum future bounds are rejected</t>
-  </si>
-  <si>
-    <t>TC-SEC-22</t>
-  </si>
-  <si>
-    <t>TC-SEC-22: X-Frame-Options: DENY clickjacking headers verification check</t>
-  </si>
-  <si>
-    <t>Server returns X-Frame-Options: DENY or SAMEORIGIN header configurations</t>
-  </si>
-  <si>
-    <t>0.16s</t>
-  </si>
-  <si>
-    <t>TC-SEC-23</t>
-  </si>
-  <si>
-    <t>TC-SEC-23: Content-Security-Policy (CSP) headers verification check</t>
-  </si>
-  <si>
-    <t>CSP header blocks execution of external script elements</t>
-  </si>
-  <si>
-    <t>0.28s</t>
-  </si>
-  <si>
-    <t>TC-SEC-24</t>
-  </si>
-  <si>
-    <t>TC-SEC-24: X-Content-Type-Options: nosniff headers check</t>
-  </si>
-  <si>
-    <t>Nosniff headers prevent browsers from executing script MIME type spoofing</t>
-  </si>
-  <si>
-    <t>0.41s</t>
-  </si>
-  <si>
-    <t>TC-SEC-25</t>
-  </si>
-  <si>
-    <t>TC-SEC-25: Strict-Transport-Security (HSTS) headers verification check</t>
-  </si>
-  <si>
-    <t>Server returns HSTS headers forcing browser redirects to HTTPS protocol</t>
-  </si>
-  <si>
-    <t>0.24s</t>
-  </si>
-  <si>
-    <t>TC-SEC-26</t>
-  </si>
-  <si>
-    <t>TC-SEC-26: API keys and client access rate limiting checking</t>
-  </si>
-  <si>
-    <t>API rate limit blocks traffic exceeding 100 requests per minute</t>
-  </si>
-  <si>
-    <t>0.44s</t>
   </si>
   <si>
     <t>TC-SEC-27</t>
@@ -1178,53 +1172,53 @@
         <v>28</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1270,30 +1264,30 @@
         <v>28</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1316,53 +1310,53 @@
         <v>28</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>82</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1408,21 +1402,21 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1431,21 +1425,21 @@
         <v>28</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>27</v>
@@ -1454,7 +1448,7 @@
         <v>28</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>97</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1500,7 +1494,7 @@
         <v>28</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1523,68 +1517,68 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>108</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>115</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
       </c>
@@ -1592,68 +1586,68 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="3" t="s">
+      <c r="E27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="3" t="s">
+      <c r="E28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28" s="5" t="s">
         <v>126</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="E29" s="3" t="s">
         <v>27</v>
       </c>
@@ -1661,22 +1655,22 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="E30" s="3" t="s">
         <v>27</v>
       </c>
@@ -1684,22 +1678,22 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="E31" s="3" t="s">
         <v>27</v>
       </c>
@@ -1707,7 +1701,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1739,10 +1733,10 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1753,10 +1747,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
@@ -1782,19 +1776,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1924,7 +1918,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>28</v>
@@ -1941,7 +1935,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
@@ -1992,7 +1986,7 @@
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
@@ -2026,7 +2020,7 @@
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
@@ -2043,7 +2037,7 @@
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>28</v>
@@ -2094,7 +2088,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
@@ -2111,7 +2105,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
@@ -2179,7 +2173,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>28</v>
@@ -2196,7 +2190,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>28</v>
@@ -2213,7 +2207,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>28</v>
@@ -2230,7 +2224,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>28</v>
@@ -2247,7 +2241,7 @@
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>28</v>
@@ -2264,7 +2258,7 @@
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>
@@ -2281,7 +2275,7 @@
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>28</v>
@@ -2298,7 +2292,7 @@
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>28</v>

--- a/reports/Security_Report.xlsx
+++ b/reports/Security_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="146">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 6:39:20 AM</t>
+    <t>6/16/2026, 6:44:24 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>8.59s</t>
+    <t>8.73s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,316 +103,322 @@
     <t>PASS</t>
   </si>
   <si>
+    <t>0.40s</t>
+  </si>
+  <si>
+    <t>TC-SEC-02</t>
+  </si>
+  <si>
+    <t>TC-SEC-02: Dashboard search box query sanitization check against inline comment characters</t>
+  </si>
+  <si>
+    <t>Search query drops comment blocks (--) to prevent database parsing errors</t>
+  </si>
+  <si>
+    <t>0.47s</t>
+  </si>
+  <si>
+    <t>TC-SEC-03</t>
+  </si>
+  <si>
+    <t>TC-SEC-03: Transaction Description parameter validator check against SELECT union query commands</t>
+  </si>
+  <si>
+    <t>SELECT UNION query patterns in transaction description are blocked</t>
+  </si>
+  <si>
+    <t>0.30s</t>
+  </si>
+  <si>
+    <t>TC-SEC-04</t>
+  </si>
+  <si>
+    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
+  </si>
+  <si>
+    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
+  </si>
+  <si>
+    <t>0.27s</t>
+  </si>
+  <si>
+    <t>TC-SEC-05</t>
+  </si>
+  <si>
+    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
+  </si>
+  <si>
+    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
+  </si>
+  <si>
+    <t>0.28s</t>
+  </si>
+  <si>
+    <t>TC-SEC-06</t>
+  </si>
+  <si>
+    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
+  </si>
+  <si>
+    <t>Reflected query parameters from URL string are parsed and encoded</t>
+  </si>
+  <si>
+    <t>0.21s</t>
+  </si>
+  <si>
+    <t>TC-SEC-07</t>
+  </si>
+  <si>
+    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
+  </si>
+  <si>
+    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
+  </si>
+  <si>
+    <t>0.26s</t>
+  </si>
+  <si>
+    <t>TC-SEC-08</t>
+  </si>
+  <si>
+    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
+  </si>
+  <si>
+    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
+  </si>
+  <si>
+    <t>TC-SEC-09</t>
+  </si>
+  <si>
+    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
+  </si>
+  <si>
+    <t>Forms submit payloads include active unique CSRF session hashes</t>
+  </si>
+  <si>
     <t>0.18s</t>
   </si>
   <si>
-    <t>TC-SEC-02</t>
-  </si>
-  <si>
-    <t>TC-SEC-02: Dashboard search box query sanitization check against inline comment characters</t>
-  </si>
-  <si>
-    <t>Search query drops comment blocks (--) to prevent database parsing errors</t>
-  </si>
-  <si>
-    <t>0.26s</t>
-  </si>
-  <si>
-    <t>TC-SEC-03</t>
-  </si>
-  <si>
-    <t>TC-SEC-03: Transaction Description parameter validator check against SELECT union query commands</t>
-  </si>
-  <si>
-    <t>SELECT UNION query patterns in transaction description are blocked</t>
-  </si>
-  <si>
-    <t>0.40s</t>
-  </si>
-  <si>
-    <t>TC-SEC-04</t>
-  </si>
-  <si>
-    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
-  </si>
-  <si>
-    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
-  </si>
-  <si>
-    <t>0.31s</t>
-  </si>
-  <si>
-    <t>TC-SEC-05</t>
-  </si>
-  <si>
-    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
-  </si>
-  <si>
-    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
+    <t>TC-SEC-10</t>
+  </si>
+  <si>
+    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
+  </si>
+  <si>
+    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
+  </si>
+  <si>
+    <t>TC-SEC-11</t>
+  </si>
+  <si>
+    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
+  </si>
+  <si>
+    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
+  </si>
+  <si>
+    <t>0.33s</t>
+  </si>
+  <si>
+    <t>TC-SEC-12</t>
+  </si>
+  <si>
+    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
+  </si>
+  <si>
+    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-13</t>
+  </si>
+  <si>
+    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
+  </si>
+  <si>
+    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
+  </si>
+  <si>
+    <t>0.14s</t>
+  </si>
+  <si>
+    <t>TC-SEC-14</t>
+  </si>
+  <si>
+    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
+  </si>
+  <si>
+    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
+  </si>
+  <si>
+    <t>0.38s</t>
+  </si>
+  <si>
+    <t>TC-SEC-15</t>
+  </si>
+  <si>
+    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
+  </si>
+  <si>
+    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
+  </si>
+  <si>
+    <t>0.16s</t>
+  </si>
+  <si>
+    <t>TC-SEC-16</t>
+  </si>
+  <si>
+    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
+  </si>
+  <si>
+    <t>Inactivity over 15 minutes invalidates session token automatically</t>
+  </si>
+  <si>
+    <t>TC-SEC-17</t>
+  </si>
+  <si>
+    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
+  </si>
+  <si>
+    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
+  </si>
+  <si>
+    <t>0.15s</t>
+  </si>
+  <si>
+    <t>TC-SEC-18</t>
+  </si>
+  <si>
+    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
+  </si>
+  <si>
+    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
+  </si>
+  <si>
+    <t>0.23s</t>
+  </si>
+  <si>
+    <t>TC-SEC-19</t>
+  </si>
+  <si>
+    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
+  </si>
+  <si>
+    <t>Incorrect email formatting does not match registration criteria</t>
   </si>
   <si>
     <t>0.46s</t>
   </si>
   <si>
-    <t>TC-SEC-06</t>
-  </si>
-  <si>
-    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
-  </si>
-  <si>
-    <t>Reflected query parameters from URL string are parsed and encoded</t>
-  </si>
-  <si>
-    <t>0.28s</t>
-  </si>
-  <si>
-    <t>TC-SEC-07</t>
-  </si>
-  <si>
-    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
-  </si>
-  <si>
-    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
-  </si>
-  <si>
-    <t>TC-SEC-08</t>
-  </si>
-  <si>
-    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
-  </si>
-  <si>
-    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
-  </si>
-  <si>
-    <t>0.33s</t>
-  </si>
-  <si>
-    <t>TC-SEC-09</t>
-  </si>
-  <si>
-    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
-  </si>
-  <si>
-    <t>Forms submit payloads include active unique CSRF session hashes</t>
+    <t>TC-SEC-20</t>
+  </si>
+  <si>
+    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
+  </si>
+  <si>
+    <t>Transaction form validates amount bounds and rejects negative entries</t>
+  </si>
+  <si>
+    <t>0.39s</t>
+  </si>
+  <si>
+    <t>TC-SEC-21</t>
+  </si>
+  <si>
+    <t>TC-SEC-21: Transaction Date limits and bounds range checks validation</t>
+  </si>
+  <si>
+    <t>Dates set beyond maximum future bounds are rejected</t>
+  </si>
+  <si>
+    <t>0.43s</t>
+  </si>
+  <si>
+    <t>TC-SEC-22</t>
+  </si>
+  <si>
+    <t>TC-SEC-22: X-Frame-Options: DENY clickjacking headers verification check</t>
+  </si>
+  <si>
+    <t>Server returns X-Frame-Options: DENY or SAMEORIGIN header configurations</t>
+  </si>
+  <si>
+    <t>0.34s</t>
+  </si>
+  <si>
+    <t>TC-SEC-23</t>
+  </si>
+  <si>
+    <t>TC-SEC-23: Content-Security-Policy (CSP) headers verification check</t>
+  </si>
+  <si>
+    <t>CSP header blocks execution of external script elements</t>
+  </si>
+  <si>
+    <t>0.20s</t>
+  </si>
+  <si>
+    <t>TC-SEC-24</t>
+  </si>
+  <si>
+    <t>TC-SEC-24: X-Content-Type-Options: nosniff headers check</t>
+  </si>
+  <si>
+    <t>Nosniff headers prevent browsers from executing script MIME type spoofing</t>
+  </si>
+  <si>
+    <t>0.36s</t>
+  </si>
+  <si>
+    <t>TC-SEC-25</t>
+  </si>
+  <si>
+    <t>TC-SEC-25: Strict-Transport-Security (HSTS) headers verification check</t>
+  </si>
+  <si>
+    <t>Server returns HSTS headers forcing browser redirects to HTTPS protocol</t>
+  </si>
+  <si>
+    <t>TC-SEC-26</t>
+  </si>
+  <si>
+    <t>TC-SEC-26: API keys and client access rate limiting checking</t>
+  </si>
+  <si>
+    <t>API rate limit blocks traffic exceeding 100 requests per minute</t>
+  </si>
+  <si>
+    <t>0.13s</t>
+  </si>
+  <si>
+    <t>TC-SEC-27</t>
+  </si>
+  <si>
+    <t>TC-SEC-27: Unauthenticated client requests blocks on private API endpoints</t>
+  </si>
+  <si>
+    <t>Requests without valid Authorization tokens fail with 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>TC-SEC-28</t>
+  </si>
+  <si>
+    <t>TC-SEC-28: Authorization header Bearer token schema formatting validation</t>
+  </si>
+  <si>
+    <t>Improperly formatted Authorization header formats fail schema checks</t>
+  </si>
+  <si>
+    <t>TC-SEC-29</t>
+  </si>
+  <si>
+    <t>TC-SEC-29: Access-Control-Allow-Origin wildcard denial for credentialed cross-origin requests</t>
+  </si>
+  <si>
+    <t>Server restricts CORS credentials access when wildcard is used</t>
   </si>
   <si>
     <t>0.29s</t>
-  </si>
-  <si>
-    <t>TC-SEC-10</t>
-  </si>
-  <si>
-    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
-  </si>
-  <si>
-    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
-  </si>
-  <si>
-    <t>0.15s</t>
-  </si>
-  <si>
-    <t>TC-SEC-11</t>
-  </si>
-  <si>
-    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
-  </si>
-  <si>
-    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
-  </si>
-  <si>
-    <t>TC-SEC-12</t>
-  </si>
-  <si>
-    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
-  </si>
-  <si>
-    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
-  </si>
-  <si>
-    <t>0.24s</t>
-  </si>
-  <si>
-    <t>TC-SEC-13</t>
-  </si>
-  <si>
-    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
-  </si>
-  <si>
-    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
-  </si>
-  <si>
-    <t>TC-SEC-14</t>
-  </si>
-  <si>
-    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
-  </si>
-  <si>
-    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
-  </si>
-  <si>
-    <t>0.14s</t>
-  </si>
-  <si>
-    <t>TC-SEC-15</t>
-  </si>
-  <si>
-    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
-  </si>
-  <si>
-    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
-  </si>
-  <si>
-    <t>0.37s</t>
-  </si>
-  <si>
-    <t>TC-SEC-16</t>
-  </si>
-  <si>
-    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
-  </si>
-  <si>
-    <t>Inactivity over 15 minutes invalidates session token automatically</t>
-  </si>
-  <si>
-    <t>0.34s</t>
-  </si>
-  <si>
-    <t>TC-SEC-17</t>
-  </si>
-  <si>
-    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
-  </si>
-  <si>
-    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
-  </si>
-  <si>
-    <t>0.42s</t>
-  </si>
-  <si>
-    <t>TC-SEC-18</t>
-  </si>
-  <si>
-    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
-  </si>
-  <si>
-    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
-  </si>
-  <si>
-    <t>0.39s</t>
-  </si>
-  <si>
-    <t>TC-SEC-19</t>
-  </si>
-  <si>
-    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
-  </si>
-  <si>
-    <t>Incorrect email formatting does not match registration criteria</t>
-  </si>
-  <si>
-    <t>TC-SEC-20</t>
-  </si>
-  <si>
-    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
-  </si>
-  <si>
-    <t>Transaction form validates amount bounds and rejects negative entries</t>
-  </si>
-  <si>
-    <t>0.25s</t>
-  </si>
-  <si>
-    <t>TC-SEC-21</t>
-  </si>
-  <si>
-    <t>TC-SEC-21: Transaction Date limits and bounds range checks validation</t>
-  </si>
-  <si>
-    <t>Dates set beyond maximum future bounds are rejected</t>
-  </si>
-  <si>
-    <t>TC-SEC-22</t>
-  </si>
-  <si>
-    <t>TC-SEC-22: X-Frame-Options: DENY clickjacking headers verification check</t>
-  </si>
-  <si>
-    <t>Server returns X-Frame-Options: DENY or SAMEORIGIN header configurations</t>
-  </si>
-  <si>
-    <t>TC-SEC-23</t>
-  </si>
-  <si>
-    <t>TC-SEC-23: Content-Security-Policy (CSP) headers verification check</t>
-  </si>
-  <si>
-    <t>CSP header blocks execution of external script elements</t>
-  </si>
-  <si>
-    <t>0.17s</t>
-  </si>
-  <si>
-    <t>TC-SEC-24</t>
-  </si>
-  <si>
-    <t>TC-SEC-24: X-Content-Type-Options: nosniff headers check</t>
-  </si>
-  <si>
-    <t>Nosniff headers prevent browsers from executing script MIME type spoofing</t>
-  </si>
-  <si>
-    <t>0.35s</t>
-  </si>
-  <si>
-    <t>TC-SEC-25</t>
-  </si>
-  <si>
-    <t>TC-SEC-25: Strict-Transport-Security (HSTS) headers verification check</t>
-  </si>
-  <si>
-    <t>Server returns HSTS headers forcing browser redirects to HTTPS protocol</t>
-  </si>
-  <si>
-    <t>TC-SEC-26</t>
-  </si>
-  <si>
-    <t>TC-SEC-26: API keys and client access rate limiting checking</t>
-  </si>
-  <si>
-    <t>API rate limit blocks traffic exceeding 100 requests per minute</t>
-  </si>
-  <si>
-    <t>0.12s</t>
-  </si>
-  <si>
-    <t>TC-SEC-27</t>
-  </si>
-  <si>
-    <t>TC-SEC-27: Unauthenticated client requests blocks on private API endpoints</t>
-  </si>
-  <si>
-    <t>Requests without valid Authorization tokens fail with 401 Unauthorized</t>
-  </si>
-  <si>
-    <t>0.21s</t>
-  </si>
-  <si>
-    <t>TC-SEC-28</t>
-  </si>
-  <si>
-    <t>TC-SEC-28: Authorization header Bearer token schema formatting validation</t>
-  </si>
-  <si>
-    <t>Improperly formatted Authorization header formats fail schema checks</t>
-  </si>
-  <si>
-    <t>TC-SEC-29</t>
-  </si>
-  <si>
-    <t>TC-SEC-29: Access-Control-Allow-Origin wildcard denial for credentialed cross-origin requests</t>
-  </si>
-  <si>
-    <t>Server restricts CORS credentials access when wildcard is used</t>
   </si>
   <si>
     <t>TC-SEC-30</t>
@@ -1172,21 +1178,21 @@
         <v>28</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1195,7 +1201,7 @@
         <v>28</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1241,30 +1247,30 @@
         <v>28</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1287,30 +1293,30 @@
         <v>28</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1379,76 +1385,76 @@
         <v>28</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>89</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1494,21 +1500,21 @@
         <v>28</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
@@ -1517,21 +1523,21 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>27</v>
@@ -1540,21 +1546,21 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>27</v>
@@ -1563,21 +1569,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1586,21 +1592,21 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>27</v>
@@ -1609,21 +1615,21 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
@@ -1632,21 +1638,21 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>126</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>27</v>
@@ -1655,21 +1661,21 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>27</v>
@@ -1678,21 +1684,21 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>27</v>
@@ -1701,7 +1707,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1733,10 +1739,10 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1747,10 +1753,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
@@ -1776,19 +1782,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1918,7 +1924,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>28</v>
@@ -1969,7 +1975,7 @@
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
@@ -2003,7 +2009,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>28</v>
@@ -2071,7 +2077,7 @@
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>28</v>
@@ -2088,7 +2094,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
@@ -2105,7 +2111,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
@@ -2156,7 +2162,7 @@
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>28</v>
@@ -2173,7 +2179,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>28</v>
@@ -2190,7 +2196,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>28</v>
@@ -2207,7 +2213,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>28</v>
@@ -2224,7 +2230,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>28</v>
@@ -2241,7 +2247,7 @@
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>28</v>
@@ -2258,7 +2264,7 @@
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>
@@ -2275,7 +2281,7 @@
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>28</v>
@@ -2292,7 +2298,7 @@
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>28</v>

--- a/reports/Security_Report.xlsx
+++ b/reports/Security_Report.xlsx
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 6:39:20 AM</t>
+    <t>6/16/2026, 7:20:52 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>8.59s</t>
+    <t>8.98s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,307 +103,307 @@
     <t>PASS</t>
   </si>
   <si>
+    <t>0.44s</t>
+  </si>
+  <si>
+    <t>TC-SEC-02</t>
+  </si>
+  <si>
+    <t>TC-SEC-02: Dashboard search box query sanitization check against inline comment characters</t>
+  </si>
+  <si>
+    <t>Search query drops comment blocks (--) to prevent database parsing errors</t>
+  </si>
+  <si>
+    <t>0.38s</t>
+  </si>
+  <si>
+    <t>TC-SEC-03</t>
+  </si>
+  <si>
+    <t>TC-SEC-03: Transaction Description parameter validator check against SELECT union query commands</t>
+  </si>
+  <si>
+    <t>SELECT UNION query patterns in transaction description are blocked</t>
+  </si>
+  <si>
+    <t>0.41s</t>
+  </si>
+  <si>
+    <t>TC-SEC-04</t>
+  </si>
+  <si>
+    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
+  </si>
+  <si>
+    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
+  </si>
+  <si>
+    <t>0.40s</t>
+  </si>
+  <si>
+    <t>TC-SEC-05</t>
+  </si>
+  <si>
+    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
+  </si>
+  <si>
+    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
+  </si>
+  <si>
+    <t>0.27s</t>
+  </si>
+  <si>
+    <t>TC-SEC-06</t>
+  </si>
+  <si>
+    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
+  </si>
+  <si>
+    <t>Reflected query parameters from URL string are parsed and encoded</t>
+  </si>
+  <si>
+    <t>0.28s</t>
+  </si>
+  <si>
+    <t>TC-SEC-07</t>
+  </si>
+  <si>
+    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
+  </si>
+  <si>
+    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
+  </si>
+  <si>
+    <t>0.13s</t>
+  </si>
+  <si>
+    <t>TC-SEC-08</t>
+  </si>
+  <si>
+    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
+  </si>
+  <si>
+    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
+  </si>
+  <si>
+    <t>0.21s</t>
+  </si>
+  <si>
+    <t>TC-SEC-09</t>
+  </si>
+  <si>
+    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
+  </si>
+  <si>
+    <t>Forms submit payloads include active unique CSRF session hashes</t>
+  </si>
+  <si>
+    <t>TC-SEC-10</t>
+  </si>
+  <si>
+    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
+  </si>
+  <si>
+    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
+  </si>
+  <si>
+    <t>TC-SEC-11</t>
+  </si>
+  <si>
+    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
+  </si>
+  <si>
+    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
+  </si>
+  <si>
+    <t>0.26s</t>
+  </si>
+  <si>
+    <t>TC-SEC-12</t>
+  </si>
+  <si>
+    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
+  </si>
+  <si>
+    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
+  </si>
+  <si>
+    <t>0.16s</t>
+  </si>
+  <si>
+    <t>TC-SEC-13</t>
+  </si>
+  <si>
+    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
+  </si>
+  <si>
+    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
+  </si>
+  <si>
+    <t>TC-SEC-14</t>
+  </si>
+  <si>
+    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
+  </si>
+  <si>
+    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
+  </si>
+  <si>
+    <t>0.47s</t>
+  </si>
+  <si>
+    <t>TC-SEC-15</t>
+  </si>
+  <si>
+    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
+  </si>
+  <si>
+    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
+  </si>
+  <si>
+    <t>0.46s</t>
+  </si>
+  <si>
+    <t>TC-SEC-16</t>
+  </si>
+  <si>
+    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
+  </si>
+  <si>
+    <t>Inactivity over 15 minutes invalidates session token automatically</t>
+  </si>
+  <si>
+    <t>0.25s</t>
+  </si>
+  <si>
+    <t>TC-SEC-17</t>
+  </si>
+  <si>
+    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
+  </si>
+  <si>
+    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
+  </si>
+  <si>
+    <t>TC-SEC-18</t>
+  </si>
+  <si>
+    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
+  </si>
+  <si>
+    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
+  </si>
+  <si>
+    <t>0.42s</t>
+  </si>
+  <si>
+    <t>TC-SEC-19</t>
+  </si>
+  <si>
+    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
+  </si>
+  <si>
+    <t>Incorrect email formatting does not match registration criteria</t>
+  </si>
+  <si>
+    <t>TC-SEC-20</t>
+  </si>
+  <si>
+    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
+  </si>
+  <si>
+    <t>Transaction form validates amount bounds and rejects negative entries</t>
+  </si>
+  <si>
+    <t>0.43s</t>
+  </si>
+  <si>
+    <t>TC-SEC-21</t>
+  </si>
+  <si>
+    <t>TC-SEC-21: Transaction Date limits and bounds range checks validation</t>
+  </si>
+  <si>
+    <t>Dates set beyond maximum future bounds are rejected</t>
+  </si>
+  <si>
+    <t>0.31s</t>
+  </si>
+  <si>
+    <t>TC-SEC-22</t>
+  </si>
+  <si>
+    <t>TC-SEC-22: X-Frame-Options: DENY clickjacking headers verification check</t>
+  </si>
+  <si>
+    <t>Server returns X-Frame-Options: DENY or SAMEORIGIN header configurations</t>
+  </si>
+  <si>
+    <t>0.39s</t>
+  </si>
+  <si>
+    <t>TC-SEC-23</t>
+  </si>
+  <si>
+    <t>TC-SEC-23: Content-Security-Policy (CSP) headers verification check</t>
+  </si>
+  <si>
+    <t>CSP header blocks execution of external script elements</t>
+  </si>
+  <si>
+    <t>TC-SEC-24</t>
+  </si>
+  <si>
+    <t>TC-SEC-24: X-Content-Type-Options: nosniff headers check</t>
+  </si>
+  <si>
+    <t>Nosniff headers prevent browsers from executing script MIME type spoofing</t>
+  </si>
+  <si>
+    <t>TC-SEC-25</t>
+  </si>
+  <si>
+    <t>TC-SEC-25: Strict-Transport-Security (HSTS) headers verification check</t>
+  </si>
+  <si>
+    <t>Server returns HSTS headers forcing browser redirects to HTTPS protocol</t>
+  </si>
+  <si>
+    <t>0.23s</t>
+  </si>
+  <si>
+    <t>TC-SEC-26</t>
+  </si>
+  <si>
+    <t>TC-SEC-26: API keys and client access rate limiting checking</t>
+  </si>
+  <si>
+    <t>API rate limit blocks traffic exceeding 100 requests per minute</t>
+  </si>
+  <si>
+    <t>TC-SEC-27</t>
+  </si>
+  <si>
+    <t>TC-SEC-27: Unauthenticated client requests blocks on private API endpoints</t>
+  </si>
+  <si>
+    <t>Requests without valid Authorization tokens fail with 401 Unauthorized</t>
+  </si>
+  <si>
     <t>0.18s</t>
   </si>
   <si>
-    <t>TC-SEC-02</t>
-  </si>
-  <si>
-    <t>TC-SEC-02: Dashboard search box query sanitization check against inline comment characters</t>
-  </si>
-  <si>
-    <t>Search query drops comment blocks (--) to prevent database parsing errors</t>
-  </si>
-  <si>
-    <t>0.26s</t>
-  </si>
-  <si>
-    <t>TC-SEC-03</t>
-  </si>
-  <si>
-    <t>TC-SEC-03: Transaction Description parameter validator check against SELECT union query commands</t>
-  </si>
-  <si>
-    <t>SELECT UNION query patterns in transaction description are blocked</t>
-  </si>
-  <si>
-    <t>0.40s</t>
-  </si>
-  <si>
-    <t>TC-SEC-04</t>
-  </si>
-  <si>
-    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
-  </si>
-  <si>
-    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
-  </si>
-  <si>
-    <t>0.31s</t>
-  </si>
-  <si>
-    <t>TC-SEC-05</t>
-  </si>
-  <si>
-    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
-  </si>
-  <si>
-    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
-  </si>
-  <si>
-    <t>0.46s</t>
-  </si>
-  <si>
-    <t>TC-SEC-06</t>
-  </si>
-  <si>
-    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
-  </si>
-  <si>
-    <t>Reflected query parameters from URL string are parsed and encoded</t>
-  </si>
-  <si>
-    <t>0.28s</t>
-  </si>
-  <si>
-    <t>TC-SEC-07</t>
-  </si>
-  <si>
-    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
-  </si>
-  <si>
-    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
-  </si>
-  <si>
-    <t>TC-SEC-08</t>
-  </si>
-  <si>
-    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
-  </si>
-  <si>
-    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
-  </si>
-  <si>
-    <t>0.33s</t>
-  </si>
-  <si>
-    <t>TC-SEC-09</t>
-  </si>
-  <si>
-    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
-  </si>
-  <si>
-    <t>Forms submit payloads include active unique CSRF session hashes</t>
-  </si>
-  <si>
-    <t>0.29s</t>
-  </si>
-  <si>
-    <t>TC-SEC-10</t>
-  </si>
-  <si>
-    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
-  </si>
-  <si>
-    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
-  </si>
-  <si>
-    <t>0.15s</t>
-  </si>
-  <si>
-    <t>TC-SEC-11</t>
-  </si>
-  <si>
-    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
-  </si>
-  <si>
-    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
-  </si>
-  <si>
-    <t>TC-SEC-12</t>
-  </si>
-  <si>
-    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
-  </si>
-  <si>
-    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
-  </si>
-  <si>
-    <t>0.24s</t>
-  </si>
-  <si>
-    <t>TC-SEC-13</t>
-  </si>
-  <si>
-    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
-  </si>
-  <si>
-    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
-  </si>
-  <si>
-    <t>TC-SEC-14</t>
-  </si>
-  <si>
-    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
-  </si>
-  <si>
-    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
-  </si>
-  <si>
-    <t>0.14s</t>
-  </si>
-  <si>
-    <t>TC-SEC-15</t>
-  </si>
-  <si>
-    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
-  </si>
-  <si>
-    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
-  </si>
-  <si>
-    <t>0.37s</t>
-  </si>
-  <si>
-    <t>TC-SEC-16</t>
-  </si>
-  <si>
-    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
-  </si>
-  <si>
-    <t>Inactivity over 15 minutes invalidates session token automatically</t>
-  </si>
-  <si>
-    <t>0.34s</t>
-  </si>
-  <si>
-    <t>TC-SEC-17</t>
-  </si>
-  <si>
-    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
-  </si>
-  <si>
-    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
-  </si>
-  <si>
-    <t>0.42s</t>
-  </si>
-  <si>
-    <t>TC-SEC-18</t>
-  </si>
-  <si>
-    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
-  </si>
-  <si>
-    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
-  </si>
-  <si>
-    <t>0.39s</t>
-  </si>
-  <si>
-    <t>TC-SEC-19</t>
-  </si>
-  <si>
-    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
-  </si>
-  <si>
-    <t>Incorrect email formatting does not match registration criteria</t>
-  </si>
-  <si>
-    <t>TC-SEC-20</t>
-  </si>
-  <si>
-    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
-  </si>
-  <si>
-    <t>Transaction form validates amount bounds and rejects negative entries</t>
-  </si>
-  <si>
-    <t>0.25s</t>
-  </si>
-  <si>
-    <t>TC-SEC-21</t>
-  </si>
-  <si>
-    <t>TC-SEC-21: Transaction Date limits and bounds range checks validation</t>
-  </si>
-  <si>
-    <t>Dates set beyond maximum future bounds are rejected</t>
-  </si>
-  <si>
-    <t>TC-SEC-22</t>
-  </si>
-  <si>
-    <t>TC-SEC-22: X-Frame-Options: DENY clickjacking headers verification check</t>
-  </si>
-  <si>
-    <t>Server returns X-Frame-Options: DENY or SAMEORIGIN header configurations</t>
-  </si>
-  <si>
-    <t>TC-SEC-23</t>
-  </si>
-  <si>
-    <t>TC-SEC-23: Content-Security-Policy (CSP) headers verification check</t>
-  </si>
-  <si>
-    <t>CSP header blocks execution of external script elements</t>
-  </si>
-  <si>
-    <t>0.17s</t>
-  </si>
-  <si>
-    <t>TC-SEC-24</t>
-  </si>
-  <si>
-    <t>TC-SEC-24: X-Content-Type-Options: nosniff headers check</t>
-  </si>
-  <si>
-    <t>Nosniff headers prevent browsers from executing script MIME type spoofing</t>
-  </si>
-  <si>
-    <t>0.35s</t>
-  </si>
-  <si>
-    <t>TC-SEC-25</t>
-  </si>
-  <si>
-    <t>TC-SEC-25: Strict-Transport-Security (HSTS) headers verification check</t>
-  </si>
-  <si>
-    <t>Server returns HSTS headers forcing browser redirects to HTTPS protocol</t>
-  </si>
-  <si>
-    <t>TC-SEC-26</t>
-  </si>
-  <si>
-    <t>TC-SEC-26: API keys and client access rate limiting checking</t>
-  </si>
-  <si>
-    <t>API rate limit blocks traffic exceeding 100 requests per minute</t>
+    <t>TC-SEC-28</t>
+  </si>
+  <si>
+    <t>TC-SEC-28: Authorization header Bearer token schema formatting validation</t>
+  </si>
+  <si>
+    <t>Improperly formatted Authorization header formats fail schema checks</t>
   </si>
   <si>
     <t>0.12s</t>
-  </si>
-  <si>
-    <t>TC-SEC-27</t>
-  </si>
-  <si>
-    <t>TC-SEC-27: Unauthenticated client requests blocks on private API endpoints</t>
-  </si>
-  <si>
-    <t>Requests without valid Authorization tokens fail with 401 Unauthorized</t>
-  </si>
-  <si>
-    <t>0.21s</t>
-  </si>
-  <si>
-    <t>TC-SEC-28</t>
-  </si>
-  <si>
-    <t>TC-SEC-28: Authorization header Bearer token schema formatting validation</t>
-  </si>
-  <si>
-    <t>Improperly formatted Authorization header formats fail schema checks</t>
   </si>
   <si>
     <t>TC-SEC-29</t>
@@ -1172,21 +1172,21 @@
         <v>28</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1195,21 +1195,21 @@
         <v>28</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>27</v>
@@ -1218,7 +1218,7 @@
         <v>28</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1241,30 +1241,30 @@
         <v>28</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1310,7 +1310,7 @@
         <v>28</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1402,45 +1402,45 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="E20" s="3" t="s">
         <v>27</v>
       </c>
@@ -1448,53 +1448,53 @@
         <v>28</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1517,21 +1517,21 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>41</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>27</v>
@@ -1540,7 +1540,7 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>111</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1563,30 +1563,30 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1609,53 +1609,53 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>122</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="E29" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G29" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1678,7 +1678,7 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>115</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1701,7 +1701,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1918,7 +1918,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>28</v>
@@ -1935,7 +1935,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
@@ -1969,7 +1969,7 @@
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
@@ -2088,7 +2088,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
@@ -2105,7 +2105,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
@@ -2122,7 +2122,7 @@
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>28</v>
@@ -2139,7 +2139,7 @@
         <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>28</v>
@@ -2173,7 +2173,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>28</v>
@@ -2207,7 +2207,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>28</v>
@@ -2241,7 +2241,7 @@
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>28</v>
@@ -2258,7 +2258,7 @@
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>

--- a/reports/Security_Report.xlsx
+++ b/reports/Security_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="143">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 7:20:52 AM</t>
+    <t>6/16/2026, 7:25:16 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>8.98s</t>
+    <t>8.02s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,309 +103,303 @@
     <t>PASS</t>
   </si>
   <si>
+    <t>0.20s</t>
+  </si>
+  <si>
+    <t>TC-SEC-02</t>
+  </si>
+  <si>
+    <t>TC-SEC-02: Dashboard search box query sanitization check against inline comment characters</t>
+  </si>
+  <si>
+    <t>Search query drops comment blocks (--) to prevent database parsing errors</t>
+  </si>
+  <si>
+    <t>0.14s</t>
+  </si>
+  <si>
+    <t>TC-SEC-03</t>
+  </si>
+  <si>
+    <t>TC-SEC-03: Transaction Description parameter validator check against SELECT union query commands</t>
+  </si>
+  <si>
+    <t>SELECT UNION query patterns in transaction description are blocked</t>
+  </si>
+  <si>
+    <t>0.23s</t>
+  </si>
+  <si>
+    <t>TC-SEC-04</t>
+  </si>
+  <si>
+    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
+  </si>
+  <si>
+    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
+  </si>
+  <si>
+    <t>0.26s</t>
+  </si>
+  <si>
+    <t>TC-SEC-05</t>
+  </si>
+  <si>
+    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
+  </si>
+  <si>
+    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
+  </si>
+  <si>
+    <t>0.16s</t>
+  </si>
+  <si>
+    <t>TC-SEC-06</t>
+  </si>
+  <si>
+    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
+  </si>
+  <si>
+    <t>Reflected query parameters from URL string are parsed and encoded</t>
+  </si>
+  <si>
+    <t>0.48s</t>
+  </si>
+  <si>
+    <t>TC-SEC-07</t>
+  </si>
+  <si>
+    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
+  </si>
+  <si>
+    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
+  </si>
+  <si>
+    <t>0.24s</t>
+  </si>
+  <si>
+    <t>TC-SEC-08</t>
+  </si>
+  <si>
+    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
+  </si>
+  <si>
+    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
+  </si>
+  <si>
+    <t>0.12s</t>
+  </si>
+  <si>
+    <t>TC-SEC-09</t>
+  </si>
+  <si>
+    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
+  </si>
+  <si>
+    <t>Forms submit payloads include active unique CSRF session hashes</t>
+  </si>
+  <si>
+    <t>0.40s</t>
+  </si>
+  <si>
+    <t>TC-SEC-10</t>
+  </si>
+  <si>
+    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
+  </si>
+  <si>
+    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
+  </si>
+  <si>
+    <t>0.21s</t>
+  </si>
+  <si>
+    <t>TC-SEC-11</t>
+  </si>
+  <si>
+    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
+  </si>
+  <si>
+    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
+  </si>
+  <si>
+    <t>0.31s</t>
+  </si>
+  <si>
+    <t>TC-SEC-12</t>
+  </si>
+  <si>
+    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
+  </si>
+  <si>
+    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-13</t>
+  </si>
+  <si>
+    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
+  </si>
+  <si>
+    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
+  </si>
+  <si>
+    <t>TC-SEC-14</t>
+  </si>
+  <si>
+    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
+  </si>
+  <si>
+    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
+  </si>
+  <si>
+    <t>0.35s</t>
+  </si>
+  <si>
+    <t>TC-SEC-15</t>
+  </si>
+  <si>
+    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
+  </si>
+  <si>
+    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
+  </si>
+  <si>
+    <t>0.29s</t>
+  </si>
+  <si>
+    <t>TC-SEC-16</t>
+  </si>
+  <si>
+    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
+  </si>
+  <si>
+    <t>Inactivity over 15 minutes invalidates session token automatically</t>
+  </si>
+  <si>
+    <t>0.18s</t>
+  </si>
+  <si>
+    <t>TC-SEC-17</t>
+  </si>
+  <si>
+    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
+  </si>
+  <si>
+    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
+  </si>
+  <si>
+    <t>0.30s</t>
+  </si>
+  <si>
+    <t>TC-SEC-18</t>
+  </si>
+  <si>
+    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
+  </si>
+  <si>
+    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
+  </si>
+  <si>
+    <t>TC-SEC-19</t>
+  </si>
+  <si>
+    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
+  </si>
+  <si>
+    <t>Incorrect email formatting does not match registration criteria</t>
+  </si>
+  <si>
+    <t>TC-SEC-20</t>
+  </si>
+  <si>
+    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
+  </si>
+  <si>
+    <t>Transaction form validates amount bounds and rejects negative entries</t>
+  </si>
+  <si>
+    <t>TC-SEC-21</t>
+  </si>
+  <si>
+    <t>TC-SEC-21: Transaction Date limits and bounds range checks validation</t>
+  </si>
+  <si>
+    <t>Dates set beyond maximum future bounds are rejected</t>
+  </si>
+  <si>
     <t>0.44s</t>
   </si>
   <si>
-    <t>TC-SEC-02</t>
-  </si>
-  <si>
-    <t>TC-SEC-02: Dashboard search box query sanitization check against inline comment characters</t>
-  </si>
-  <si>
-    <t>Search query drops comment blocks (--) to prevent database parsing errors</t>
-  </si>
-  <si>
-    <t>0.38s</t>
-  </si>
-  <si>
-    <t>TC-SEC-03</t>
-  </si>
-  <si>
-    <t>TC-SEC-03: Transaction Description parameter validator check against SELECT union query commands</t>
-  </si>
-  <si>
-    <t>SELECT UNION query patterns in transaction description are blocked</t>
-  </si>
-  <si>
-    <t>0.41s</t>
-  </si>
-  <si>
-    <t>TC-SEC-04</t>
-  </si>
-  <si>
-    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
-  </si>
-  <si>
-    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
-  </si>
-  <si>
-    <t>0.40s</t>
-  </si>
-  <si>
-    <t>TC-SEC-05</t>
-  </si>
-  <si>
-    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
-  </si>
-  <si>
-    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
-  </si>
-  <si>
-    <t>0.27s</t>
-  </si>
-  <si>
-    <t>TC-SEC-06</t>
-  </si>
-  <si>
-    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
-  </si>
-  <si>
-    <t>Reflected query parameters from URL string are parsed and encoded</t>
-  </si>
-  <si>
-    <t>0.28s</t>
-  </si>
-  <si>
-    <t>TC-SEC-07</t>
-  </si>
-  <si>
-    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
-  </si>
-  <si>
-    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
-  </si>
-  <si>
-    <t>0.13s</t>
-  </si>
-  <si>
-    <t>TC-SEC-08</t>
-  </si>
-  <si>
-    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
-  </si>
-  <si>
-    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
-  </si>
-  <si>
-    <t>0.21s</t>
-  </si>
-  <si>
-    <t>TC-SEC-09</t>
-  </si>
-  <si>
-    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
-  </si>
-  <si>
-    <t>Forms submit payloads include active unique CSRF session hashes</t>
-  </si>
-  <si>
-    <t>TC-SEC-10</t>
-  </si>
-  <si>
-    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
-  </si>
-  <si>
-    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
-  </si>
-  <si>
-    <t>TC-SEC-11</t>
-  </si>
-  <si>
-    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
-  </si>
-  <si>
-    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
-  </si>
-  <si>
-    <t>0.26s</t>
-  </si>
-  <si>
-    <t>TC-SEC-12</t>
-  </si>
-  <si>
-    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
-  </si>
-  <si>
-    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
-  </si>
-  <si>
-    <t>0.16s</t>
-  </si>
-  <si>
-    <t>TC-SEC-13</t>
-  </si>
-  <si>
-    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
-  </si>
-  <si>
-    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
-  </si>
-  <si>
-    <t>TC-SEC-14</t>
-  </si>
-  <si>
-    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
-  </si>
-  <si>
-    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
-  </si>
-  <si>
-    <t>0.47s</t>
-  </si>
-  <si>
-    <t>TC-SEC-15</t>
-  </si>
-  <si>
-    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
-  </si>
-  <si>
-    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
-  </si>
-  <si>
-    <t>0.46s</t>
-  </si>
-  <si>
-    <t>TC-SEC-16</t>
-  </si>
-  <si>
-    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
-  </si>
-  <si>
-    <t>Inactivity over 15 minutes invalidates session token automatically</t>
-  </si>
-  <si>
-    <t>0.25s</t>
-  </si>
-  <si>
-    <t>TC-SEC-17</t>
-  </si>
-  <si>
-    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
-  </si>
-  <si>
-    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
-  </si>
-  <si>
-    <t>TC-SEC-18</t>
-  </si>
-  <si>
-    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
-  </si>
-  <si>
-    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
-  </si>
-  <si>
-    <t>0.42s</t>
-  </si>
-  <si>
-    <t>TC-SEC-19</t>
-  </si>
-  <si>
-    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
-  </si>
-  <si>
-    <t>Incorrect email formatting does not match registration criteria</t>
-  </si>
-  <si>
-    <t>TC-SEC-20</t>
-  </si>
-  <si>
-    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
-  </si>
-  <si>
-    <t>Transaction form validates amount bounds and rejects negative entries</t>
+    <t>TC-SEC-22</t>
+  </si>
+  <si>
+    <t>TC-SEC-22: X-Frame-Options: DENY clickjacking headers verification check</t>
+  </si>
+  <si>
+    <t>Server returns X-Frame-Options: DENY or SAMEORIGIN header configurations</t>
+  </si>
+  <si>
+    <t>TC-SEC-23</t>
+  </si>
+  <si>
+    <t>TC-SEC-23: Content-Security-Policy (CSP) headers verification check</t>
+  </si>
+  <si>
+    <t>CSP header blocks execution of external script elements</t>
+  </si>
+  <si>
+    <t>TC-SEC-24</t>
+  </si>
+  <si>
+    <t>TC-SEC-24: X-Content-Type-Options: nosniff headers check</t>
+  </si>
+  <si>
+    <t>Nosniff headers prevent browsers from executing script MIME type spoofing</t>
+  </si>
+  <si>
+    <t>0.17s</t>
+  </si>
+  <si>
+    <t>TC-SEC-25</t>
+  </si>
+  <si>
+    <t>TC-SEC-25: Strict-Transport-Security (HSTS) headers verification check</t>
+  </si>
+  <si>
+    <t>Server returns HSTS headers forcing browser redirects to HTTPS protocol</t>
+  </si>
+  <si>
+    <t>TC-SEC-26</t>
+  </si>
+  <si>
+    <t>TC-SEC-26: API keys and client access rate limiting checking</t>
+  </si>
+  <si>
+    <t>API rate limit blocks traffic exceeding 100 requests per minute</t>
+  </si>
+  <si>
+    <t>TC-SEC-27</t>
+  </si>
+  <si>
+    <t>TC-SEC-27: Unauthenticated client requests blocks on private API endpoints</t>
+  </si>
+  <si>
+    <t>Requests without valid Authorization tokens fail with 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>TC-SEC-28</t>
+  </si>
+  <si>
+    <t>TC-SEC-28: Authorization header Bearer token schema formatting validation</t>
+  </si>
+  <si>
+    <t>Improperly formatted Authorization header formats fail schema checks</t>
   </si>
   <si>
     <t>0.43s</t>
   </si>
   <si>
-    <t>TC-SEC-21</t>
-  </si>
-  <si>
-    <t>TC-SEC-21: Transaction Date limits and bounds range checks validation</t>
-  </si>
-  <si>
-    <t>Dates set beyond maximum future bounds are rejected</t>
-  </si>
-  <si>
-    <t>0.31s</t>
-  </si>
-  <si>
-    <t>TC-SEC-22</t>
-  </si>
-  <si>
-    <t>TC-SEC-22: X-Frame-Options: DENY clickjacking headers verification check</t>
-  </si>
-  <si>
-    <t>Server returns X-Frame-Options: DENY or SAMEORIGIN header configurations</t>
-  </si>
-  <si>
-    <t>0.39s</t>
-  </si>
-  <si>
-    <t>TC-SEC-23</t>
-  </si>
-  <si>
-    <t>TC-SEC-23: Content-Security-Policy (CSP) headers verification check</t>
-  </si>
-  <si>
-    <t>CSP header blocks execution of external script elements</t>
-  </si>
-  <si>
-    <t>TC-SEC-24</t>
-  </si>
-  <si>
-    <t>TC-SEC-24: X-Content-Type-Options: nosniff headers check</t>
-  </si>
-  <si>
-    <t>Nosniff headers prevent browsers from executing script MIME type spoofing</t>
-  </si>
-  <si>
-    <t>TC-SEC-25</t>
-  </si>
-  <si>
-    <t>TC-SEC-25: Strict-Transport-Security (HSTS) headers verification check</t>
-  </si>
-  <si>
-    <t>Server returns HSTS headers forcing browser redirects to HTTPS protocol</t>
-  </si>
-  <si>
-    <t>0.23s</t>
-  </si>
-  <si>
-    <t>TC-SEC-26</t>
-  </si>
-  <si>
-    <t>TC-SEC-26: API keys and client access rate limiting checking</t>
-  </si>
-  <si>
-    <t>API rate limit blocks traffic exceeding 100 requests per minute</t>
-  </si>
-  <si>
-    <t>TC-SEC-27</t>
-  </si>
-  <si>
-    <t>TC-SEC-27: Unauthenticated client requests blocks on private API endpoints</t>
-  </si>
-  <si>
-    <t>Requests without valid Authorization tokens fail with 401 Unauthorized</t>
-  </si>
-  <si>
-    <t>0.18s</t>
-  </si>
-  <si>
-    <t>TC-SEC-28</t>
-  </si>
-  <si>
-    <t>TC-SEC-28: Authorization header Bearer token schema formatting validation</t>
-  </si>
-  <si>
-    <t>Improperly formatted Authorization header formats fail schema checks</t>
-  </si>
-  <si>
-    <t>0.12s</t>
-  </si>
-  <si>
     <t>TC-SEC-29</t>
   </si>
   <si>
@@ -422,6 +416,9 @@
   </si>
   <si>
     <t>Sensitive API endpoints restrict access to specific trusted domains and reject * wildcards</t>
+  </si>
+  <si>
+    <t>0.22s</t>
   </si>
   <si>
     <t>Failure Message</t>
@@ -1218,21 +1215,21 @@
         <v>28</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
@@ -1241,21 +1238,21 @@
         <v>28</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>27</v>
@@ -1264,21 +1261,21 @@
         <v>28</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>27</v>
@@ -1287,21 +1284,21 @@
         <v>28</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
@@ -1315,16 +1312,16 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>27</v>
@@ -1333,21 +1330,21 @@
         <v>28</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>27</v>
@@ -1356,21 +1353,21 @@
         <v>28</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>27</v>
@@ -1379,21 +1376,21 @@
         <v>28</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>27</v>
@@ -1402,21 +1399,21 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1425,21 +1422,21 @@
         <v>28</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>27</v>
@@ -1448,21 +1445,21 @@
         <v>28</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>27</v>
@@ -1471,7 +1468,7 @@
         <v>28</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1517,22 +1514,22 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>108</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="E24" s="3" t="s">
         <v>27</v>
       </c>
@@ -1540,30 +1537,30 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>114</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1586,22 +1583,22 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="E27" s="3" t="s">
         <v>27</v>
       </c>
@@ -1609,22 +1606,22 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
       </c>
@@ -1632,45 +1629,45 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="E29" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G29" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>132</v>
-      </c>
       <c r="E30" s="3" t="s">
         <v>27</v>
       </c>
@@ -1678,30 +1675,30 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C31" s="3" t="s">
+      <c r="E31" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G31" s="5" t="s">
         <v>134</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1733,10 +1730,10 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1747,10 +1744,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
@@ -1776,19 +1773,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1952,7 +1949,7 @@
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>28</v>
@@ -1969,7 +1966,7 @@
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
@@ -1986,7 +1983,7 @@
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
@@ -2003,7 +2000,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>28</v>
@@ -2020,7 +2017,7 @@
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
@@ -2037,7 +2034,7 @@
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>28</v>
@@ -2054,7 +2051,7 @@
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>28</v>
@@ -2071,7 +2068,7 @@
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>28</v>
@@ -2088,7 +2085,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
@@ -2105,7 +2102,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
@@ -2122,7 +2119,7 @@
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>28</v>
@@ -2173,7 +2170,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>28</v>
@@ -2190,7 +2187,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>28</v>
@@ -2224,7 +2221,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>28</v>
@@ -2241,7 +2238,7 @@
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>28</v>
@@ -2258,7 +2255,7 @@
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>
@@ -2275,7 +2272,7 @@
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>28</v>
@@ -2292,7 +2289,7 @@
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>28</v>

--- a/reports/Security_Report.xlsx
+++ b/reports/Security_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="145">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 7:20:52 AM</t>
+    <t>6/16/2026, 7:30:58 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>8.98s</t>
+    <t>10.08s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,325 +103,328 @@
     <t>PASS</t>
   </si>
   <si>
+    <t>0.47s</t>
+  </si>
+  <si>
+    <t>TC-SEC-02</t>
+  </si>
+  <si>
+    <t>TC-SEC-02: Dashboard search box query sanitization check against inline comment characters</t>
+  </si>
+  <si>
+    <t>Search query drops comment blocks (--) to prevent database parsing errors</t>
+  </si>
+  <si>
+    <t>0.42s</t>
+  </si>
+  <si>
+    <t>TC-SEC-03</t>
+  </si>
+  <si>
+    <t>TC-SEC-03: Transaction Description parameter validator check against SELECT union query commands</t>
+  </si>
+  <si>
+    <t>SELECT UNION query patterns in transaction description are blocked</t>
+  </si>
+  <si>
+    <t>0.13s</t>
+  </si>
+  <si>
+    <t>TC-SEC-04</t>
+  </si>
+  <si>
+    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
+  </si>
+  <si>
+    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
+  </si>
+  <si>
+    <t>TC-SEC-05</t>
+  </si>
+  <si>
+    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
+  </si>
+  <si>
+    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
+  </si>
+  <si>
+    <t>0.14s</t>
+  </si>
+  <si>
+    <t>TC-SEC-06</t>
+  </si>
+  <si>
+    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
+  </si>
+  <si>
+    <t>Reflected query parameters from URL string are parsed and encoded</t>
+  </si>
+  <si>
+    <t>0.34s</t>
+  </si>
+  <si>
+    <t>TC-SEC-07</t>
+  </si>
+  <si>
+    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
+  </si>
+  <si>
+    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
+  </si>
+  <si>
+    <t>TC-SEC-08</t>
+  </si>
+  <si>
+    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
+  </si>
+  <si>
+    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
+  </si>
+  <si>
+    <t>0.32s</t>
+  </si>
+  <si>
+    <t>TC-SEC-09</t>
+  </si>
+  <si>
+    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
+  </si>
+  <si>
+    <t>Forms submit payloads include active unique CSRF session hashes</t>
+  </si>
+  <si>
+    <t>0.36s</t>
+  </si>
+  <si>
+    <t>TC-SEC-10</t>
+  </si>
+  <si>
+    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
+  </si>
+  <si>
+    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
+  </si>
+  <si>
+    <t>0.22s</t>
+  </si>
+  <si>
+    <t>TC-SEC-11</t>
+  </si>
+  <si>
+    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
+  </si>
+  <si>
+    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
+  </si>
+  <si>
+    <t>0.20s</t>
+  </si>
+  <si>
+    <t>TC-SEC-12</t>
+  </si>
+  <si>
+    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
+  </si>
+  <si>
+    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-13</t>
+  </si>
+  <si>
+    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
+  </si>
+  <si>
+    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
+  </si>
+  <si>
+    <t>TC-SEC-14</t>
+  </si>
+  <si>
+    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
+  </si>
+  <si>
+    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
+  </si>
+  <si>
+    <t>0.41s</t>
+  </si>
+  <si>
+    <t>TC-SEC-15</t>
+  </si>
+  <si>
+    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
+  </si>
+  <si>
+    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
+  </si>
+  <si>
+    <t>0.48s</t>
+  </si>
+  <si>
+    <t>TC-SEC-16</t>
+  </si>
+  <si>
+    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
+  </si>
+  <si>
+    <t>Inactivity over 15 minutes invalidates session token automatically</t>
+  </si>
+  <si>
+    <t>0.45s</t>
+  </si>
+  <si>
+    <t>TC-SEC-17</t>
+  </si>
+  <si>
+    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
+  </si>
+  <si>
+    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
+  </si>
+  <si>
+    <t>TC-SEC-18</t>
+  </si>
+  <si>
+    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
+  </si>
+  <si>
+    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
+  </si>
+  <si>
+    <t>0.15s</t>
+  </si>
+  <si>
+    <t>TC-SEC-19</t>
+  </si>
+  <si>
+    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
+  </si>
+  <si>
+    <t>Incorrect email formatting does not match registration criteria</t>
+  </si>
+  <si>
+    <t>0.37s</t>
+  </si>
+  <si>
+    <t>TC-SEC-20</t>
+  </si>
+  <si>
+    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
+  </si>
+  <si>
+    <t>Transaction form validates amount bounds and rejects negative entries</t>
+  </si>
+  <si>
+    <t>0.27s</t>
+  </si>
+  <si>
+    <t>TC-SEC-21</t>
+  </si>
+  <si>
+    <t>TC-SEC-21: Transaction Date limits and bounds range checks validation</t>
+  </si>
+  <si>
+    <t>Dates set beyond maximum future bounds are rejected</t>
+  </si>
+  <si>
     <t>0.44s</t>
   </si>
   <si>
-    <t>TC-SEC-02</t>
-  </si>
-  <si>
-    <t>TC-SEC-02: Dashboard search box query sanitization check against inline comment characters</t>
-  </si>
-  <si>
-    <t>Search query drops comment blocks (--) to prevent database parsing errors</t>
-  </si>
-  <si>
-    <t>0.38s</t>
-  </si>
-  <si>
-    <t>TC-SEC-03</t>
-  </si>
-  <si>
-    <t>TC-SEC-03: Transaction Description parameter validator check against SELECT union query commands</t>
-  </si>
-  <si>
-    <t>SELECT UNION query patterns in transaction description are blocked</t>
-  </si>
-  <si>
-    <t>0.41s</t>
-  </si>
-  <si>
-    <t>TC-SEC-04</t>
-  </si>
-  <si>
-    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
-  </si>
-  <si>
-    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
-  </si>
-  <si>
-    <t>0.40s</t>
-  </si>
-  <si>
-    <t>TC-SEC-05</t>
-  </si>
-  <si>
-    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
-  </si>
-  <si>
-    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
-  </si>
-  <si>
-    <t>0.27s</t>
-  </si>
-  <si>
-    <t>TC-SEC-06</t>
-  </si>
-  <si>
-    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
-  </si>
-  <si>
-    <t>Reflected query parameters from URL string are parsed and encoded</t>
-  </si>
-  <si>
-    <t>0.28s</t>
-  </si>
-  <si>
-    <t>TC-SEC-07</t>
-  </si>
-  <si>
-    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
-  </si>
-  <si>
-    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
-  </si>
-  <si>
-    <t>0.13s</t>
-  </si>
-  <si>
-    <t>TC-SEC-08</t>
-  </si>
-  <si>
-    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
-  </si>
-  <si>
-    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
-  </si>
-  <si>
-    <t>0.21s</t>
-  </si>
-  <si>
-    <t>TC-SEC-09</t>
-  </si>
-  <si>
-    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
-  </si>
-  <si>
-    <t>Forms submit payloads include active unique CSRF session hashes</t>
-  </si>
-  <si>
-    <t>TC-SEC-10</t>
-  </si>
-  <si>
-    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
-  </si>
-  <si>
-    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
-  </si>
-  <si>
-    <t>TC-SEC-11</t>
-  </si>
-  <si>
-    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
-  </si>
-  <si>
-    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
-  </si>
-  <si>
-    <t>0.26s</t>
-  </si>
-  <si>
-    <t>TC-SEC-12</t>
-  </si>
-  <si>
-    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
-  </si>
-  <si>
-    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
-  </si>
-  <si>
-    <t>0.16s</t>
-  </si>
-  <si>
-    <t>TC-SEC-13</t>
-  </si>
-  <si>
-    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
-  </si>
-  <si>
-    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
-  </si>
-  <si>
-    <t>TC-SEC-14</t>
-  </si>
-  <si>
-    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
-  </si>
-  <si>
-    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
-  </si>
-  <si>
-    <t>0.47s</t>
-  </si>
-  <si>
-    <t>TC-SEC-15</t>
-  </si>
-  <si>
-    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
-  </si>
-  <si>
-    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
+    <t>TC-SEC-22</t>
+  </si>
+  <si>
+    <t>TC-SEC-22: X-Frame-Options: DENY clickjacking headers verification check</t>
+  </si>
+  <si>
+    <t>Server returns X-Frame-Options: DENY or SAMEORIGIN header configurations</t>
+  </si>
+  <si>
+    <t>0.35s</t>
+  </si>
+  <si>
+    <t>TC-SEC-23</t>
+  </si>
+  <si>
+    <t>TC-SEC-23: Content-Security-Policy (CSP) headers verification check</t>
+  </si>
+  <si>
+    <t>CSP header blocks execution of external script elements</t>
+  </si>
+  <si>
+    <t>TC-SEC-24</t>
+  </si>
+  <si>
+    <t>TC-SEC-24: X-Content-Type-Options: nosniff headers check</t>
+  </si>
+  <si>
+    <t>Nosniff headers prevent browsers from executing script MIME type spoofing</t>
   </si>
   <si>
     <t>0.46s</t>
   </si>
   <si>
-    <t>TC-SEC-16</t>
-  </si>
-  <si>
-    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
-  </si>
-  <si>
-    <t>Inactivity over 15 minutes invalidates session token automatically</t>
-  </si>
-  <si>
-    <t>0.25s</t>
-  </si>
-  <si>
-    <t>TC-SEC-17</t>
-  </si>
-  <si>
-    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
-  </si>
-  <si>
-    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
-  </si>
-  <si>
-    <t>TC-SEC-18</t>
-  </si>
-  <si>
-    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
-  </si>
-  <si>
-    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
-  </si>
-  <si>
-    <t>0.42s</t>
-  </si>
-  <si>
-    <t>TC-SEC-19</t>
-  </si>
-  <si>
-    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
-  </si>
-  <si>
-    <t>Incorrect email formatting does not match registration criteria</t>
-  </si>
-  <si>
-    <t>TC-SEC-20</t>
-  </si>
-  <si>
-    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
-  </si>
-  <si>
-    <t>Transaction form validates amount bounds and rejects negative entries</t>
+    <t>TC-SEC-25</t>
+  </si>
+  <si>
+    <t>TC-SEC-25: Strict-Transport-Security (HSTS) headers verification check</t>
+  </si>
+  <si>
+    <t>Server returns HSTS headers forcing browser redirects to HTTPS protocol</t>
+  </si>
+  <si>
+    <t>0.31s</t>
+  </si>
+  <si>
+    <t>TC-SEC-26</t>
+  </si>
+  <si>
+    <t>TC-SEC-26: API keys and client access rate limiting checking</t>
+  </si>
+  <si>
+    <t>API rate limit blocks traffic exceeding 100 requests per minute</t>
+  </si>
+  <si>
+    <t>TC-SEC-27</t>
+  </si>
+  <si>
+    <t>TC-SEC-27: Unauthenticated client requests blocks on private API endpoints</t>
+  </si>
+  <si>
+    <t>Requests without valid Authorization tokens fail with 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>TC-SEC-28</t>
+  </si>
+  <si>
+    <t>TC-SEC-28: Authorization header Bearer token schema formatting validation</t>
+  </si>
+  <si>
+    <t>Improperly formatted Authorization header formats fail schema checks</t>
   </si>
   <si>
     <t>0.43s</t>
   </si>
   <si>
-    <t>TC-SEC-21</t>
-  </si>
-  <si>
-    <t>TC-SEC-21: Transaction Date limits and bounds range checks validation</t>
-  </si>
-  <si>
-    <t>Dates set beyond maximum future bounds are rejected</t>
-  </si>
-  <si>
-    <t>0.31s</t>
-  </si>
-  <si>
-    <t>TC-SEC-22</t>
-  </si>
-  <si>
-    <t>TC-SEC-22: X-Frame-Options: DENY clickjacking headers verification check</t>
-  </si>
-  <si>
-    <t>Server returns X-Frame-Options: DENY or SAMEORIGIN header configurations</t>
+    <t>TC-SEC-29</t>
+  </si>
+  <si>
+    <t>TC-SEC-29: Access-Control-Allow-Origin wildcard denial for credentialed cross-origin requests</t>
+  </si>
+  <si>
+    <t>Server restricts CORS credentials access when wildcard is used</t>
+  </si>
+  <si>
+    <t>TC-SEC-30</t>
+  </si>
+  <si>
+    <t>TC-SEC-30: Verify CORS preflight headers Access-Control-Allow-Origin checks on sensitive endpoints</t>
+  </si>
+  <si>
+    <t>Sensitive API endpoints restrict access to specific trusted domains and reject * wildcards</t>
   </si>
   <si>
     <t>0.39s</t>
-  </si>
-  <si>
-    <t>TC-SEC-23</t>
-  </si>
-  <si>
-    <t>TC-SEC-23: Content-Security-Policy (CSP) headers verification check</t>
-  </si>
-  <si>
-    <t>CSP header blocks execution of external script elements</t>
-  </si>
-  <si>
-    <t>TC-SEC-24</t>
-  </si>
-  <si>
-    <t>TC-SEC-24: X-Content-Type-Options: nosniff headers check</t>
-  </si>
-  <si>
-    <t>Nosniff headers prevent browsers from executing script MIME type spoofing</t>
-  </si>
-  <si>
-    <t>TC-SEC-25</t>
-  </si>
-  <si>
-    <t>TC-SEC-25: Strict-Transport-Security (HSTS) headers verification check</t>
-  </si>
-  <si>
-    <t>Server returns HSTS headers forcing browser redirects to HTTPS protocol</t>
-  </si>
-  <si>
-    <t>0.23s</t>
-  </si>
-  <si>
-    <t>TC-SEC-26</t>
-  </si>
-  <si>
-    <t>TC-SEC-26: API keys and client access rate limiting checking</t>
-  </si>
-  <si>
-    <t>API rate limit blocks traffic exceeding 100 requests per minute</t>
-  </si>
-  <si>
-    <t>TC-SEC-27</t>
-  </si>
-  <si>
-    <t>TC-SEC-27: Unauthenticated client requests blocks on private API endpoints</t>
-  </si>
-  <si>
-    <t>Requests without valid Authorization tokens fail with 401 Unauthorized</t>
-  </si>
-  <si>
-    <t>0.18s</t>
-  </si>
-  <si>
-    <t>TC-SEC-28</t>
-  </si>
-  <si>
-    <t>TC-SEC-28: Authorization header Bearer token schema formatting validation</t>
-  </si>
-  <si>
-    <t>Improperly formatted Authorization header formats fail schema checks</t>
-  </si>
-  <si>
-    <t>0.12s</t>
-  </si>
-  <si>
-    <t>TC-SEC-29</t>
-  </si>
-  <si>
-    <t>TC-SEC-29: Access-Control-Allow-Origin wildcard denial for credentialed cross-origin requests</t>
-  </si>
-  <si>
-    <t>Server restricts CORS credentials access when wildcard is used</t>
-  </si>
-  <si>
-    <t>TC-SEC-30</t>
-  </si>
-  <si>
-    <t>TC-SEC-30: Verify CORS preflight headers Access-Control-Allow-Origin checks on sensitive endpoints</t>
-  </si>
-  <si>
-    <t>Sensitive API endpoints restrict access to specific trusted domains and reject * wildcards</t>
   </si>
   <si>
     <t>Failure Message</t>
@@ -1103,68 +1106,68 @@
         <v>28</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="E8" s="3" t="s">
         <v>27</v>
       </c>
@@ -1172,76 +1175,76 @@
         <v>28</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="E10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1287,22 +1290,22 @@
         <v>28</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
       </c>
@@ -1310,91 +1313,91 @@
         <v>28</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="E18" s="3" t="s">
         <v>27</v>
       </c>
@@ -1402,53 +1405,53 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1540,7 +1543,7 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1563,21 +1566,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1586,21 +1589,21 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>27</v>
@@ -1609,21 +1612,21 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
@@ -1632,7 +1635,7 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>125</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1678,7 +1681,7 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1701,7 +1704,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -1733,10 +1736,10 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1747,10 +1750,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
@@ -1776,19 +1779,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1867,7 +1870,7 @@
         <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>28</v>
@@ -1884,7 +1887,7 @@
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>28</v>
@@ -1901,7 +1904,7 @@
         <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
@@ -1918,7 +1921,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>28</v>
@@ -1935,7 +1938,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
@@ -1952,7 +1955,7 @@
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>28</v>
@@ -2003,7 +2006,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>28</v>
@@ -2020,7 +2023,7 @@
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
@@ -2037,7 +2040,7 @@
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>28</v>
@@ -2054,7 +2057,7 @@
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>28</v>
@@ -2071,7 +2074,7 @@
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>28</v>
@@ -2088,7 +2091,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
@@ -2105,7 +2108,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
@@ -2207,7 +2210,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>28</v>
@@ -2224,7 +2227,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>28</v>
@@ -2241,7 +2244,7 @@
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>28</v>

--- a/reports/Security_Report.xlsx
+++ b/reports/Security_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="144">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 7:30:58 AM</t>
+    <t>6/16/2026, 7:34:42 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>10.08s</t>
+    <t>8.90s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,7 +103,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>0.47s</t>
+    <t>0.41s</t>
   </si>
   <si>
     <t>TC-SEC-02</t>
@@ -115,255 +115,261 @@
     <t>Search query drops comment blocks (--) to prevent database parsing errors</t>
   </si>
   <si>
+    <t>0.48s</t>
+  </si>
+  <si>
+    <t>TC-SEC-03</t>
+  </si>
+  <si>
+    <t>TC-SEC-03: Transaction Description parameter validator check against SELECT union query commands</t>
+  </si>
+  <si>
+    <t>SELECT UNION query patterns in transaction description are blocked</t>
+  </si>
+  <si>
+    <t>0.43s</t>
+  </si>
+  <si>
+    <t>TC-SEC-04</t>
+  </si>
+  <si>
+    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
+  </si>
+  <si>
+    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
+  </si>
+  <si>
+    <t>0.23s</t>
+  </si>
+  <si>
+    <t>TC-SEC-05</t>
+  </si>
+  <si>
+    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
+  </si>
+  <si>
+    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
+  </si>
+  <si>
+    <t>0.27s</t>
+  </si>
+  <si>
+    <t>TC-SEC-06</t>
+  </si>
+  <si>
+    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
+  </si>
+  <si>
+    <t>Reflected query parameters from URL string are parsed and encoded</t>
+  </si>
+  <si>
+    <t>0.13s</t>
+  </si>
+  <si>
+    <t>TC-SEC-07</t>
+  </si>
+  <si>
+    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
+  </si>
+  <si>
+    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
+  </si>
+  <si>
+    <t>0.38s</t>
+  </si>
+  <si>
+    <t>TC-SEC-08</t>
+  </si>
+  <si>
+    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
+  </si>
+  <si>
+    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
+  </si>
+  <si>
+    <t>TC-SEC-09</t>
+  </si>
+  <si>
+    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
+  </si>
+  <si>
+    <t>Forms submit payloads include active unique CSRF session hashes</t>
+  </si>
+  <si>
+    <t>0.16s</t>
+  </si>
+  <si>
+    <t>TC-SEC-10</t>
+  </si>
+  <si>
+    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
+  </si>
+  <si>
+    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
+  </si>
+  <si>
+    <t>0.21s</t>
+  </si>
+  <si>
+    <t>TC-SEC-11</t>
+  </si>
+  <si>
+    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
+  </si>
+  <si>
+    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
+  </si>
+  <si>
+    <t>0.15s</t>
+  </si>
+  <si>
+    <t>TC-SEC-12</t>
+  </si>
+  <si>
+    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
+  </si>
+  <si>
+    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
+  </si>
+  <si>
+    <t>0.34s</t>
+  </si>
+  <si>
+    <t>TC-SEC-13</t>
+  </si>
+  <si>
+    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
+  </si>
+  <si>
+    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
+  </si>
+  <si>
+    <t>0.40s</t>
+  </si>
+  <si>
+    <t>TC-SEC-14</t>
+  </si>
+  <si>
+    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
+  </si>
+  <si>
+    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
+  </si>
+  <si>
+    <t>TC-SEC-15</t>
+  </si>
+  <si>
+    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
+  </si>
+  <si>
+    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
+  </si>
+  <si>
+    <t>0.25s</t>
+  </si>
+  <si>
+    <t>TC-SEC-16</t>
+  </si>
+  <si>
+    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
+  </si>
+  <si>
+    <t>Inactivity over 15 minutes invalidates session token automatically</t>
+  </si>
+  <si>
+    <t>0.26s</t>
+  </si>
+  <si>
+    <t>TC-SEC-17</t>
+  </si>
+  <si>
+    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
+  </si>
+  <si>
+    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
+  </si>
+  <si>
+    <t>0.36s</t>
+  </si>
+  <si>
+    <t>TC-SEC-18</t>
+  </si>
+  <si>
+    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
+  </si>
+  <si>
+    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
+  </si>
+  <si>
+    <t>0.24s</t>
+  </si>
+  <si>
+    <t>TC-SEC-19</t>
+  </si>
+  <si>
+    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
+  </si>
+  <si>
+    <t>Incorrect email formatting does not match registration criteria</t>
+  </si>
+  <si>
     <t>0.42s</t>
   </si>
   <si>
-    <t>TC-SEC-03</t>
-  </si>
-  <si>
-    <t>TC-SEC-03: Transaction Description parameter validator check against SELECT union query commands</t>
-  </si>
-  <si>
-    <t>SELECT UNION query patterns in transaction description are blocked</t>
-  </si>
-  <si>
-    <t>0.13s</t>
-  </si>
-  <si>
-    <t>TC-SEC-04</t>
-  </si>
-  <si>
-    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
-  </si>
-  <si>
-    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
-  </si>
-  <si>
-    <t>TC-SEC-05</t>
-  </si>
-  <si>
-    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
-  </si>
-  <si>
-    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
-  </si>
-  <si>
-    <t>0.14s</t>
-  </si>
-  <si>
-    <t>TC-SEC-06</t>
-  </si>
-  <si>
-    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
-  </si>
-  <si>
-    <t>Reflected query parameters from URL string are parsed and encoded</t>
-  </si>
-  <si>
-    <t>0.34s</t>
-  </si>
-  <si>
-    <t>TC-SEC-07</t>
-  </si>
-  <si>
-    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
-  </si>
-  <si>
-    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
-  </si>
-  <si>
-    <t>TC-SEC-08</t>
-  </si>
-  <si>
-    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
-  </si>
-  <si>
-    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
+    <t>TC-SEC-20</t>
+  </si>
+  <si>
+    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
+  </si>
+  <si>
+    <t>Transaction form validates amount bounds and rejects negative entries</t>
+  </si>
+  <si>
+    <t>0.39s</t>
+  </si>
+  <si>
+    <t>TC-SEC-21</t>
+  </si>
+  <si>
+    <t>TC-SEC-21: Transaction Date limits and bounds range checks validation</t>
+  </si>
+  <si>
+    <t>Dates set beyond maximum future bounds are rejected</t>
+  </si>
+  <si>
+    <t>TC-SEC-22</t>
+  </si>
+  <si>
+    <t>TC-SEC-22: X-Frame-Options: DENY clickjacking headers verification check</t>
+  </si>
+  <si>
+    <t>Server returns X-Frame-Options: DENY or SAMEORIGIN header configurations</t>
+  </si>
+  <si>
+    <t>TC-SEC-23</t>
+  </si>
+  <si>
+    <t>TC-SEC-23: Content-Security-Policy (CSP) headers verification check</t>
+  </si>
+  <si>
+    <t>CSP header blocks execution of external script elements</t>
+  </si>
+  <si>
+    <t>0.37s</t>
+  </si>
+  <si>
+    <t>TC-SEC-24</t>
+  </si>
+  <si>
+    <t>TC-SEC-24: X-Content-Type-Options: nosniff headers check</t>
+  </si>
+  <si>
+    <t>Nosniff headers prevent browsers from executing script MIME type spoofing</t>
   </si>
   <si>
     <t>0.32s</t>
   </si>
   <si>
-    <t>TC-SEC-09</t>
-  </si>
-  <si>
-    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
-  </si>
-  <si>
-    <t>Forms submit payloads include active unique CSRF session hashes</t>
-  </si>
-  <si>
-    <t>0.36s</t>
-  </si>
-  <si>
-    <t>TC-SEC-10</t>
-  </si>
-  <si>
-    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
-  </si>
-  <si>
-    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
-  </si>
-  <si>
-    <t>0.22s</t>
-  </si>
-  <si>
-    <t>TC-SEC-11</t>
-  </si>
-  <si>
-    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
-  </si>
-  <si>
-    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
-  </si>
-  <si>
-    <t>0.20s</t>
-  </si>
-  <si>
-    <t>TC-SEC-12</t>
-  </si>
-  <si>
-    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
-  </si>
-  <si>
-    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-13</t>
-  </si>
-  <si>
-    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
-  </si>
-  <si>
-    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
-  </si>
-  <si>
-    <t>TC-SEC-14</t>
-  </si>
-  <si>
-    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
-  </si>
-  <si>
-    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
-  </si>
-  <si>
-    <t>0.41s</t>
-  </si>
-  <si>
-    <t>TC-SEC-15</t>
-  </si>
-  <si>
-    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
-  </si>
-  <si>
-    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
-  </si>
-  <si>
-    <t>0.48s</t>
-  </si>
-  <si>
-    <t>TC-SEC-16</t>
-  </si>
-  <si>
-    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
-  </si>
-  <si>
-    <t>Inactivity over 15 minutes invalidates session token automatically</t>
-  </si>
-  <si>
-    <t>0.45s</t>
-  </si>
-  <si>
-    <t>TC-SEC-17</t>
-  </si>
-  <si>
-    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
-  </si>
-  <si>
-    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
-  </si>
-  <si>
-    <t>TC-SEC-18</t>
-  </si>
-  <si>
-    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
-  </si>
-  <si>
-    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
-  </si>
-  <si>
-    <t>0.15s</t>
-  </si>
-  <si>
-    <t>TC-SEC-19</t>
-  </si>
-  <si>
-    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
-  </si>
-  <si>
-    <t>Incorrect email formatting does not match registration criteria</t>
-  </si>
-  <si>
-    <t>0.37s</t>
-  </si>
-  <si>
-    <t>TC-SEC-20</t>
-  </si>
-  <si>
-    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
-  </si>
-  <si>
-    <t>Transaction form validates amount bounds and rejects negative entries</t>
-  </si>
-  <si>
-    <t>0.27s</t>
-  </si>
-  <si>
-    <t>TC-SEC-21</t>
-  </si>
-  <si>
-    <t>TC-SEC-21: Transaction Date limits and bounds range checks validation</t>
-  </si>
-  <si>
-    <t>Dates set beyond maximum future bounds are rejected</t>
-  </si>
-  <si>
-    <t>0.44s</t>
-  </si>
-  <si>
-    <t>TC-SEC-22</t>
-  </si>
-  <si>
-    <t>TC-SEC-22: X-Frame-Options: DENY clickjacking headers verification check</t>
-  </si>
-  <si>
-    <t>Server returns X-Frame-Options: DENY or SAMEORIGIN header configurations</t>
-  </si>
-  <si>
-    <t>0.35s</t>
-  </si>
-  <si>
-    <t>TC-SEC-23</t>
-  </si>
-  <si>
-    <t>TC-SEC-23: Content-Security-Policy (CSP) headers verification check</t>
-  </si>
-  <si>
-    <t>CSP header blocks execution of external script elements</t>
-  </si>
-  <si>
-    <t>TC-SEC-24</t>
-  </si>
-  <si>
-    <t>TC-SEC-24: X-Content-Type-Options: nosniff headers check</t>
-  </si>
-  <si>
-    <t>Nosniff headers prevent browsers from executing script MIME type spoofing</t>
-  </si>
-  <si>
-    <t>0.46s</t>
-  </si>
-  <si>
     <t>TC-SEC-25</t>
   </si>
   <si>
@@ -373,9 +379,6 @@
     <t>Server returns HSTS headers forcing browser redirects to HTTPS protocol</t>
   </si>
   <si>
-    <t>0.31s</t>
-  </si>
-  <si>
     <t>TC-SEC-26</t>
   </si>
   <si>
@@ -403,9 +406,6 @@
     <t>Improperly formatted Authorization header formats fail schema checks</t>
   </si>
   <si>
-    <t>0.43s</t>
-  </si>
-  <si>
     <t>TC-SEC-29</t>
   </si>
   <si>
@@ -422,9 +422,6 @@
   </si>
   <si>
     <t>Sensitive API endpoints restrict access to specific trusted domains and reject * wildcards</t>
-  </si>
-  <si>
-    <t>0.39s</t>
   </si>
   <si>
     <t>Failure Message</t>
@@ -1106,21 +1103,21 @@
         <v>28</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>27</v>
@@ -1129,21 +1126,21 @@
         <v>28</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>27</v>
@@ -1152,21 +1149,21 @@
         <v>28</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>27</v>
@@ -1175,21 +1172,21 @@
         <v>28</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1198,21 +1195,21 @@
         <v>28</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>27</v>
@@ -1221,21 +1218,21 @@
         <v>28</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
@@ -1244,21 +1241,21 @@
         <v>28</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>27</v>
@@ -1267,21 +1264,21 @@
         <v>28</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>27</v>
@@ -1290,21 +1287,21 @@
         <v>28</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
@@ -1313,21 +1310,21 @@
         <v>28</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>27</v>
@@ -1336,21 +1333,21 @@
         <v>28</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>27</v>
@@ -1359,21 +1356,21 @@
         <v>28</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>27</v>
@@ -1382,21 +1379,21 @@
         <v>28</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>27</v>
@@ -1405,21 +1402,21 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1428,21 +1425,21 @@
         <v>28</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>27</v>
@@ -1451,21 +1448,21 @@
         <v>28</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>27</v>
@@ -1474,21 +1471,21 @@
         <v>28</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>27</v>
@@ -1497,21 +1494,21 @@
         <v>28</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
@@ -1520,21 +1517,21 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>27</v>
@@ -1543,21 +1540,21 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>27</v>
@@ -1566,21 +1563,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1589,21 +1586,21 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>27</v>
@@ -1612,21 +1609,21 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>96</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
@@ -1635,21 +1632,21 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>27</v>
@@ -1658,7 +1655,7 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1681,7 +1678,7 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1704,7 +1701,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1736,10 +1733,10 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1750,10 +1747,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
@@ -1779,19 +1776,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1870,7 +1867,7 @@
         <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>28</v>
@@ -1887,7 +1884,7 @@
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>28</v>
@@ -1904,7 +1901,7 @@
         <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
@@ -1921,7 +1918,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>28</v>
@@ -1938,7 +1935,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
@@ -1955,7 +1952,7 @@
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>28</v>
@@ -1972,7 +1969,7 @@
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
@@ -1989,7 +1986,7 @@
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
@@ -2006,7 +2003,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>28</v>
@@ -2023,7 +2020,7 @@
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
@@ -2040,7 +2037,7 @@
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>28</v>
@@ -2057,7 +2054,7 @@
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>28</v>
@@ -2074,7 +2071,7 @@
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>28</v>
@@ -2091,7 +2088,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
@@ -2108,7 +2105,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
@@ -2125,7 +2122,7 @@
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>28</v>
@@ -2142,7 +2139,7 @@
         <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>28</v>
@@ -2159,7 +2156,7 @@
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>28</v>
@@ -2176,7 +2173,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>28</v>
@@ -2193,7 +2190,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>28</v>
@@ -2210,7 +2207,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>28</v>
@@ -2227,7 +2224,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>28</v>
@@ -2244,7 +2241,7 @@
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>28</v>
@@ -2261,7 +2258,7 @@
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>

--- a/reports/Security_Report.xlsx
+++ b/reports/Security_Report.xlsx
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 7:30:58 AM</t>
+    <t>6/18/2026, 5:58:12 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>10.08s</t>
+    <t>8.52s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,7 +103,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>0.47s</t>
+    <t>0.12s</t>
   </si>
   <si>
     <t>TC-SEC-02</t>
@@ -115,306 +115,306 @@
     <t>Search query drops comment blocks (--) to prevent database parsing errors</t>
   </si>
   <si>
+    <t>0.32s</t>
+  </si>
+  <si>
+    <t>TC-SEC-03</t>
+  </si>
+  <si>
+    <t>TC-SEC-03: Transaction Description parameter validator check against SELECT union query commands</t>
+  </si>
+  <si>
+    <t>SELECT UNION query patterns in transaction description are blocked</t>
+  </si>
+  <si>
     <t>0.42s</t>
   </si>
   <si>
-    <t>TC-SEC-03</t>
-  </si>
-  <si>
-    <t>TC-SEC-03: Transaction Description parameter validator check against SELECT union query commands</t>
-  </si>
-  <si>
-    <t>SELECT UNION query patterns in transaction description are blocked</t>
+    <t>TC-SEC-04</t>
+  </si>
+  <si>
+    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
+  </si>
+  <si>
+    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
+  </si>
+  <si>
+    <t>0.29s</t>
+  </si>
+  <si>
+    <t>TC-SEC-05</t>
+  </si>
+  <si>
+    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
+  </si>
+  <si>
+    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
+  </si>
+  <si>
+    <t>0.25s</t>
+  </si>
+  <si>
+    <t>TC-SEC-06</t>
+  </si>
+  <si>
+    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
+  </si>
+  <si>
+    <t>Reflected query parameters from URL string are parsed and encoded</t>
+  </si>
+  <si>
+    <t>0.28s</t>
+  </si>
+  <si>
+    <t>TC-SEC-07</t>
+  </si>
+  <si>
+    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
+  </si>
+  <si>
+    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
+  </si>
+  <si>
+    <t>0.19s</t>
+  </si>
+  <si>
+    <t>TC-SEC-08</t>
+  </si>
+  <si>
+    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
+  </si>
+  <si>
+    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
+  </si>
+  <si>
+    <t>0.45s</t>
+  </si>
+  <si>
+    <t>TC-SEC-09</t>
+  </si>
+  <si>
+    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
+  </si>
+  <si>
+    <t>Forms submit payloads include active unique CSRF session hashes</t>
+  </si>
+  <si>
+    <t>0.18s</t>
+  </si>
+  <si>
+    <t>TC-SEC-10</t>
+  </si>
+  <si>
+    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
+  </si>
+  <si>
+    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
+  </si>
+  <si>
+    <t>TC-SEC-11</t>
+  </si>
+  <si>
+    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
+  </si>
+  <si>
+    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
+  </si>
+  <si>
+    <t>0.27s</t>
+  </si>
+  <si>
+    <t>TC-SEC-12</t>
+  </si>
+  <si>
+    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
+  </si>
+  <si>
+    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
   </si>
   <si>
     <t>0.13s</t>
   </si>
   <si>
-    <t>TC-SEC-04</t>
-  </si>
-  <si>
-    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
-  </si>
-  <si>
-    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
-  </si>
-  <si>
-    <t>TC-SEC-05</t>
-  </si>
-  <si>
-    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
-  </si>
-  <si>
-    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
+    <t>TC-SEC-13</t>
+  </si>
+  <si>
+    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
+  </si>
+  <si>
+    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
+  </si>
+  <si>
+    <t>0.16s</t>
+  </si>
+  <si>
+    <t>TC-SEC-14</t>
+  </si>
+  <si>
+    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
+  </si>
+  <si>
+    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
+  </si>
+  <si>
+    <t>TC-SEC-15</t>
+  </si>
+  <si>
+    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
+  </si>
+  <si>
+    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
+  </si>
+  <si>
+    <t>TC-SEC-16</t>
+  </si>
+  <si>
+    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
+  </si>
+  <si>
+    <t>Inactivity over 15 minutes invalidates session token automatically</t>
+  </si>
+  <si>
+    <t>0.40s</t>
+  </si>
+  <si>
+    <t>TC-SEC-17</t>
+  </si>
+  <si>
+    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
+  </si>
+  <si>
+    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
+  </si>
+  <si>
+    <t>0.26s</t>
+  </si>
+  <si>
+    <t>TC-SEC-18</t>
+  </si>
+  <si>
+    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
+  </si>
+  <si>
+    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
+  </si>
+  <si>
+    <t>TC-SEC-19</t>
+  </si>
+  <si>
+    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
+  </si>
+  <si>
+    <t>Incorrect email formatting does not match registration criteria</t>
+  </si>
+  <si>
+    <t>0.17s</t>
+  </si>
+  <si>
+    <t>TC-SEC-20</t>
+  </si>
+  <si>
+    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
+  </si>
+  <si>
+    <t>Transaction form validates amount bounds and rejects negative entries</t>
+  </si>
+  <si>
+    <t>0.35s</t>
+  </si>
+  <si>
+    <t>TC-SEC-21</t>
+  </si>
+  <si>
+    <t>TC-SEC-21: Transaction Date limits and bounds range checks validation</t>
+  </si>
+  <si>
+    <t>Dates set beyond maximum future bounds are rejected</t>
+  </si>
+  <si>
+    <t>0.43s</t>
+  </si>
+  <si>
+    <t>TC-SEC-22</t>
+  </si>
+  <si>
+    <t>TC-SEC-22: X-Frame-Options: DENY clickjacking headers verification check</t>
+  </si>
+  <si>
+    <t>Server returns X-Frame-Options: DENY or SAMEORIGIN header configurations</t>
+  </si>
+  <si>
+    <t>TC-SEC-23</t>
+  </si>
+  <si>
+    <t>TC-SEC-23: Content-Security-Policy (CSP) headers verification check</t>
+  </si>
+  <si>
+    <t>CSP header blocks execution of external script elements</t>
+  </si>
+  <si>
+    <t>TC-SEC-24</t>
+  </si>
+  <si>
+    <t>TC-SEC-24: X-Content-Type-Options: nosniff headers check</t>
+  </si>
+  <si>
+    <t>Nosniff headers prevent browsers from executing script MIME type spoofing</t>
+  </si>
+  <si>
+    <t>TC-SEC-25</t>
+  </si>
+  <si>
+    <t>TC-SEC-25: Strict-Transport-Security (HSTS) headers verification check</t>
+  </si>
+  <si>
+    <t>Server returns HSTS headers forcing browser redirects to HTTPS protocol</t>
+  </si>
+  <si>
+    <t>0.30s</t>
+  </si>
+  <si>
+    <t>TC-SEC-26</t>
+  </si>
+  <si>
+    <t>TC-SEC-26: API keys and client access rate limiting checking</t>
+  </si>
+  <si>
+    <t>API rate limit blocks traffic exceeding 100 requests per minute</t>
+  </si>
+  <si>
+    <t>0.22s</t>
+  </si>
+  <si>
+    <t>TC-SEC-27</t>
+  </si>
+  <si>
+    <t>TC-SEC-27: Unauthenticated client requests blocks on private API endpoints</t>
+  </si>
+  <si>
+    <t>Requests without valid Authorization tokens fail with 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>TC-SEC-28</t>
+  </si>
+  <si>
+    <t>TC-SEC-28: Authorization header Bearer token schema formatting validation</t>
+  </si>
+  <si>
+    <t>Improperly formatted Authorization header formats fail schema checks</t>
+  </si>
+  <si>
+    <t>TC-SEC-29</t>
+  </si>
+  <si>
+    <t>TC-SEC-29: Access-Control-Allow-Origin wildcard denial for credentialed cross-origin requests</t>
+  </si>
+  <si>
+    <t>Server restricts CORS credentials access when wildcard is used</t>
   </si>
   <si>
     <t>0.14s</t>
   </si>
   <si>
-    <t>TC-SEC-06</t>
-  </si>
-  <si>
-    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
-  </si>
-  <si>
-    <t>Reflected query parameters from URL string are parsed and encoded</t>
-  </si>
-  <si>
-    <t>0.34s</t>
-  </si>
-  <si>
-    <t>TC-SEC-07</t>
-  </si>
-  <si>
-    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
-  </si>
-  <si>
-    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
-  </si>
-  <si>
-    <t>TC-SEC-08</t>
-  </si>
-  <si>
-    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
-  </si>
-  <si>
-    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
-  </si>
-  <si>
-    <t>0.32s</t>
-  </si>
-  <si>
-    <t>TC-SEC-09</t>
-  </si>
-  <si>
-    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
-  </si>
-  <si>
-    <t>Forms submit payloads include active unique CSRF session hashes</t>
-  </si>
-  <si>
-    <t>0.36s</t>
-  </si>
-  <si>
-    <t>TC-SEC-10</t>
-  </si>
-  <si>
-    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
-  </si>
-  <si>
-    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
-  </si>
-  <si>
-    <t>0.22s</t>
-  </si>
-  <si>
-    <t>TC-SEC-11</t>
-  </si>
-  <si>
-    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
-  </si>
-  <si>
-    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
-  </si>
-  <si>
-    <t>0.20s</t>
-  </si>
-  <si>
-    <t>TC-SEC-12</t>
-  </si>
-  <si>
-    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
-  </si>
-  <si>
-    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-13</t>
-  </si>
-  <si>
-    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
-  </si>
-  <si>
-    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
-  </si>
-  <si>
-    <t>TC-SEC-14</t>
-  </si>
-  <si>
-    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
-  </si>
-  <si>
-    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
-  </si>
-  <si>
-    <t>0.41s</t>
-  </si>
-  <si>
-    <t>TC-SEC-15</t>
-  </si>
-  <si>
-    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
-  </si>
-  <si>
-    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
-  </si>
-  <si>
-    <t>0.48s</t>
-  </si>
-  <si>
-    <t>TC-SEC-16</t>
-  </si>
-  <si>
-    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
-  </si>
-  <si>
-    <t>Inactivity over 15 minutes invalidates session token automatically</t>
-  </si>
-  <si>
-    <t>0.45s</t>
-  </si>
-  <si>
-    <t>TC-SEC-17</t>
-  </si>
-  <si>
-    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
-  </si>
-  <si>
-    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
-  </si>
-  <si>
-    <t>TC-SEC-18</t>
-  </si>
-  <si>
-    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
-  </si>
-  <si>
-    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
-  </si>
-  <si>
-    <t>0.15s</t>
-  </si>
-  <si>
-    <t>TC-SEC-19</t>
-  </si>
-  <si>
-    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
-  </si>
-  <si>
-    <t>Incorrect email formatting does not match registration criteria</t>
-  </si>
-  <si>
-    <t>0.37s</t>
-  </si>
-  <si>
-    <t>TC-SEC-20</t>
-  </si>
-  <si>
-    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
-  </si>
-  <si>
-    <t>Transaction form validates amount bounds and rejects negative entries</t>
-  </si>
-  <si>
-    <t>0.27s</t>
-  </si>
-  <si>
-    <t>TC-SEC-21</t>
-  </si>
-  <si>
-    <t>TC-SEC-21: Transaction Date limits and bounds range checks validation</t>
-  </si>
-  <si>
-    <t>Dates set beyond maximum future bounds are rejected</t>
-  </si>
-  <si>
-    <t>0.44s</t>
-  </si>
-  <si>
-    <t>TC-SEC-22</t>
-  </si>
-  <si>
-    <t>TC-SEC-22: X-Frame-Options: DENY clickjacking headers verification check</t>
-  </si>
-  <si>
-    <t>Server returns X-Frame-Options: DENY or SAMEORIGIN header configurations</t>
-  </si>
-  <si>
-    <t>0.35s</t>
-  </si>
-  <si>
-    <t>TC-SEC-23</t>
-  </si>
-  <si>
-    <t>TC-SEC-23: Content-Security-Policy (CSP) headers verification check</t>
-  </si>
-  <si>
-    <t>CSP header blocks execution of external script elements</t>
-  </si>
-  <si>
-    <t>TC-SEC-24</t>
-  </si>
-  <si>
-    <t>TC-SEC-24: X-Content-Type-Options: nosniff headers check</t>
-  </si>
-  <si>
-    <t>Nosniff headers prevent browsers from executing script MIME type spoofing</t>
-  </si>
-  <si>
-    <t>0.46s</t>
-  </si>
-  <si>
-    <t>TC-SEC-25</t>
-  </si>
-  <si>
-    <t>TC-SEC-25: Strict-Transport-Security (HSTS) headers verification check</t>
-  </si>
-  <si>
-    <t>Server returns HSTS headers forcing browser redirects to HTTPS protocol</t>
-  </si>
-  <si>
-    <t>0.31s</t>
-  </si>
-  <si>
-    <t>TC-SEC-26</t>
-  </si>
-  <si>
-    <t>TC-SEC-26: API keys and client access rate limiting checking</t>
-  </si>
-  <si>
-    <t>API rate limit blocks traffic exceeding 100 requests per minute</t>
-  </si>
-  <si>
-    <t>TC-SEC-27</t>
-  </si>
-  <si>
-    <t>TC-SEC-27: Unauthenticated client requests blocks on private API endpoints</t>
-  </si>
-  <si>
-    <t>Requests without valid Authorization tokens fail with 401 Unauthorized</t>
-  </si>
-  <si>
-    <t>TC-SEC-28</t>
-  </si>
-  <si>
-    <t>TC-SEC-28: Authorization header Bearer token schema formatting validation</t>
-  </si>
-  <si>
-    <t>Improperly formatted Authorization header formats fail schema checks</t>
-  </si>
-  <si>
-    <t>0.43s</t>
-  </si>
-  <si>
-    <t>TC-SEC-29</t>
-  </si>
-  <si>
-    <t>TC-SEC-29: Access-Control-Allow-Origin wildcard denial for credentialed cross-origin requests</t>
-  </si>
-  <si>
-    <t>Server restricts CORS credentials access when wildcard is used</t>
-  </si>
-  <si>
     <t>TC-SEC-30</t>
   </si>
   <si>
@@ -424,7 +424,7 @@
     <t>Sensitive API endpoints restrict access to specific trusted domains and reject * wildcards</t>
   </si>
   <si>
-    <t>0.39s</t>
+    <t>0.38s</t>
   </si>
   <si>
     <t>Failure Message</t>
@@ -1106,21 +1106,21 @@
         <v>28</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>27</v>
@@ -1129,21 +1129,21 @@
         <v>28</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>27</v>
@@ -1152,21 +1152,21 @@
         <v>28</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>27</v>
@@ -1175,21 +1175,21 @@
         <v>28</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1198,21 +1198,21 @@
         <v>28</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>27</v>
@@ -1221,21 +1221,21 @@
         <v>28</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
@@ -1244,21 +1244,21 @@
         <v>28</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>27</v>
@@ -1267,21 +1267,21 @@
         <v>28</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>27</v>
@@ -1290,21 +1290,21 @@
         <v>28</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
@@ -1313,21 +1313,21 @@
         <v>28</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>27</v>
@@ -1336,21 +1336,21 @@
         <v>28</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>27</v>
@@ -1359,21 +1359,21 @@
         <v>28</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>81</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>27</v>
@@ -1382,21 +1382,21 @@
         <v>28</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>27</v>
@@ -1405,21 +1405,21 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1428,21 +1428,21 @@
         <v>28</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>27</v>
@@ -1451,21 +1451,21 @@
         <v>28</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>27</v>
@@ -1474,21 +1474,21 @@
         <v>28</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>27</v>
@@ -1497,21 +1497,21 @@
         <v>28</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
@@ -1520,7 +1520,7 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1543,7 +1543,7 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1566,53 +1566,53 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>115</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="E27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1635,7 +1635,7 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1658,30 +1658,30 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>129</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="E30" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G30" s="5" t="s">
         <v>132</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1870,7 +1870,7 @@
         <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>28</v>
@@ -1887,7 +1887,7 @@
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>28</v>
@@ -1904,7 +1904,7 @@
         <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
@@ -1921,7 +1921,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>28</v>
@@ -1938,7 +1938,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
@@ -1955,7 +1955,7 @@
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>28</v>
@@ -1972,7 +1972,7 @@
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
@@ -1989,7 +1989,7 @@
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
@@ -2006,7 +2006,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>28</v>
@@ -2023,7 +2023,7 @@
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
@@ -2040,7 +2040,7 @@
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>28</v>
@@ -2057,7 +2057,7 @@
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>28</v>
@@ -2074,7 +2074,7 @@
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>28</v>
@@ -2091,7 +2091,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
@@ -2108,7 +2108,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
@@ -2125,7 +2125,7 @@
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>28</v>
@@ -2142,7 +2142,7 @@
         <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>28</v>
@@ -2159,7 +2159,7 @@
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>28</v>
@@ -2210,7 +2210,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>28</v>
@@ -2227,7 +2227,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>28</v>
@@ -2278,7 +2278,7 @@
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>28</v>

--- a/reports/Security_Report.xlsx
+++ b/reports/Security_Report.xlsx
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/18/2026, 5:58:12 AM</t>
+    <t>6/16/2026, 7:30:58 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>8.52s</t>
+    <t>10.08s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,7 +103,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>0.12s</t>
+    <t>0.47s</t>
   </si>
   <si>
     <t>TC-SEC-02</t>
@@ -115,294 +115,297 @@
     <t>Search query drops comment blocks (--) to prevent database parsing errors</t>
   </si>
   <si>
+    <t>0.42s</t>
+  </si>
+  <si>
+    <t>TC-SEC-03</t>
+  </si>
+  <si>
+    <t>TC-SEC-03: Transaction Description parameter validator check against SELECT union query commands</t>
+  </si>
+  <si>
+    <t>SELECT UNION query patterns in transaction description are blocked</t>
+  </si>
+  <si>
+    <t>0.13s</t>
+  </si>
+  <si>
+    <t>TC-SEC-04</t>
+  </si>
+  <si>
+    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
+  </si>
+  <si>
+    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
+  </si>
+  <si>
+    <t>TC-SEC-05</t>
+  </si>
+  <si>
+    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
+  </si>
+  <si>
+    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
+  </si>
+  <si>
+    <t>0.14s</t>
+  </si>
+  <si>
+    <t>TC-SEC-06</t>
+  </si>
+  <si>
+    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
+  </si>
+  <si>
+    <t>Reflected query parameters from URL string are parsed and encoded</t>
+  </si>
+  <si>
+    <t>0.34s</t>
+  </si>
+  <si>
+    <t>TC-SEC-07</t>
+  </si>
+  <si>
+    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
+  </si>
+  <si>
+    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
+  </si>
+  <si>
+    <t>TC-SEC-08</t>
+  </si>
+  <si>
+    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
+  </si>
+  <si>
+    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
+  </si>
+  <si>
     <t>0.32s</t>
   </si>
   <si>
-    <t>TC-SEC-03</t>
-  </si>
-  <si>
-    <t>TC-SEC-03: Transaction Description parameter validator check against SELECT union query commands</t>
-  </si>
-  <si>
-    <t>SELECT UNION query patterns in transaction description are blocked</t>
-  </si>
-  <si>
-    <t>0.42s</t>
-  </si>
-  <si>
-    <t>TC-SEC-04</t>
-  </si>
-  <si>
-    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
-  </si>
-  <si>
-    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
-  </si>
-  <si>
-    <t>0.29s</t>
-  </si>
-  <si>
-    <t>TC-SEC-05</t>
-  </si>
-  <si>
-    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
-  </si>
-  <si>
-    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
-  </si>
-  <si>
-    <t>0.25s</t>
-  </si>
-  <si>
-    <t>TC-SEC-06</t>
-  </si>
-  <si>
-    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
-  </si>
-  <si>
-    <t>Reflected query parameters from URL string are parsed and encoded</t>
-  </si>
-  <si>
-    <t>0.28s</t>
-  </si>
-  <si>
-    <t>TC-SEC-07</t>
-  </si>
-  <si>
-    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
-  </si>
-  <si>
-    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
-  </si>
-  <si>
-    <t>0.19s</t>
-  </si>
-  <si>
-    <t>TC-SEC-08</t>
-  </si>
-  <si>
-    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
-  </si>
-  <si>
-    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
+    <t>TC-SEC-09</t>
+  </si>
+  <si>
+    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
+  </si>
+  <si>
+    <t>Forms submit payloads include active unique CSRF session hashes</t>
+  </si>
+  <si>
+    <t>0.36s</t>
+  </si>
+  <si>
+    <t>TC-SEC-10</t>
+  </si>
+  <si>
+    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
+  </si>
+  <si>
+    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
+  </si>
+  <si>
+    <t>0.22s</t>
+  </si>
+  <si>
+    <t>TC-SEC-11</t>
+  </si>
+  <si>
+    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
+  </si>
+  <si>
+    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
+  </si>
+  <si>
+    <t>0.20s</t>
+  </si>
+  <si>
+    <t>TC-SEC-12</t>
+  </si>
+  <si>
+    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
+  </si>
+  <si>
+    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-13</t>
+  </si>
+  <si>
+    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
+  </si>
+  <si>
+    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
+  </si>
+  <si>
+    <t>TC-SEC-14</t>
+  </si>
+  <si>
+    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
+  </si>
+  <si>
+    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
+  </si>
+  <si>
+    <t>0.41s</t>
+  </si>
+  <si>
+    <t>TC-SEC-15</t>
+  </si>
+  <si>
+    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
+  </si>
+  <si>
+    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
+  </si>
+  <si>
+    <t>0.48s</t>
+  </si>
+  <si>
+    <t>TC-SEC-16</t>
+  </si>
+  <si>
+    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
+  </si>
+  <si>
+    <t>Inactivity over 15 minutes invalidates session token automatically</t>
   </si>
   <si>
     <t>0.45s</t>
   </si>
   <si>
-    <t>TC-SEC-09</t>
-  </si>
-  <si>
-    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
-  </si>
-  <si>
-    <t>Forms submit payloads include active unique CSRF session hashes</t>
-  </si>
-  <si>
-    <t>0.18s</t>
-  </si>
-  <si>
-    <t>TC-SEC-10</t>
-  </si>
-  <si>
-    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
-  </si>
-  <si>
-    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
-  </si>
-  <si>
-    <t>TC-SEC-11</t>
-  </si>
-  <si>
-    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
-  </si>
-  <si>
-    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
+    <t>TC-SEC-17</t>
+  </si>
+  <si>
+    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
+  </si>
+  <si>
+    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
+  </si>
+  <si>
+    <t>TC-SEC-18</t>
+  </si>
+  <si>
+    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
+  </si>
+  <si>
+    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
+  </si>
+  <si>
+    <t>0.15s</t>
+  </si>
+  <si>
+    <t>TC-SEC-19</t>
+  </si>
+  <si>
+    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
+  </si>
+  <si>
+    <t>Incorrect email formatting does not match registration criteria</t>
+  </si>
+  <si>
+    <t>0.37s</t>
+  </si>
+  <si>
+    <t>TC-SEC-20</t>
+  </si>
+  <si>
+    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
+  </si>
+  <si>
+    <t>Transaction form validates amount bounds and rejects negative entries</t>
   </si>
   <si>
     <t>0.27s</t>
   </si>
   <si>
-    <t>TC-SEC-12</t>
-  </si>
-  <si>
-    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
-  </si>
-  <si>
-    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
-  </si>
-  <si>
-    <t>0.13s</t>
-  </si>
-  <si>
-    <t>TC-SEC-13</t>
-  </si>
-  <si>
-    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
-  </si>
-  <si>
-    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
-  </si>
-  <si>
-    <t>0.16s</t>
-  </si>
-  <si>
-    <t>TC-SEC-14</t>
-  </si>
-  <si>
-    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
-  </si>
-  <si>
-    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
-  </si>
-  <si>
-    <t>TC-SEC-15</t>
-  </si>
-  <si>
-    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
-  </si>
-  <si>
-    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
-  </si>
-  <si>
-    <t>TC-SEC-16</t>
-  </si>
-  <si>
-    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
-  </si>
-  <si>
-    <t>Inactivity over 15 minutes invalidates session token automatically</t>
-  </si>
-  <si>
-    <t>0.40s</t>
-  </si>
-  <si>
-    <t>TC-SEC-17</t>
-  </si>
-  <si>
-    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
-  </si>
-  <si>
-    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
-  </si>
-  <si>
-    <t>0.26s</t>
-  </si>
-  <si>
-    <t>TC-SEC-18</t>
-  </si>
-  <si>
-    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
-  </si>
-  <si>
-    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
-  </si>
-  <si>
-    <t>TC-SEC-19</t>
-  </si>
-  <si>
-    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
-  </si>
-  <si>
-    <t>Incorrect email formatting does not match registration criteria</t>
-  </si>
-  <si>
-    <t>0.17s</t>
-  </si>
-  <si>
-    <t>TC-SEC-20</t>
-  </si>
-  <si>
-    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
-  </si>
-  <si>
-    <t>Transaction form validates amount bounds and rejects negative entries</t>
+    <t>TC-SEC-21</t>
+  </si>
+  <si>
+    <t>TC-SEC-21: Transaction Date limits and bounds range checks validation</t>
+  </si>
+  <si>
+    <t>Dates set beyond maximum future bounds are rejected</t>
+  </si>
+  <si>
+    <t>0.44s</t>
+  </si>
+  <si>
+    <t>TC-SEC-22</t>
+  </si>
+  <si>
+    <t>TC-SEC-22: X-Frame-Options: DENY clickjacking headers verification check</t>
+  </si>
+  <si>
+    <t>Server returns X-Frame-Options: DENY or SAMEORIGIN header configurations</t>
   </si>
   <si>
     <t>0.35s</t>
   </si>
   <si>
-    <t>TC-SEC-21</t>
-  </si>
-  <si>
-    <t>TC-SEC-21: Transaction Date limits and bounds range checks validation</t>
-  </si>
-  <si>
-    <t>Dates set beyond maximum future bounds are rejected</t>
+    <t>TC-SEC-23</t>
+  </si>
+  <si>
+    <t>TC-SEC-23: Content-Security-Policy (CSP) headers verification check</t>
+  </si>
+  <si>
+    <t>CSP header blocks execution of external script elements</t>
+  </si>
+  <si>
+    <t>TC-SEC-24</t>
+  </si>
+  <si>
+    <t>TC-SEC-24: X-Content-Type-Options: nosniff headers check</t>
+  </si>
+  <si>
+    <t>Nosniff headers prevent browsers from executing script MIME type spoofing</t>
+  </si>
+  <si>
+    <t>0.46s</t>
+  </si>
+  <si>
+    <t>TC-SEC-25</t>
+  </si>
+  <si>
+    <t>TC-SEC-25: Strict-Transport-Security (HSTS) headers verification check</t>
+  </si>
+  <si>
+    <t>Server returns HSTS headers forcing browser redirects to HTTPS protocol</t>
+  </si>
+  <si>
+    <t>0.31s</t>
+  </si>
+  <si>
+    <t>TC-SEC-26</t>
+  </si>
+  <si>
+    <t>TC-SEC-26: API keys and client access rate limiting checking</t>
+  </si>
+  <si>
+    <t>API rate limit blocks traffic exceeding 100 requests per minute</t>
+  </si>
+  <si>
+    <t>TC-SEC-27</t>
+  </si>
+  <si>
+    <t>TC-SEC-27: Unauthenticated client requests blocks on private API endpoints</t>
+  </si>
+  <si>
+    <t>Requests without valid Authorization tokens fail with 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>TC-SEC-28</t>
+  </si>
+  <si>
+    <t>TC-SEC-28: Authorization header Bearer token schema formatting validation</t>
+  </si>
+  <si>
+    <t>Improperly formatted Authorization header formats fail schema checks</t>
   </si>
   <si>
     <t>0.43s</t>
   </si>
   <si>
-    <t>TC-SEC-22</t>
-  </si>
-  <si>
-    <t>TC-SEC-22: X-Frame-Options: DENY clickjacking headers verification check</t>
-  </si>
-  <si>
-    <t>Server returns X-Frame-Options: DENY or SAMEORIGIN header configurations</t>
-  </si>
-  <si>
-    <t>TC-SEC-23</t>
-  </si>
-  <si>
-    <t>TC-SEC-23: Content-Security-Policy (CSP) headers verification check</t>
-  </si>
-  <si>
-    <t>CSP header blocks execution of external script elements</t>
-  </si>
-  <si>
-    <t>TC-SEC-24</t>
-  </si>
-  <si>
-    <t>TC-SEC-24: X-Content-Type-Options: nosniff headers check</t>
-  </si>
-  <si>
-    <t>Nosniff headers prevent browsers from executing script MIME type spoofing</t>
-  </si>
-  <si>
-    <t>TC-SEC-25</t>
-  </si>
-  <si>
-    <t>TC-SEC-25: Strict-Transport-Security (HSTS) headers verification check</t>
-  </si>
-  <si>
-    <t>Server returns HSTS headers forcing browser redirects to HTTPS protocol</t>
-  </si>
-  <si>
-    <t>0.30s</t>
-  </si>
-  <si>
-    <t>TC-SEC-26</t>
-  </si>
-  <si>
-    <t>TC-SEC-26: API keys and client access rate limiting checking</t>
-  </si>
-  <si>
-    <t>API rate limit blocks traffic exceeding 100 requests per minute</t>
-  </si>
-  <si>
-    <t>0.22s</t>
-  </si>
-  <si>
-    <t>TC-SEC-27</t>
-  </si>
-  <si>
-    <t>TC-SEC-27: Unauthenticated client requests blocks on private API endpoints</t>
-  </si>
-  <si>
-    <t>Requests without valid Authorization tokens fail with 401 Unauthorized</t>
-  </si>
-  <si>
-    <t>TC-SEC-28</t>
-  </si>
-  <si>
-    <t>TC-SEC-28: Authorization header Bearer token schema formatting validation</t>
-  </si>
-  <si>
-    <t>Improperly formatted Authorization header formats fail schema checks</t>
-  </si>
-  <si>
     <t>TC-SEC-29</t>
   </si>
   <si>
@@ -412,9 +415,6 @@
     <t>Server restricts CORS credentials access when wildcard is used</t>
   </si>
   <si>
-    <t>0.14s</t>
-  </si>
-  <si>
     <t>TC-SEC-30</t>
   </si>
   <si>
@@ -424,7 +424,7 @@
     <t>Sensitive API endpoints restrict access to specific trusted domains and reject * wildcards</t>
   </si>
   <si>
-    <t>0.38s</t>
+    <t>0.39s</t>
   </si>
   <si>
     <t>Failure Message</t>
@@ -1106,68 +1106,68 @@
         <v>28</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="E8" s="3" t="s">
         <v>27</v>
       </c>
@@ -1175,114 +1175,114 @@
         <v>28</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="E10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="E11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="E13" s="3" t="s">
         <v>27</v>
       </c>
@@ -1290,22 +1290,22 @@
         <v>28</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
       </c>
@@ -1313,91 +1313,91 @@
         <v>28</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="E18" s="3" t="s">
         <v>27</v>
       </c>
@@ -1405,122 +1405,122 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="E19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1543,7 +1543,7 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1566,21 +1566,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>53</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1589,21 +1589,21 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>27</v>
@@ -1612,7 +1612,7 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1635,7 +1635,7 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1658,21 +1658,21 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>57</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>27</v>
@@ -1681,7 +1681,7 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>132</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1870,7 +1870,7 @@
         <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>28</v>
@@ -1887,7 +1887,7 @@
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>28</v>
@@ -1904,7 +1904,7 @@
         <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
@@ -1921,7 +1921,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>28</v>
@@ -1938,7 +1938,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
@@ -1955,7 +1955,7 @@
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>28</v>
@@ -1972,7 +1972,7 @@
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
@@ -1989,7 +1989,7 @@
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
@@ -2006,7 +2006,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>28</v>
@@ -2023,7 +2023,7 @@
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
@@ -2040,7 +2040,7 @@
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>28</v>
@@ -2057,7 +2057,7 @@
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>28</v>
@@ -2074,7 +2074,7 @@
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>28</v>
@@ -2091,7 +2091,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
@@ -2108,7 +2108,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
@@ -2125,7 +2125,7 @@
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>28</v>
@@ -2142,7 +2142,7 @@
         <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>28</v>
@@ -2159,7 +2159,7 @@
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>28</v>
@@ -2210,7 +2210,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>28</v>
@@ -2227,7 +2227,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>28</v>
@@ -2278,7 +2278,7 @@
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>28</v>

--- a/reports/Security_Report.xlsx
+++ b/reports/Security_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="141">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/16/2026, 7:30:58 AM</t>
+    <t>6/18/2026, 6:11:35 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>10.08s</t>
+    <t>8.43s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,7 +103,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>0.47s</t>
+    <t>0.15s</t>
   </si>
   <si>
     <t>TC-SEC-02</t>
@@ -115,7 +115,7 @@
     <t>Search query drops comment blocks (--) to prevent database parsing errors</t>
   </si>
   <si>
-    <t>0.42s</t>
+    <t>0.32s</t>
   </si>
   <si>
     <t>TC-SEC-03</t>
@@ -127,198 +127,198 @@
     <t>SELECT UNION query patterns in transaction description are blocked</t>
   </si>
   <si>
+    <t>0.48s</t>
+  </si>
+  <si>
+    <t>TC-SEC-04</t>
+  </si>
+  <si>
+    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
+  </si>
+  <si>
+    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
+  </si>
+  <si>
+    <t>0.21s</t>
+  </si>
+  <si>
+    <t>TC-SEC-05</t>
+  </si>
+  <si>
+    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
+  </si>
+  <si>
+    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
+  </si>
+  <si>
+    <t>0.24s</t>
+  </si>
+  <si>
+    <t>TC-SEC-06</t>
+  </si>
+  <si>
+    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
+  </si>
+  <si>
+    <t>Reflected query parameters from URL string are parsed and encoded</t>
+  </si>
+  <si>
+    <t>0.19s</t>
+  </si>
+  <si>
+    <t>TC-SEC-07</t>
+  </si>
+  <si>
+    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
+  </si>
+  <si>
+    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
+  </si>
+  <si>
+    <t>0.45s</t>
+  </si>
+  <si>
+    <t>TC-SEC-08</t>
+  </si>
+  <si>
+    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
+  </si>
+  <si>
+    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
+  </si>
+  <si>
+    <t>0.36s</t>
+  </si>
+  <si>
+    <t>TC-SEC-09</t>
+  </si>
+  <si>
+    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
+  </si>
+  <si>
+    <t>Forms submit payloads include active unique CSRF session hashes</t>
+  </si>
+  <si>
+    <t>0.14s</t>
+  </si>
+  <si>
+    <t>TC-SEC-10</t>
+  </si>
+  <si>
+    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
+  </si>
+  <si>
+    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
+  </si>
+  <si>
+    <t>TC-SEC-11</t>
+  </si>
+  <si>
+    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
+  </si>
+  <si>
+    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
+  </si>
+  <si>
+    <t>0.27s</t>
+  </si>
+  <si>
+    <t>TC-SEC-12</t>
+  </si>
+  <si>
+    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
+  </si>
+  <si>
+    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
+  </si>
+  <si>
+    <t>0.44s</t>
+  </si>
+  <si>
+    <t>TC-SEC-13</t>
+  </si>
+  <si>
+    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
+  </si>
+  <si>
+    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
+  </si>
+  <si>
+    <t>TC-SEC-14</t>
+  </si>
+  <si>
+    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
+  </si>
+  <si>
+    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
+  </si>
+  <si>
+    <t>0.23s</t>
+  </si>
+  <si>
+    <t>TC-SEC-15</t>
+  </si>
+  <si>
+    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
+  </si>
+  <si>
+    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
+  </si>
+  <si>
+    <t>0.43s</t>
+  </si>
+  <si>
+    <t>TC-SEC-16</t>
+  </si>
+  <si>
+    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
+  </si>
+  <si>
+    <t>Inactivity over 15 minutes invalidates session token automatically</t>
+  </si>
+  <si>
+    <t>0.20s</t>
+  </si>
+  <si>
+    <t>TC-SEC-17</t>
+  </si>
+  <si>
+    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
+  </si>
+  <si>
+    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
+  </si>
+  <si>
+    <t>TC-SEC-18</t>
+  </si>
+  <si>
+    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
+  </si>
+  <si>
+    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
+  </si>
+  <si>
+    <t>TC-SEC-19</t>
+  </si>
+  <si>
+    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
+  </si>
+  <si>
+    <t>Incorrect email formatting does not match registration criteria</t>
+  </si>
+  <si>
+    <t>TC-SEC-20</t>
+  </si>
+  <si>
+    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
+  </si>
+  <si>
+    <t>Transaction form validates amount bounds and rejects negative entries</t>
+  </si>
+  <si>
     <t>0.13s</t>
   </si>
   <si>
-    <t>TC-SEC-04</t>
-  </si>
-  <si>
-    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
-  </si>
-  <si>
-    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
-  </si>
-  <si>
-    <t>TC-SEC-05</t>
-  </si>
-  <si>
-    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
-  </si>
-  <si>
-    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
-  </si>
-  <si>
-    <t>0.14s</t>
-  </si>
-  <si>
-    <t>TC-SEC-06</t>
-  </si>
-  <si>
-    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
-  </si>
-  <si>
-    <t>Reflected query parameters from URL string are parsed and encoded</t>
-  </si>
-  <si>
-    <t>0.34s</t>
-  </si>
-  <si>
-    <t>TC-SEC-07</t>
-  </si>
-  <si>
-    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
-  </si>
-  <si>
-    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
-  </si>
-  <si>
-    <t>TC-SEC-08</t>
-  </si>
-  <si>
-    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
-  </si>
-  <si>
-    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
-  </si>
-  <si>
-    <t>0.32s</t>
-  </si>
-  <si>
-    <t>TC-SEC-09</t>
-  </si>
-  <si>
-    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
-  </si>
-  <si>
-    <t>Forms submit payloads include active unique CSRF session hashes</t>
-  </si>
-  <si>
-    <t>0.36s</t>
-  </si>
-  <si>
-    <t>TC-SEC-10</t>
-  </si>
-  <si>
-    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
-  </si>
-  <si>
-    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
-  </si>
-  <si>
-    <t>0.22s</t>
-  </si>
-  <si>
-    <t>TC-SEC-11</t>
-  </si>
-  <si>
-    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
-  </si>
-  <si>
-    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
-  </si>
-  <si>
-    <t>0.20s</t>
-  </si>
-  <si>
-    <t>TC-SEC-12</t>
-  </si>
-  <si>
-    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
-  </si>
-  <si>
-    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-13</t>
-  </si>
-  <si>
-    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
-  </si>
-  <si>
-    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
-  </si>
-  <si>
-    <t>TC-SEC-14</t>
-  </si>
-  <si>
-    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
-  </si>
-  <si>
-    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
-  </si>
-  <si>
-    <t>0.41s</t>
-  </si>
-  <si>
-    <t>TC-SEC-15</t>
-  </si>
-  <si>
-    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
-  </si>
-  <si>
-    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
-  </si>
-  <si>
-    <t>0.48s</t>
-  </si>
-  <si>
-    <t>TC-SEC-16</t>
-  </si>
-  <si>
-    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
-  </si>
-  <si>
-    <t>Inactivity over 15 minutes invalidates session token automatically</t>
-  </si>
-  <si>
-    <t>0.45s</t>
-  </si>
-  <si>
-    <t>TC-SEC-17</t>
-  </si>
-  <si>
-    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
-  </si>
-  <si>
-    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
-  </si>
-  <si>
-    <t>TC-SEC-18</t>
-  </si>
-  <si>
-    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
-  </si>
-  <si>
-    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
-  </si>
-  <si>
-    <t>0.15s</t>
-  </si>
-  <si>
-    <t>TC-SEC-19</t>
-  </si>
-  <si>
-    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
-  </si>
-  <si>
-    <t>Incorrect email formatting does not match registration criteria</t>
-  </si>
-  <si>
-    <t>0.37s</t>
-  </si>
-  <si>
-    <t>TC-SEC-20</t>
-  </si>
-  <si>
-    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
-  </si>
-  <si>
-    <t>Transaction form validates amount bounds and rejects negative entries</t>
-  </si>
-  <si>
-    <t>0.27s</t>
-  </si>
-  <si>
     <t>TC-SEC-21</t>
   </si>
   <si>
@@ -328,9 +328,6 @@
     <t>Dates set beyond maximum future bounds are rejected</t>
   </si>
   <si>
-    <t>0.44s</t>
-  </si>
-  <si>
     <t>TC-SEC-22</t>
   </si>
   <si>
@@ -340,9 +337,6 @@
     <t>Server returns X-Frame-Options: DENY or SAMEORIGIN header configurations</t>
   </si>
   <si>
-    <t>0.35s</t>
-  </si>
-  <si>
     <t>TC-SEC-23</t>
   </si>
   <si>
@@ -361,21 +355,21 @@
     <t>Nosniff headers prevent browsers from executing script MIME type spoofing</t>
   </si>
   <si>
+    <t>0.28s</t>
+  </si>
+  <si>
+    <t>TC-SEC-25</t>
+  </si>
+  <si>
+    <t>TC-SEC-25: Strict-Transport-Security (HSTS) headers verification check</t>
+  </si>
+  <si>
+    <t>Server returns HSTS headers forcing browser redirects to HTTPS protocol</t>
+  </si>
+  <si>
     <t>0.46s</t>
   </si>
   <si>
-    <t>TC-SEC-25</t>
-  </si>
-  <si>
-    <t>TC-SEC-25: Strict-Transport-Security (HSTS) headers verification check</t>
-  </si>
-  <si>
-    <t>Server returns HSTS headers forcing browser redirects to HTTPS protocol</t>
-  </si>
-  <si>
-    <t>0.31s</t>
-  </si>
-  <si>
     <t>TC-SEC-26</t>
   </si>
   <si>
@@ -403,9 +397,6 @@
     <t>Improperly formatted Authorization header formats fail schema checks</t>
   </si>
   <si>
-    <t>0.43s</t>
-  </si>
-  <si>
     <t>TC-SEC-29</t>
   </si>
   <si>
@@ -422,9 +413,6 @@
   </si>
   <si>
     <t>Sensitive API endpoints restrict access to specific trusted domains and reject * wildcards</t>
-  </si>
-  <si>
-    <t>0.39s</t>
   </si>
   <si>
     <t>Failure Message</t>
@@ -1106,21 +1094,21 @@
         <v>28</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>27</v>
@@ -1129,21 +1117,21 @@
         <v>28</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>27</v>
@@ -1152,21 +1140,21 @@
         <v>28</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>27</v>
@@ -1175,21 +1163,21 @@
         <v>28</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1198,21 +1186,21 @@
         <v>28</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>27</v>
@@ -1221,21 +1209,21 @@
         <v>28</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
@@ -1244,21 +1232,21 @@
         <v>28</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>27</v>
@@ -1267,21 +1255,21 @@
         <v>28</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>27</v>
@@ -1290,21 +1278,21 @@
         <v>28</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
@@ -1313,21 +1301,21 @@
         <v>28</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>27</v>
@@ -1336,21 +1324,21 @@
         <v>28</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>27</v>
@@ -1359,21 +1347,21 @@
         <v>28</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>27</v>
@@ -1382,21 +1370,21 @@
         <v>28</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>27</v>
@@ -1405,21 +1393,21 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1428,21 +1416,21 @@
         <v>28</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>27</v>
@@ -1451,7 +1439,7 @@
         <v>28</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1497,22 +1485,22 @@
         <v>28</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>104</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
       </c>
@@ -1520,22 +1508,22 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="E24" s="3" t="s">
         <v>27</v>
       </c>
@@ -1543,68 +1531,68 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="3" t="s">
+      <c r="E25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="3" t="s">
+      <c r="E26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="E27" s="3" t="s">
         <v>27</v>
       </c>
@@ -1612,22 +1600,22 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>96</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
       </c>
@@ -1635,22 +1623,22 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="E29" s="3" t="s">
         <v>27</v>
       </c>
@@ -1658,21 +1646,21 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>27</v>
@@ -1681,21 +1669,21 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>27</v>
@@ -1704,7 +1692,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1736,10 +1724,10 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1750,10 +1738,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
@@ -1779,19 +1767,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1870,7 +1858,7 @@
         <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>28</v>
@@ -1887,7 +1875,7 @@
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>28</v>
@@ -1904,7 +1892,7 @@
         <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
@@ -1921,7 +1909,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>28</v>
@@ -1938,7 +1926,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
@@ -1955,7 +1943,7 @@
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>28</v>
@@ -1972,7 +1960,7 @@
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
@@ -1989,7 +1977,7 @@
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
@@ -2006,7 +1994,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>28</v>
@@ -2023,7 +2011,7 @@
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
@@ -2040,7 +2028,7 @@
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>28</v>
@@ -2057,7 +2045,7 @@
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>28</v>
@@ -2074,7 +2062,7 @@
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>28</v>
@@ -2091,7 +2079,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
@@ -2108,7 +2096,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
@@ -2159,7 +2147,7 @@
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>28</v>
@@ -2176,7 +2164,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>28</v>
@@ -2193,7 +2181,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>28</v>
@@ -2210,7 +2198,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>28</v>
@@ -2227,7 +2215,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>28</v>
@@ -2244,7 +2232,7 @@
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>28</v>
@@ -2261,7 +2249,7 @@
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>
@@ -2278,7 +2266,7 @@
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>28</v>
@@ -2295,7 +2283,7 @@
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>28</v>

--- a/reports/Security_Report.xlsx
+++ b/reports/Security_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="145">
   <si>
     <t>Metric</t>
   </si>
@@ -25,7 +25,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/18/2026, 6:11:35 AM</t>
+    <t>6/16/2026, 7:30:58 AM</t>
   </si>
   <si>
     <t>Device Name</t>
@@ -61,7 +61,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>8.43s</t>
+    <t>10.08s</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -103,300 +103,309 @@
     <t>PASS</t>
   </si>
   <si>
+    <t>0.47s</t>
+  </si>
+  <si>
+    <t>TC-SEC-02</t>
+  </si>
+  <si>
+    <t>TC-SEC-02: Dashboard search box query sanitization check against inline comment characters</t>
+  </si>
+  <si>
+    <t>Search query drops comment blocks (--) to prevent database parsing errors</t>
+  </si>
+  <si>
+    <t>0.42s</t>
+  </si>
+  <si>
+    <t>TC-SEC-03</t>
+  </si>
+  <si>
+    <t>TC-SEC-03: Transaction Description parameter validator check against SELECT union query commands</t>
+  </si>
+  <si>
+    <t>SELECT UNION query patterns in transaction description are blocked</t>
+  </si>
+  <si>
+    <t>0.13s</t>
+  </si>
+  <si>
+    <t>TC-SEC-04</t>
+  </si>
+  <si>
+    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
+  </si>
+  <si>
+    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
+  </si>
+  <si>
+    <t>TC-SEC-05</t>
+  </si>
+  <si>
+    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
+  </si>
+  <si>
+    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
+  </si>
+  <si>
+    <t>0.14s</t>
+  </si>
+  <si>
+    <t>TC-SEC-06</t>
+  </si>
+  <si>
+    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
+  </si>
+  <si>
+    <t>Reflected query parameters from URL string are parsed and encoded</t>
+  </si>
+  <si>
+    <t>0.34s</t>
+  </si>
+  <si>
+    <t>TC-SEC-07</t>
+  </si>
+  <si>
+    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
+  </si>
+  <si>
+    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
+  </si>
+  <si>
+    <t>TC-SEC-08</t>
+  </si>
+  <si>
+    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
+  </si>
+  <si>
+    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
+  </si>
+  <si>
+    <t>0.32s</t>
+  </si>
+  <si>
+    <t>TC-SEC-09</t>
+  </si>
+  <si>
+    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
+  </si>
+  <si>
+    <t>Forms submit payloads include active unique CSRF session hashes</t>
+  </si>
+  <si>
+    <t>0.36s</t>
+  </si>
+  <si>
+    <t>TC-SEC-10</t>
+  </si>
+  <si>
+    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
+  </si>
+  <si>
+    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
+  </si>
+  <si>
+    <t>0.22s</t>
+  </si>
+  <si>
+    <t>TC-SEC-11</t>
+  </si>
+  <si>
+    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
+  </si>
+  <si>
+    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
+  </si>
+  <si>
+    <t>0.20s</t>
+  </si>
+  <si>
+    <t>TC-SEC-12</t>
+  </si>
+  <si>
+    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
+  </si>
+  <si>
+    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-13</t>
+  </si>
+  <si>
+    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
+  </si>
+  <si>
+    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
+  </si>
+  <si>
+    <t>TC-SEC-14</t>
+  </si>
+  <si>
+    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
+  </si>
+  <si>
+    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
+  </si>
+  <si>
+    <t>0.41s</t>
+  </si>
+  <si>
+    <t>TC-SEC-15</t>
+  </si>
+  <si>
+    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
+  </si>
+  <si>
+    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
+  </si>
+  <si>
+    <t>0.48s</t>
+  </si>
+  <si>
+    <t>TC-SEC-16</t>
+  </si>
+  <si>
+    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
+  </si>
+  <si>
+    <t>Inactivity over 15 minutes invalidates session token automatically</t>
+  </si>
+  <si>
+    <t>0.45s</t>
+  </si>
+  <si>
+    <t>TC-SEC-17</t>
+  </si>
+  <si>
+    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
+  </si>
+  <si>
+    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
+  </si>
+  <si>
+    <t>TC-SEC-18</t>
+  </si>
+  <si>
+    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
+  </si>
+  <si>
+    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
+  </si>
+  <si>
     <t>0.15s</t>
   </si>
   <si>
-    <t>TC-SEC-02</t>
-  </si>
-  <si>
-    <t>TC-SEC-02: Dashboard search box query sanitization check against inline comment characters</t>
-  </si>
-  <si>
-    <t>Search query drops comment blocks (--) to prevent database parsing errors</t>
-  </si>
-  <si>
-    <t>0.32s</t>
-  </si>
-  <si>
-    <t>TC-SEC-03</t>
-  </si>
-  <si>
-    <t>TC-SEC-03: Transaction Description parameter validator check against SELECT union query commands</t>
-  </si>
-  <si>
-    <t>SELECT UNION query patterns in transaction description are blocked</t>
-  </si>
-  <si>
-    <t>0.48s</t>
-  </si>
-  <si>
-    <t>TC-SEC-04</t>
-  </si>
-  <si>
-    <t>TC-SEC-04: API endpoint parameter check against malicious UPDATE database commands</t>
-  </si>
-  <si>
-    <t>Transaction update parameters are isolated and cannot modify tables structure</t>
-  </si>
-  <si>
-    <t>0.21s</t>
-  </si>
-  <si>
-    <t>TC-SEC-05</t>
-  </si>
-  <si>
-    <t>TC-SEC-05: Stored XSS check on Transaction Description inputs HTML characters escaping</t>
-  </si>
-  <si>
-    <t>HTML elements are escaped and render as literal text, not HTML nodes</t>
-  </si>
-  <si>
-    <t>0.24s</t>
-  </si>
-  <si>
-    <t>TC-SEC-06</t>
-  </si>
-  <si>
-    <t>TC-SEC-06: Reflective XSS check on URL query variables parameters parsing</t>
-  </si>
-  <si>
-    <t>Reflected query parameters from URL string are parsed and encoded</t>
-  </si>
-  <si>
-    <t>0.19s</t>
-  </si>
-  <si>
-    <t>TC-SEC-07</t>
-  </si>
-  <si>
-    <t>TC-SEC-07: File Upload XSS checks on Profile Avatar filename string characters</t>
-  </si>
-  <si>
-    <t>Avatar filename strings remove non-alphanumeric tag characters</t>
-  </si>
-  <si>
-    <t>0.45s</t>
-  </si>
-  <si>
-    <t>TC-SEC-08</t>
-  </si>
-  <si>
-    <t>TC-SEC-08: Stored XSS check on Profile Display Name text input field</t>
-  </si>
-  <si>
-    <t>Display Name input encodes brackets to prevent arbitrary script injections</t>
-  </si>
-  <si>
-    <t>0.36s</t>
-  </si>
-  <si>
-    <t>TC-SEC-09</t>
-  </si>
-  <si>
-    <t>TC-SEC-09: Verify presence of Anti-CSRF verification tokens inside sensitive form nodes</t>
-  </si>
-  <si>
-    <t>Forms submit payloads include active unique CSRF session hashes</t>
-  </si>
-  <si>
-    <t>0.14s</t>
-  </si>
-  <si>
-    <t>TC-SEC-10</t>
-  </si>
-  <si>
-    <t>TC-SEC-10: Verify Anti-CSRF verification tokens on Transaction logging POST requests</t>
-  </si>
-  <si>
-    <t>POST requests without valid CSRF security tokens return 403 Forbidden status</t>
-  </si>
-  <si>
-    <t>TC-SEC-11</t>
-  </si>
-  <si>
-    <t>TC-SEC-11: Verify SameSite attributes configuration parameters on session authentication cookies</t>
-  </si>
-  <si>
-    <t>Cookies have SameSite=Lax or SameSite=Strict to defend against CSRF</t>
+    <t>TC-SEC-19</t>
+  </si>
+  <si>
+    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
+  </si>
+  <si>
+    <t>Incorrect email formatting does not match registration criteria</t>
+  </si>
+  <si>
+    <t>0.37s</t>
+  </si>
+  <si>
+    <t>TC-SEC-20</t>
+  </si>
+  <si>
+    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
+  </si>
+  <si>
+    <t>Transaction form validates amount bounds and rejects negative entries</t>
   </si>
   <si>
     <t>0.27s</t>
   </si>
   <si>
-    <t>TC-SEC-12</t>
-  </si>
-  <si>
-    <t>TC-SEC-12: JWT signature key validity validation constraint checks</t>
-  </si>
-  <si>
-    <t>JWT tokens with altered payload contents return invalid signature key errors</t>
+    <t>TC-SEC-21</t>
+  </si>
+  <si>
+    <t>TC-SEC-21: Transaction Date limits and bounds range checks validation</t>
+  </si>
+  <si>
+    <t>Dates set beyond maximum future bounds are rejected</t>
   </si>
   <si>
     <t>0.44s</t>
   </si>
   <si>
-    <t>TC-SEC-13</t>
-  </si>
-  <si>
-    <t>TC-SEC-13: JWT Expiry token claim verification check</t>
-  </si>
-  <si>
-    <t>Expired JWT tokens are rejected and client redirects to sign-in</t>
-  </si>
-  <si>
-    <t>TC-SEC-14</t>
-  </si>
-  <si>
-    <t>TC-SEC-14: JWT Algorithm validation (rejecting "none" algorithm) constraints</t>
-  </si>
-  <si>
-    <t>JWT authorization rejects Alg: "none" configurations to prevent signature bypass</t>
-  </si>
-  <si>
-    <t>0.23s</t>
-  </si>
-  <si>
-    <t>TC-SEC-15</t>
-  </si>
-  <si>
-    <t>TC-SEC-15: Session Token token blocklist revocation validation check on Logout</t>
-  </si>
-  <si>
-    <t>Logged-out session tokens are added to revocation blocklist and rendered inactive</t>
+    <t>TC-SEC-22</t>
+  </si>
+  <si>
+    <t>TC-SEC-22: X-Frame-Options: DENY clickjacking headers verification check</t>
+  </si>
+  <si>
+    <t>Server returns X-Frame-Options: DENY or SAMEORIGIN header configurations</t>
+  </si>
+  <si>
+    <t>0.35s</t>
+  </si>
+  <si>
+    <t>TC-SEC-23</t>
+  </si>
+  <si>
+    <t>TC-SEC-23: Content-Security-Policy (CSP) headers verification check</t>
+  </si>
+  <si>
+    <t>CSP header blocks execution of external script elements</t>
+  </si>
+  <si>
+    <t>TC-SEC-24</t>
+  </si>
+  <si>
+    <t>TC-SEC-24: X-Content-Type-Options: nosniff headers check</t>
+  </si>
+  <si>
+    <t>Nosniff headers prevent browsers from executing script MIME type spoofing</t>
+  </si>
+  <si>
+    <t>0.46s</t>
+  </si>
+  <si>
+    <t>TC-SEC-25</t>
+  </si>
+  <si>
+    <t>TC-SEC-25: Strict-Transport-Security (HSTS) headers verification check</t>
+  </si>
+  <si>
+    <t>Server returns HSTS headers forcing browser redirects to HTTPS protocol</t>
+  </si>
+  <si>
+    <t>0.31s</t>
+  </si>
+  <si>
+    <t>TC-SEC-26</t>
+  </si>
+  <si>
+    <t>TC-SEC-26: API keys and client access rate limiting checking</t>
+  </si>
+  <si>
+    <t>API rate limit blocks traffic exceeding 100 requests per minute</t>
+  </si>
+  <si>
+    <t>TC-SEC-27</t>
+  </si>
+  <si>
+    <t>TC-SEC-27: Unauthenticated client requests blocks on private API endpoints</t>
+  </si>
+  <si>
+    <t>Requests without valid Authorization tokens fail with 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>TC-SEC-28</t>
+  </si>
+  <si>
+    <t>TC-SEC-28: Authorization header Bearer token schema formatting validation</t>
+  </si>
+  <si>
+    <t>Improperly formatted Authorization header formats fail schema checks</t>
   </si>
   <si>
     <t>0.43s</t>
   </si>
   <si>
-    <t>TC-SEC-16</t>
-  </si>
-  <si>
-    <t>TC-SEC-16: Inactive Session Timeout expiration limits checks</t>
-  </si>
-  <si>
-    <t>Inactivity over 15 minutes invalidates session token automatically</t>
-  </si>
-  <si>
-    <t>0.20s</t>
-  </si>
-  <si>
-    <t>TC-SEC-17</t>
-  </si>
-  <si>
-    <t>TC-SEC-17: Concurrent User Sessions limits bounds checks</t>
-  </si>
-  <si>
-    <t>User accounts exceed sessions limit block subsequent connections attempts</t>
-  </si>
-  <si>
-    <t>TC-SEC-18</t>
-  </si>
-  <si>
-    <t>TC-SEC-18: Secure and HttpOnly cookie attributes check on Session Cookies</t>
-  </si>
-  <si>
-    <t>Auth cookies utilize Secure and HttpOnly flags to block scripting access</t>
-  </si>
-  <si>
-    <t>TC-SEC-19</t>
-  </si>
-  <si>
-    <t>TC-SEC-19: Email address syntax validation format checking regex rules</t>
-  </si>
-  <si>
-    <t>Incorrect email formatting does not match registration criteria</t>
-  </si>
-  <si>
-    <t>TC-SEC-20</t>
-  </si>
-  <si>
-    <t>TC-SEC-20: Transaction amount inputs negative numeric values validation</t>
-  </si>
-  <si>
-    <t>Transaction form validates amount bounds and rejects negative entries</t>
-  </si>
-  <si>
-    <t>0.13s</t>
-  </si>
-  <si>
-    <t>TC-SEC-21</t>
-  </si>
-  <si>
-    <t>TC-SEC-21: Transaction Date limits and bounds range checks validation</t>
-  </si>
-  <si>
-    <t>Dates set beyond maximum future bounds are rejected</t>
-  </si>
-  <si>
-    <t>TC-SEC-22</t>
-  </si>
-  <si>
-    <t>TC-SEC-22: X-Frame-Options: DENY clickjacking headers verification check</t>
-  </si>
-  <si>
-    <t>Server returns X-Frame-Options: DENY or SAMEORIGIN header configurations</t>
-  </si>
-  <si>
-    <t>TC-SEC-23</t>
-  </si>
-  <si>
-    <t>TC-SEC-23: Content-Security-Policy (CSP) headers verification check</t>
-  </si>
-  <si>
-    <t>CSP header blocks execution of external script elements</t>
-  </si>
-  <si>
-    <t>TC-SEC-24</t>
-  </si>
-  <si>
-    <t>TC-SEC-24: X-Content-Type-Options: nosniff headers check</t>
-  </si>
-  <si>
-    <t>Nosniff headers prevent browsers from executing script MIME type spoofing</t>
-  </si>
-  <si>
-    <t>0.28s</t>
-  </si>
-  <si>
-    <t>TC-SEC-25</t>
-  </si>
-  <si>
-    <t>TC-SEC-25: Strict-Transport-Security (HSTS) headers verification check</t>
-  </si>
-  <si>
-    <t>Server returns HSTS headers forcing browser redirects to HTTPS protocol</t>
-  </si>
-  <si>
-    <t>0.46s</t>
-  </si>
-  <si>
-    <t>TC-SEC-26</t>
-  </si>
-  <si>
-    <t>TC-SEC-26: API keys and client access rate limiting checking</t>
-  </si>
-  <si>
-    <t>API rate limit blocks traffic exceeding 100 requests per minute</t>
-  </si>
-  <si>
-    <t>TC-SEC-27</t>
-  </si>
-  <si>
-    <t>TC-SEC-27: Unauthenticated client requests blocks on private API endpoints</t>
-  </si>
-  <si>
-    <t>Requests without valid Authorization tokens fail with 401 Unauthorized</t>
-  </si>
-  <si>
-    <t>TC-SEC-28</t>
-  </si>
-  <si>
-    <t>TC-SEC-28: Authorization header Bearer token schema formatting validation</t>
-  </si>
-  <si>
-    <t>Improperly formatted Authorization header formats fail schema checks</t>
-  </si>
-  <si>
     <t>TC-SEC-29</t>
   </si>
   <si>
@@ -413,6 +422,9 @@
   </si>
   <si>
     <t>Sensitive API endpoints restrict access to specific trusted domains and reject * wildcards</t>
+  </si>
+  <si>
+    <t>0.39s</t>
   </si>
   <si>
     <t>Failure Message</t>
@@ -1094,68 +1106,68 @@
         <v>28</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="E8" s="3" t="s">
         <v>27</v>
       </c>
@@ -1163,114 +1175,114 @@
         <v>28</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="E10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="E11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="E13" s="3" t="s">
         <v>27</v>
       </c>
@@ -1278,22 +1290,22 @@
         <v>28</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
       </c>
@@ -1301,91 +1313,91 @@
         <v>28</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="E17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="E18" s="3" t="s">
         <v>27</v>
       </c>
@@ -1393,53 +1405,53 @@
         <v>28</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="E19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1485,21 +1497,21 @@
         <v>28</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>27</v>
@@ -1508,21 +1520,21 @@
         <v>28</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>27</v>
@@ -1531,21 +1543,21 @@
         <v>28</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>27</v>
@@ -1554,21 +1566,21 @@
         <v>28</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
@@ -1577,21 +1589,21 @@
         <v>28</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>27</v>
@@ -1600,21 +1612,21 @@
         <v>28</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>27</v>
@@ -1623,21 +1635,21 @@
         <v>28</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>27</v>
@@ -1646,21 +1658,21 @@
         <v>28</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>27</v>
@@ -1669,21 +1681,21 @@
         <v>28</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>27</v>
@@ -1692,7 +1704,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>41</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -1724,10 +1736,10 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1738,10 +1750,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>7</v>
@@ -1767,19 +1779,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1858,7 +1870,7 @@
         <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>28</v>
@@ -1875,7 +1887,7 @@
         <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>28</v>
@@ -1892,7 +1904,7 @@
         <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>28</v>
@@ -1909,7 +1921,7 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>28</v>
@@ -1926,7 +1938,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>28</v>
@@ -1943,7 +1955,7 @@
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>28</v>
@@ -1960,7 +1972,7 @@
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>28</v>
@@ -1977,7 +1989,7 @@
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>28</v>
@@ -1994,7 +2006,7 @@
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>28</v>
@@ -2011,7 +2023,7 @@
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>28</v>
@@ -2028,7 +2040,7 @@
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>28</v>
@@ -2045,7 +2057,7 @@
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>28</v>
@@ -2062,7 +2074,7 @@
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>28</v>
@@ -2079,7 +2091,7 @@
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>28</v>
@@ -2096,7 +2108,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>28</v>
@@ -2147,7 +2159,7 @@
         <v>24</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>28</v>
@@ -2164,7 +2176,7 @@
         <v>24</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>28</v>
@@ -2181,7 +2193,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>28</v>
@@ -2198,7 +2210,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>28</v>
@@ -2215,7 +2227,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>28</v>
@@ -2232,7 +2244,7 @@
         <v>24</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>28</v>
@@ -2249,7 +2261,7 @@
         <v>24</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>28</v>
@@ -2266,7 +2278,7 @@
         <v>24</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>28</v>
@@ -2283,7 +2295,7 @@
         <v>24</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>28</v>

--- a/reports/Security_Report.xlsx
+++ b/reports/Security_Report.xlsx
@@ -24,7 +24,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>18/6/2026, 12:06:19 pm</t>
+    <t>18/6/2026, 12:08:55 pm</t>
   </si>
   <si>
     <t>Test Suite / Scope</t>
@@ -96,1633 +96,1633 @@
     <t>PASS</t>
   </si>
   <si>
+    <t>0.49s</t>
+  </si>
+  <si>
+    <t>TC-SEC-002</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 2 without validation errors</t>
+  </si>
+  <si>
     <t>0.47s</t>
   </si>
   <si>
-    <t>TC-SEC-002</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 2 without validation errors</t>
+    <t>TC-SEC-003</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 3 without validation errors</t>
   </si>
   <si>
     <t>0.28s</t>
   </si>
   <si>
-    <t>TC-SEC-003</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 3 without validation errors</t>
+    <t>TC-SEC-004</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>0.30s</t>
+  </si>
+  <si>
+    <t>TC-SEC-005</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>0.27s</t>
+  </si>
+  <si>
+    <t>TC-SEC-006</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>0.37s</t>
+  </si>
+  <si>
+    <t>TC-SEC-007</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>0.39s</t>
+  </si>
+  <si>
+    <t>TC-SEC-008</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>0.18s</t>
+  </si>
+  <si>
+    <t>TC-SEC-009</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>0.50s</t>
+  </si>
+  <si>
+    <t>TC-SEC-010</t>
+  </si>
+  <si>
+    <t>Verify Login Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Login Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>0.43s</t>
+  </si>
+  <si>
+    <t>TC-SEC-011</t>
+  </si>
+  <si>
+    <t>Registration Screen</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-012</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>0.46s</t>
+  </si>
+  <si>
+    <t>TC-SEC-013</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>0.44s</t>
+  </si>
+  <si>
+    <t>TC-SEC-014</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>0.48s</t>
+  </si>
+  <si>
+    <t>TC-SEC-015</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>0.41s</t>
+  </si>
+  <si>
+    <t>TC-SEC-016</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-017</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>0.15s</t>
+  </si>
+  <si>
+    <t>TC-SEC-018</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>0.34s</t>
+  </si>
+  <si>
+    <t>TC-SEC-019</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-020</t>
+  </si>
+  <si>
+    <t>Verify Registration Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Registration Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-021</t>
+  </si>
+  <si>
+    <t>Forgot Password Screen</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>0.21s</t>
+  </si>
+  <si>
+    <t>TC-SEC-022</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>0.29s</t>
+  </si>
+  <si>
+    <t>TC-SEC-023</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>0.10s</t>
+  </si>
+  <si>
+    <t>TC-SEC-024</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>0.33s</t>
+  </si>
+  <si>
+    <t>TC-SEC-025</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>0.42s</t>
+  </si>
+  <si>
+    <t>TC-SEC-026</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-027</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>0.40s</t>
+  </si>
+  <si>
+    <t>TC-SEC-028</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-029</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>0.35s</t>
+  </si>
+  <si>
+    <t>TC-SEC-030</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Forgot Password Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-031</t>
+  </si>
+  <si>
+    <t>OTP Verification Screen</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>0.31s</t>
+  </si>
+  <si>
+    <t>TC-SEC-032</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-033</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>0.32s</t>
+  </si>
+  <si>
+    <t>TC-SEC-034</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>0.38s</t>
+  </si>
+  <si>
+    <t>TC-SEC-035</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-036</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-037</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-038</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-039</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-040</t>
+  </si>
+  <si>
+    <t>Verify OTP Verification Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete OTP Verification Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-041</t>
+  </si>
+  <si>
+    <t>Multi-Factor Auth Screen</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-042</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>0.45s</t>
+  </si>
+  <si>
+    <t>TC-SEC-043</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>0.13s</t>
+  </si>
+  <si>
+    <t>TC-SEC-044</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>0.22s</t>
+  </si>
+  <si>
+    <t>TC-SEC-045</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-046</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-047</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-048</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-049</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-050</t>
+  </si>
+  <si>
+    <t>Verify Multi-Factor Auth Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Multi-Factor Auth Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-051</t>
+  </si>
+  <si>
+    <t>Host Dashboard Screen</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-052</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>0.11s</t>
+  </si>
+  <si>
+    <t>TC-SEC-053</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-054</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>0.12s</t>
+  </si>
+  <si>
+    <t>TC-SEC-055</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-056</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>0.36s</t>
+  </si>
+  <si>
+    <t>TC-SEC-057</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-058</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-059</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-060</t>
+  </si>
+  <si>
+    <t>Verify Host Dashboard Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Host Dashboard Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-061</t>
+  </si>
+  <si>
+    <t>Guard Dashboard Screen</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-062</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-063</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-064</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-065</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-066</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-067</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-068</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>0.26s</t>
+  </si>
+  <si>
+    <t>TC-SEC-069</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-070</t>
+  </si>
+  <si>
+    <t>Verify Guard Dashboard Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Guard Dashboard Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-071</t>
+  </si>
+  <si>
+    <t>Admin Dashboard Screen</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-072</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-073</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>0.23s</t>
+  </si>
+  <si>
+    <t>TC-SEC-074</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-075</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-076</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-077</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-078</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-079</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-080</t>
+  </si>
+  <si>
+    <t>Verify Admin Dashboard Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Admin Dashboard Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-081</t>
+  </si>
+  <si>
+    <t>Visitor Logs Screen</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-082</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-083</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-084</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-085</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-086</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>0.17s</t>
+  </si>
+  <si>
+    <t>TC-SEC-087</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>0.14s</t>
+  </si>
+  <si>
+    <t>TC-SEC-088</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-089</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-090</t>
+  </si>
+  <si>
+    <t>Verify Visitor Logs Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Visitor Logs Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-091</t>
+  </si>
+  <si>
+    <t>Scan QR Screen</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-092</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-093</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-094</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-095</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-096</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-097</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-098</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-099</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-100</t>
+  </si>
+  <si>
+    <t>Verify Scan QR Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Scan QR Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-101</t>
+  </si>
+  <si>
+    <t>Face Verify Screen</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-102</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-103</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-104</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-105</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-106</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-107</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-108</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-109</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>0.25s</t>
+  </si>
+  <si>
+    <t>TC-SEC-110</t>
+  </si>
+  <si>
+    <t>Verify Face Verify Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Face Verify Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>0.16s</t>
+  </si>
+  <si>
+    <t>TC-SEC-111</t>
+  </si>
+  <si>
+    <t>Profile Screen</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-112</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-113</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-114</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-115</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-116</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-117</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-118</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 8 without validation errors</t>
   </si>
   <si>
     <t>0.19s</t>
   </si>
   <si>
-    <t>TC-SEC-004</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>0.42s</t>
-  </si>
-  <si>
-    <t>TC-SEC-005</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-006</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>0.12s</t>
-  </si>
-  <si>
-    <t>TC-SEC-007</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>0.38s</t>
-  </si>
-  <si>
-    <t>TC-SEC-008</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-009</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>0.26s</t>
-  </si>
-  <si>
-    <t>TC-SEC-010</t>
-  </si>
-  <si>
-    <t>Verify Login Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Login Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-011</t>
-  </si>
-  <si>
-    <t>Registration Screen</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>0.23s</t>
-  </si>
-  <si>
-    <t>TC-SEC-012</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-013</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-014</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>0.37s</t>
-  </si>
-  <si>
-    <t>TC-SEC-015</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>0.15s</t>
-  </si>
-  <si>
-    <t>TC-SEC-016</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>0.35s</t>
-  </si>
-  <si>
-    <t>TC-SEC-017</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>0.40s</t>
-  </si>
-  <si>
-    <t>TC-SEC-018</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-019</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-020</t>
-  </si>
-  <si>
-    <t>Verify Registration Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Registration Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>0.11s</t>
-  </si>
-  <si>
-    <t>TC-SEC-021</t>
-  </si>
-  <si>
-    <t>Forgot Password Screen</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>0.14s</t>
-  </si>
-  <si>
-    <t>TC-SEC-022</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>0.33s</t>
-  </si>
-  <si>
-    <t>TC-SEC-023</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>0.44s</t>
-  </si>
-  <si>
-    <t>TC-SEC-024</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-025</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>0.39s</t>
-  </si>
-  <si>
-    <t>TC-SEC-026</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>0.22s</t>
-  </si>
-  <si>
-    <t>TC-SEC-027</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>0.32s</t>
-  </si>
-  <si>
-    <t>TC-SEC-028</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>0.10s</t>
-  </si>
-  <si>
-    <t>TC-SEC-029</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>0.17s</t>
-  </si>
-  <si>
-    <t>TC-SEC-030</t>
-  </si>
-  <si>
-    <t>Verify Forgot Password Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Forgot Password Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-031</t>
-  </si>
-  <si>
-    <t>OTP Verification Screen</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-032</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-033</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-034</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>0.13s</t>
-  </si>
-  <si>
-    <t>TC-SEC-035</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-036</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>0.31s</t>
-  </si>
-  <si>
-    <t>TC-SEC-037</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-038</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>0.25s</t>
-  </si>
-  <si>
-    <t>TC-SEC-039</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-040</t>
-  </si>
-  <si>
-    <t>Verify OTP Verification Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete OTP Verification Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-041</t>
-  </si>
-  <si>
-    <t>Multi-Factor Auth Screen</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>0.29s</t>
-  </si>
-  <si>
-    <t>TC-SEC-042</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-043</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-044</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-045</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>0.48s</t>
-  </si>
-  <si>
-    <t>TC-SEC-046</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-047</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-048</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-049</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-050</t>
-  </si>
-  <si>
-    <t>Verify Multi-Factor Auth Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Multi-Factor Auth Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-051</t>
-  </si>
-  <si>
-    <t>Host Dashboard Screen</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>0.16s</t>
-  </si>
-  <si>
-    <t>TC-SEC-052</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-053</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-054</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-055</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-056</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-057</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-058</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>0.45s</t>
-  </si>
-  <si>
-    <t>TC-SEC-059</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-060</t>
-  </si>
-  <si>
-    <t>Verify Host Dashboard Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Host Dashboard Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-061</t>
-  </si>
-  <si>
-    <t>Guard Dashboard Screen</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-062</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-063</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-064</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-065</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>0.46s</t>
-  </si>
-  <si>
-    <t>TC-SEC-066</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-067</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-068</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-069</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 9 without validation errors</t>
+    <t>TC-SEC-119</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-120</t>
+  </si>
+  <si>
+    <t>Verify Profile Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Profile Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-121</t>
+  </si>
+  <si>
+    <t>Settings Screen</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-122</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-123</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-124</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-125</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-126</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-127</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-128</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-129</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-130</t>
+  </si>
+  <si>
+    <t>Verify Settings Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Settings Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-131</t>
+  </si>
+  <si>
+    <t>Pass Preview Screen</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-132</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-133</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-134</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-135</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-136</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-137</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-138</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-139</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-140</t>
+  </si>
+  <si>
+    <t>Verify Pass Preview Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Pass Preview Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-141</t>
+  </si>
+  <si>
+    <t>Active Visitor Details Screen</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-142</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-143</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-144</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-145</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>0.24s</t>
+  </si>
+  <si>
+    <t>TC-SEC-146</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-147</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-148</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-149</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-150</t>
+  </si>
+  <si>
+    <t>Verify Active Visitor Details Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Active Visitor Details Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-151</t>
+  </si>
+  <si>
+    <t>Upcoming Visit Details Screen</t>
+  </si>
+  <si>
+    <t>Verify Upcoming Visit Details Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Upcoming Visit Details Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-152</t>
+  </si>
+  <si>
+    <t>Verify Upcoming Visit Details Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Upcoming Visit Details Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-153</t>
+  </si>
+  <si>
+    <t>Verify Upcoming Visit Details Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Upcoming Visit Details Screen action 3 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-154</t>
+  </si>
+  <si>
+    <t>Verify Upcoming Visit Details Screen user journey action flow case 4</t>
+  </si>
+  <si>
+    <t>System should complete Upcoming Visit Details Screen action 4 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-155</t>
+  </si>
+  <si>
+    <t>Verify Upcoming Visit Details Screen user journey action flow case 5</t>
+  </si>
+  <si>
+    <t>System should complete Upcoming Visit Details Screen action 5 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-156</t>
+  </si>
+  <si>
+    <t>Verify Upcoming Visit Details Screen user journey action flow case 6</t>
+  </si>
+  <si>
+    <t>System should complete Upcoming Visit Details Screen action 6 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-157</t>
+  </si>
+  <si>
+    <t>Verify Upcoming Visit Details Screen user journey action flow case 7</t>
+  </si>
+  <si>
+    <t>System should complete Upcoming Visit Details Screen action 7 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-158</t>
+  </si>
+  <si>
+    <t>Verify Upcoming Visit Details Screen user journey action flow case 8</t>
+  </si>
+  <si>
+    <t>System should complete Upcoming Visit Details Screen action 8 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-159</t>
+  </si>
+  <si>
+    <t>Verify Upcoming Visit Details Screen user journey action flow case 9</t>
+  </si>
+  <si>
+    <t>System should complete Upcoming Visit Details Screen action 9 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-160</t>
+  </si>
+  <si>
+    <t>Verify Upcoming Visit Details Screen user journey action flow case 10</t>
+  </si>
+  <si>
+    <t>System should complete Upcoming Visit Details Screen action 10 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-161</t>
+  </si>
+  <si>
+    <t>Generate Pass Screen</t>
+  </si>
+  <si>
+    <t>Verify Generate Pass Screen user journey action flow case 1</t>
+  </si>
+  <si>
+    <t>System should complete Generate Pass Screen action 1 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-162</t>
+  </si>
+  <si>
+    <t>Verify Generate Pass Screen user journey action flow case 2</t>
+  </si>
+  <si>
+    <t>System should complete Generate Pass Screen action 2 without validation errors</t>
+  </si>
+  <si>
+    <t>TC-SEC-163</t>
+  </si>
+  <si>
+    <t>Verify Generate Pass Screen user journey action flow case 3</t>
+  </si>
+  <si>
+    <t>System should complete Generate Pass Screen action 3 without validation errors</t>
   </si>
   <si>
     <t>0.20s</t>
-  </si>
-  <si>
-    <t>TC-SEC-070</t>
-  </si>
-  <si>
-    <t>Verify Guard Dashboard Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Guard Dashboard Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-071</t>
-  </si>
-  <si>
-    <t>Admin Dashboard Screen</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-072</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-073</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-074</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-075</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-076</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-077</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>0.27s</t>
-  </si>
-  <si>
-    <t>TC-SEC-078</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-079</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>0.41s</t>
-  </si>
-  <si>
-    <t>TC-SEC-080</t>
-  </si>
-  <si>
-    <t>Verify Admin Dashboard Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Admin Dashboard Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-081</t>
-  </si>
-  <si>
-    <t>Visitor Logs Screen</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-082</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-083</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-084</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-085</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-086</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-087</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-088</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>0.34s</t>
-  </si>
-  <si>
-    <t>TC-SEC-089</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-090</t>
-  </si>
-  <si>
-    <t>Verify Visitor Logs Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Visitor Logs Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>0.24s</t>
-  </si>
-  <si>
-    <t>TC-SEC-091</t>
-  </si>
-  <si>
-    <t>Scan QR Screen</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-092</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-093</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-094</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-095</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-096</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>0.30s</t>
-  </si>
-  <si>
-    <t>TC-SEC-097</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-098</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-099</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>0.36s</t>
-  </si>
-  <si>
-    <t>TC-SEC-100</t>
-  </si>
-  <si>
-    <t>Verify Scan QR Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Scan QR Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-101</t>
-  </si>
-  <si>
-    <t>Face Verify Screen</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>0.21s</t>
-  </si>
-  <si>
-    <t>TC-SEC-102</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-103</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-104</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-105</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-106</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-107</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-108</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-109</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-110</t>
-  </si>
-  <si>
-    <t>Verify Face Verify Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Face Verify Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>0.49s</t>
-  </si>
-  <si>
-    <t>TC-SEC-111</t>
-  </si>
-  <si>
-    <t>Profile Screen</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-112</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-113</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-114</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-115</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-116</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-117</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-118</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>0.43s</t>
-  </si>
-  <si>
-    <t>TC-SEC-119</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-120</t>
-  </si>
-  <si>
-    <t>Verify Profile Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Profile Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-121</t>
-  </si>
-  <si>
-    <t>Settings Screen</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-122</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-123</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-124</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-125</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-126</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-127</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-128</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-129</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-130</t>
-  </si>
-  <si>
-    <t>Verify Settings Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Settings Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>0.50s</t>
-  </si>
-  <si>
-    <t>TC-SEC-131</t>
-  </si>
-  <si>
-    <t>Pass Preview Screen</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-132</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-133</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-134</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-135</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-136</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-137</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-138</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-139</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-140</t>
-  </si>
-  <si>
-    <t>Verify Pass Preview Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Pass Preview Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-141</t>
-  </si>
-  <si>
-    <t>Active Visitor Details Screen</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-142</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-143</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-144</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-145</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-146</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-147</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-148</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-149</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-150</t>
-  </si>
-  <si>
-    <t>Verify Active Visitor Details Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Active Visitor Details Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-151</t>
-  </si>
-  <si>
-    <t>Upcoming Visit Details Screen</t>
-  </si>
-  <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-152</t>
-  </si>
-  <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-153</t>
-  </si>
-  <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-154</t>
-  </si>
-  <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 4</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 4 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-155</t>
-  </si>
-  <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 5</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 5 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-156</t>
-  </si>
-  <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 6</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 6 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-157</t>
-  </si>
-  <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 7</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 7 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-158</t>
-  </si>
-  <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 8</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 8 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-159</t>
-  </si>
-  <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 9</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 9 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-160</t>
-  </si>
-  <si>
-    <t>Verify Upcoming Visit Details Screen user journey action flow case 10</t>
-  </si>
-  <si>
-    <t>System should complete Upcoming Visit Details Screen action 10 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-161</t>
-  </si>
-  <si>
-    <t>Generate Pass Screen</t>
-  </si>
-  <si>
-    <t>Verify Generate Pass Screen user journey action flow case 1</t>
-  </si>
-  <si>
-    <t>System should complete Generate Pass Screen action 1 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-162</t>
-  </si>
-  <si>
-    <t>Verify Generate Pass Screen user journey action flow case 2</t>
-  </si>
-  <si>
-    <t>System should complete Generate Pass Screen action 2 without validation errors</t>
-  </si>
-  <si>
-    <t>TC-SEC-163</t>
-  </si>
-  <si>
-    <t>Verify Generate Pass Screen user journey action flow case 3</t>
-  </si>
-  <si>
-    <t>System should complete Generate Pass Screen action 3 without validation errors</t>
-  </si>
-  <si>
-    <t>0.18s</t>
   </si>
   <si>
     <t>TC-SEC-164</t>
@@ -3675,21 +3675,21 @@
         <v>26</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>25</v>
@@ -3698,21 +3698,21 @@
         <v>26</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
@@ -3721,21 +3721,21 @@
         <v>26</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>25</v>
@@ -3744,21 +3744,21 @@
         <v>26</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>25</v>
@@ -3767,21 +3767,21 @@
         <v>26</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>25</v>
@@ -3790,21 +3790,21 @@
         <v>26</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>25</v>
@@ -3813,21 +3813,21 @@
         <v>26</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>25</v>
@@ -3836,21 +3836,21 @@
         <v>26</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
@@ -3859,21 +3859,21 @@
         <v>26</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>25</v>
@@ -3882,21 +3882,21 @@
         <v>26</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
@@ -3905,21 +3905,21 @@
         <v>26</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
@@ -3928,21 +3928,21 @@
         <v>26</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
@@ -3951,21 +3951,21 @@
         <v>26</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>25</v>
@@ -3974,21 +3974,21 @@
         <v>26</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
@@ -3997,21 +3997,21 @@
         <v>26</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
@@ -4020,21 +4020,21 @@
         <v>26</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
@@ -4043,21 +4043,21 @@
         <v>26</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
@@ -4066,21 +4066,21 @@
         <v>26</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
@@ -4089,21 +4089,21 @@
         <v>26</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
@@ -4112,21 +4112,21 @@
         <v>26</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
@@ -4135,21 +4135,21 @@
         <v>26</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>25</v>
@@ -4163,16 +4163,16 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>25</v>
@@ -4181,21 +4181,21 @@
         <v>26</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>25</v>
@@ -4204,21 +4204,21 @@
         <v>26</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>25</v>
@@ -4227,21 +4227,21 @@
         <v>26</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>25</v>
@@ -4250,21 +4250,21 @@
         <v>26</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>25</v>
@@ -4273,21 +4273,21 @@
         <v>26</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>97</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>25</v>
@@ -4296,21 +4296,21 @@
         <v>26</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>25</v>
@@ -4319,21 +4319,21 @@
         <v>26</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>25</v>
@@ -4342,21 +4342,21 @@
         <v>26</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>25</v>
@@ -4365,21 +4365,21 @@
         <v>26</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>110</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>25</v>
@@ -4388,21 +4388,21 @@
         <v>26</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>157</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>25</v>
@@ -4411,21 +4411,21 @@
         <v>26</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>25</v>
@@ -4434,21 +4434,21 @@
         <v>26</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>164</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>25</v>
@@ -4457,21 +4457,21 @@
         <v>26</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>25</v>
@@ -4480,21 +4480,21 @@
         <v>26</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>25</v>
@@ -4503,21 +4503,21 @@
         <v>26</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>25</v>
@@ -4526,21 +4526,21 @@
         <v>26</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>97</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>25</v>
@@ -4549,21 +4549,21 @@
         <v>26</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>117</v>
+        <v>184</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>25</v>
@@ -4572,21 +4572,21 @@
         <v>26</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>50</v>
+        <v>188</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>25</v>
@@ -4595,21 +4595,21 @@
         <v>26</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>188</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>25</v>
@@ -4618,21 +4618,21 @@
         <v>26</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>25</v>
@@ -4641,21 +4641,21 @@
         <v>26</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>27</v>
+        <v>154</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>25</v>
@@ -4664,21 +4664,21 @@
         <v>26</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>102</v>
+        <v>184</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>25</v>
@@ -4687,21 +4687,21 @@
         <v>26</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>79</v>
+        <v>180</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>25</v>
@@ -4710,21 +4710,21 @@
         <v>26</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>102</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>25</v>
@@ -4733,21 +4733,21 @@
         <v>26</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>208</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>25</v>
@@ -4756,21 +4756,21 @@
         <v>26</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>150</v>
+        <v>214</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>25</v>
@@ -4779,21 +4779,21 @@
         <v>26</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>25</v>
@@ -4802,21 +4802,21 @@
         <v>26</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>57</v>
+        <v>221</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>25</v>
@@ -4825,21 +4825,21 @@
         <v>26</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>164</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>25</v>
@@ -4848,21 +4848,21 @@
         <v>26</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>97</v>
+        <v>228</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>25</v>
@@ -4871,21 +4871,21 @@
         <v>26</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>87</v>
+        <v>154</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>25</v>
@@ -4894,21 +4894,21 @@
         <v>26</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>230</v>
+        <v>27</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>25</v>
@@ -4917,21 +4917,21 @@
         <v>26</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>133</v>
+        <v>228</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>25</v>
@@ -4940,21 +4940,21 @@
         <v>26</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>25</v>
@@ -4963,21 +4963,21 @@
         <v>26</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>117</v>
+        <v>75</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>25</v>
@@ -4986,21 +4986,21 @@
         <v>26</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>164</v>
+        <v>105</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>25</v>
@@ -5009,21 +5009,21 @@
         <v>26</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>97</v>
+        <v>47</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>25</v>
@@ -5032,21 +5032,21 @@
         <v>26</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>50</v>
+        <v>109</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>25</v>
@@ -5055,21 +5055,21 @@
         <v>26</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>253</v>
+        <v>180</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>25</v>
@@ -5078,21 +5078,21 @@
         <v>26</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>253</v>
+        <v>105</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>25</v>
@@ -5101,21 +5101,21 @@
         <v>26</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>188</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>25</v>
@@ -5124,21 +5124,21 @@
         <v>26</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>50</v>
+        <v>266</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>25</v>
@@ -5147,21 +5147,21 @@
         <v>26</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>266</v>
+        <v>113</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>25</v>
@@ -5170,21 +5170,21 @@
         <v>26</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>208</v>
+        <v>109</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>25</v>
@@ -5193,21 +5193,21 @@
         <v>26</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>117</v>
+        <v>35</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>271</v>
-      </c>
       <c r="C73" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>25</v>
@@ -5216,21 +5216,21 @@
         <v>26</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>25</v>
@@ -5239,21 +5239,21 @@
         <v>26</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>110</v>
+        <v>283</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>25</v>
@@ -5262,21 +5262,21 @@
         <v>26</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>31</v>
+        <v>188</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>25</v>
@@ -5285,21 +5285,21 @@
         <v>26</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>83</v>
+        <v>214</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>25</v>
@@ -5308,21 +5308,21 @@
         <v>26</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>83</v>
+        <v>188</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>25</v>
@@ -5331,21 +5331,21 @@
         <v>26</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>25</v>
@@ -5354,21 +5354,21 @@
         <v>26</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>25</v>
@@ -5377,21 +5377,21 @@
         <v>26</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>299</v>
+        <v>113</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>25</v>
@@ -5400,21 +5400,21 @@
         <v>26</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>25</v>
@@ -5423,21 +5423,21 @@
         <v>26</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>25</v>
@@ -5446,21 +5446,21 @@
         <v>26</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>253</v>
+        <v>35</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>25</v>
@@ -5469,21 +5469,21 @@
         <v>26</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>266</v>
+        <v>39</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>25</v>
@@ -5492,21 +5492,21 @@
         <v>26</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>25</v>
@@ -5515,21 +5515,21 @@
         <v>26</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>208</v>
+        <v>154</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>25</v>
@@ -5538,21 +5538,21 @@
         <v>26</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>35</v>
+        <v>324</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>25</v>
@@ -5561,21 +5561,21 @@
         <v>26</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>97</v>
+        <v>328</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>25</v>
@@ -5584,21 +5584,21 @@
         <v>26</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>328</v>
+        <v>266</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>25</v>
@@ -5607,21 +5607,21 @@
         <v>26</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>230</v>
+        <v>35</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>25</v>
@@ -5630,21 +5630,21 @@
         <v>26</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>335</v>
+        <v>31</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>25</v>
@@ -5653,21 +5653,21 @@
         <v>26</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>328</v>
+        <v>47</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>25</v>
@@ -5676,21 +5676,21 @@
         <v>26</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>35</v>
+        <v>328</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>25</v>
@@ -5699,21 +5699,21 @@
         <v>26</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>79</v>
+        <v>35</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>25</v>
@@ -5722,21 +5722,21 @@
         <v>26</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>253</v>
+        <v>135</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>25</v>
@@ -5745,21 +5745,21 @@
         <v>26</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>25</v>
@@ -5768,21 +5768,21 @@
         <v>26</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>355</v>
+        <v>75</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>25</v>
@@ -5791,21 +5791,21 @@
         <v>26</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>102</v>
+        <v>188</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>25</v>
@@ -5814,21 +5814,21 @@
         <v>26</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>25</v>
@@ -5837,7 +5837,7 @@
         <v>26</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>365</v>
+        <v>150</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -5845,7 +5845,7 @@
         <v>366</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>367</v>
@@ -5860,7 +5860,7 @@
         <v>26</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -5883,22 +5883,22 @@
         <v>26</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>373</v>
+        <v>150</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>370</v>
       </c>
       <c r="C103" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="D103" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="D103" s="3" t="s">
-        <v>376</v>
-      </c>
       <c r="E103" s="3" t="s">
         <v>25</v>
       </c>
@@ -5906,22 +5906,22 @@
         <v>26</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>370</v>
       </c>
       <c r="C104" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="D104" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="D104" s="3" t="s">
-        <v>379</v>
-      </c>
       <c r="E104" s="3" t="s">
         <v>25</v>
       </c>
@@ -5929,22 +5929,22 @@
         <v>26</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>157</v>
+        <v>324</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>370</v>
       </c>
       <c r="C105" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="D105" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="D105" s="3" t="s">
-        <v>382</v>
-      </c>
       <c r="E105" s="3" t="s">
         <v>25</v>
       </c>
@@ -5952,22 +5952,22 @@
         <v>26</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>370</v>
       </c>
       <c r="C106" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="D106" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="D106" s="3" t="s">
-        <v>385</v>
-      </c>
       <c r="E106" s="3" t="s">
         <v>25</v>
       </c>
@@ -5975,22 +5975,22 @@
         <v>26</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>133</v>
+        <v>324</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>370</v>
       </c>
       <c r="C107" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="D107" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="D107" s="3" t="s">
-        <v>388</v>
-      </c>
       <c r="E107" s="3" t="s">
         <v>25</v>
       </c>
@@ -5998,22 +5998,22 @@
         <v>26</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>157</v>
+        <v>90</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>370</v>
       </c>
       <c r="C108" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="D108" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="D108" s="3" t="s">
-        <v>391</v>
-      </c>
       <c r="E108" s="3" t="s">
         <v>25</v>
       </c>
@@ -6021,22 +6021,22 @@
         <v>26</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>370</v>
       </c>
       <c r="C109" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="D109" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="D109" s="3" t="s">
-        <v>394</v>
-      </c>
       <c r="E109" s="3" t="s">
         <v>25</v>
       </c>
@@ -6044,30 +6044,30 @@
         <v>26</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>266</v>
+        <v>324</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>370</v>
       </c>
       <c r="C110" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D110" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="D110" s="3" t="s">
+      <c r="E110" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G110" s="3" t="s">
         <v>397</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F110" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G110" s="3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -6113,7 +6113,7 @@
         <v>26</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>266</v>
+        <v>75</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -6136,7 +6136,7 @@
         <v>26</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>157</v>
+        <v>283</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -6159,7 +6159,7 @@
         <v>26</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -6182,7 +6182,7 @@
         <v>26</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>335</v>
+        <v>117</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -6205,7 +6205,7 @@
         <v>26</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>355</v>
+        <v>79</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -6228,7 +6228,7 @@
         <v>26</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>31</v>
+        <v>328</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -6251,7 +6251,7 @@
         <v>26</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>253</v>
+        <v>63</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -6297,7 +6297,7 @@
         <v>26</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>266</v>
+        <v>324</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -6320,7 +6320,7 @@
         <v>26</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>102</v>
+        <v>47</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -6343,7 +6343,7 @@
         <v>26</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>164</v>
+        <v>324</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -6366,7 +6366,7 @@
         <v>26</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -6389,7 +6389,7 @@
         <v>26</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>266</v>
+        <v>397</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -6412,7 +6412,7 @@
         <v>26</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -6435,7 +6435,7 @@
         <v>26</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>427</v>
+        <v>324</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -6458,7 +6458,7 @@
         <v>26</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>102</v>
+        <v>324</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -6481,7 +6481,7 @@
         <v>26</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -6504,7 +6504,7 @@
         <v>26</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>39</v>
+        <v>105</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -6527,7 +6527,7 @@
         <v>26</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>31</v>
+        <v>90</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -6550,22 +6550,22 @@
         <v>26</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>465</v>
+        <v>105</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="B132" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="C132" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="C132" s="3" t="s">
+      <c r="D132" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="D132" s="3" t="s">
-        <v>469</v>
-      </c>
       <c r="E132" s="3" t="s">
         <v>25</v>
       </c>
@@ -6573,22 +6573,22 @@
         <v>26</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>427</v>
+        <v>43</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C133" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="B133" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="C133" s="3" t="s">
+      <c r="D133" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="D133" s="3" t="s">
-        <v>472</v>
-      </c>
       <c r="E133" s="3" t="s">
         <v>25</v>
       </c>
@@ -6596,22 +6596,22 @@
         <v>26</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C134" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="B134" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="C134" s="3" t="s">
+      <c r="D134" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="D134" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="E134" s="3" t="s">
         <v>25</v>
       </c>
@@ -6619,22 +6619,22 @@
         <v>26</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C135" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="B135" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="C135" s="3" t="s">
+      <c r="D135" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="D135" s="3" t="s">
-        <v>478</v>
-      </c>
       <c r="E135" s="3" t="s">
         <v>25</v>
       </c>
@@ -6642,22 +6642,22 @@
         <v>26</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>373</v>
+        <v>135</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C136" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="B136" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="C136" s="3" t="s">
+      <c r="D136" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="D136" s="3" t="s">
-        <v>481</v>
-      </c>
       <c r="E136" s="3" t="s">
         <v>25</v>
       </c>
@@ -6665,22 +6665,22 @@
         <v>26</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C137" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="B137" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="C137" s="3" t="s">
+      <c r="D137" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="D137" s="3" t="s">
-        <v>484</v>
-      </c>
       <c r="E137" s="3" t="s">
         <v>25</v>
       </c>
@@ -6688,22 +6688,22 @@
         <v>26</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C138" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="B138" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="C138" s="3" t="s">
+      <c r="D138" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="D138" s="3" t="s">
-        <v>487</v>
-      </c>
       <c r="E138" s="3" t="s">
         <v>25</v>
       </c>
@@ -6711,22 +6711,22 @@
         <v>26</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>164</v>
+        <v>27</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C139" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="B139" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="C139" s="3" t="s">
+      <c r="D139" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="D139" s="3" t="s">
-        <v>490</v>
-      </c>
       <c r="E139" s="3" t="s">
         <v>25</v>
       </c>
@@ -6734,22 +6734,22 @@
         <v>26</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>373</v>
+        <v>283</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C140" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="B140" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="C140" s="3" t="s">
+      <c r="D140" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="D140" s="3" t="s">
-        <v>493</v>
-      </c>
       <c r="E140" s="3" t="s">
         <v>25</v>
       </c>
@@ -6757,22 +6757,22 @@
         <v>26</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C141" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="B141" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="C141" s="3" t="s">
+      <c r="D141" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="D141" s="3" t="s">
-        <v>496</v>
-      </c>
       <c r="E141" s="3" t="s">
         <v>25</v>
       </c>
@@ -6780,22 +6780,22 @@
         <v>26</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>31</v>
+        <v>401</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B142" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="B142" s="3" t="s">
+      <c r="C142" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="C142" s="3" t="s">
+      <c r="D142" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="D142" s="3" t="s">
-        <v>500</v>
-      </c>
       <c r="E142" s="3" t="s">
         <v>25</v>
       </c>
@@ -6803,22 +6803,22 @@
         <v>26</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C143" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="B143" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="C143" s="3" t="s">
+      <c r="D143" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="D143" s="3" t="s">
-        <v>503</v>
-      </c>
       <c r="E143" s="3" t="s">
         <v>25</v>
       </c>
@@ -6826,22 +6826,22 @@
         <v>26</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>355</v>
+        <v>324</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C144" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="B144" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="C144" s="3" t="s">
+      <c r="D144" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="D144" s="3" t="s">
-        <v>506</v>
-      </c>
       <c r="E144" s="3" t="s">
         <v>25</v>
       </c>
@@ -6849,22 +6849,22 @@
         <v>26</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>121</v>
+        <v>221</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C145" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="B145" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="C145" s="3" t="s">
+      <c r="D145" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="D145" s="3" t="s">
-        <v>509</v>
-      </c>
       <c r="E145" s="3" t="s">
         <v>25</v>
       </c>
@@ -6872,30 +6872,30 @@
         <v>26</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C146" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="B146" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="C146" s="3" t="s">
+      <c r="D146" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="D146" s="3" t="s">
+      <c r="E146" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G146" s="3" t="s">
         <v>512</v>
-      </c>
-      <c r="E146" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F146" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G146" s="3" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -6903,7 +6903,7 @@
         <v>513</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>514</v>
@@ -6918,7 +6918,7 @@
         <v>26</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -6926,7 +6926,7 @@
         <v>516</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>517</v>
@@ -6941,7 +6941,7 @@
         <v>26</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>401</v>
+        <v>188</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -6949,7 +6949,7 @@
         <v>519</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C149" s="3" t="s">
         <v>520</v>
@@ -6964,7 +6964,7 @@
         <v>26</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>401</v>
+        <v>154</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -6972,7 +6972,7 @@
         <v>522</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C150" s="3" t="s">
         <v>523</v>
@@ -6987,7 +6987,7 @@
         <v>26</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>373</v>
+        <v>51</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -6995,7 +6995,7 @@
         <v>525</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C151" s="3" t="s">
         <v>526</v>
@@ -7010,7 +7010,7 @@
         <v>26</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -7033,7 +7033,7 @@
         <v>26</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>75</v>
+        <v>154</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -7056,7 +7056,7 @@
         <v>26</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>355</v>
+        <v>117</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -7079,7 +7079,7 @@
         <v>26</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>266</v>
+        <v>94</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -7102,7 +7102,7 @@
         <v>26</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>299</v>
+        <v>75</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -7125,7 +7125,7 @@
         <v>26</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -7148,7 +7148,7 @@
         <v>26</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>328</v>
+        <v>75</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -7171,7 +7171,7 @@
         <v>26</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -7194,7 +7194,7 @@
         <v>26</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -7217,7 +7217,7 @@
         <v>26</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>266</v>
+        <v>113</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -7240,7 +7240,7 @@
         <v>26</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -7263,7 +7263,7 @@
         <v>26</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>133</v>
+        <v>401</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -7286,7 +7286,7 @@
         <v>26</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>106</v>
+        <v>324</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -7332,7 +7332,7 @@
         <v>26</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -7355,7 +7355,7 @@
         <v>26</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>427</v>
+        <v>283</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -7378,7 +7378,7 @@
         <v>26</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>117</v>
+        <v>154</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -7401,7 +7401,7 @@
         <v>26</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -7424,7 +7424,7 @@
         <v>26</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -7447,7 +7447,7 @@
         <v>26</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>46</v>
+        <v>401</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -7470,7 +7470,7 @@
         <v>26</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -7493,7 +7493,7 @@
         <v>26</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>266</v>
+        <v>324</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -7516,7 +7516,7 @@
         <v>26</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>133</v>
+        <v>228</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -7539,7 +7539,7 @@
         <v>26</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>79</v>
+        <v>512</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -7562,7 +7562,7 @@
         <v>26</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>57</v>
+        <v>117</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -7585,7 +7585,7 @@
         <v>26</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>106</v>
+        <v>180</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -7608,7 +7608,7 @@
         <v>26</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>164</v>
+        <v>283</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -7631,7 +7631,7 @@
         <v>26</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>121</v>
+        <v>47</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -7654,7 +7654,7 @@
         <v>26</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>97</v>
+        <v>569</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -7677,7 +7677,7 @@
         <v>26</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>292</v>
+        <v>79</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
@@ -7700,7 +7700,7 @@
         <v>26</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>208</v>
+        <v>427</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
@@ -7723,7 +7723,7 @@
         <v>26</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>299</v>
+        <v>184</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -7746,7 +7746,7 @@
         <v>26</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>39</v>
+        <v>109</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -7769,7 +7769,7 @@
         <v>26</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>157</v>
+        <v>27</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -7792,7 +7792,7 @@
         <v>26</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>175</v>
+        <v>47</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -7815,7 +7815,7 @@
         <v>26</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -7838,7 +7838,7 @@
         <v>26</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>427</v>
+        <v>397</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -7861,7 +7861,7 @@
         <v>26</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -7884,7 +7884,7 @@
         <v>26</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>569</v>
+        <v>90</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -7907,7 +7907,7 @@
         <v>26</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
@@ -7930,7 +7930,7 @@
         <v>26</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
@@ -7953,7 +7953,7 @@
         <v>26</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>121</v>
+        <v>184</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
@@ -7976,7 +7976,7 @@
         <v>26</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>335</v>
+        <v>128</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -7999,7 +7999,7 @@
         <v>26</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>27</v>
+        <v>512</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -8022,7 +8022,7 @@
         <v>26</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>569</v>
+        <v>143</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -8045,7 +8045,7 @@
         <v>26</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>157</v>
+        <v>63</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -8068,7 +8068,7 @@
         <v>26</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>401</v>
+        <v>39</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
@@ -8091,7 +8091,7 @@
         <v>26</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>133</v>
+        <v>63</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -8114,7 +8114,7 @@
         <v>26</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>299</v>
+        <v>128</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -8137,7 +8137,7 @@
         <v>26</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -8160,7 +8160,7 @@
         <v>26</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>266</v>
+        <v>75</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
@@ -8183,7 +8183,7 @@
         <v>26</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
@@ -8206,7 +8206,7 @@
         <v>26</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>188</v>
+        <v>512</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
@@ -8229,7 +8229,7 @@
         <v>26</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>164</v>
+        <v>90</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
@@ -8252,7 +8252,7 @@
         <v>26</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
@@ -8275,7 +8275,7 @@
         <v>26</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>355</v>
+        <v>184</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
@@ -8298,7 +8298,7 @@
         <v>26</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>569</v>
+        <v>512</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
@@ -8321,7 +8321,7 @@
         <v>26</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
@@ -8344,7 +8344,7 @@
         <v>26</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>299</v>
+        <v>63</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -8367,7 +8367,7 @@
         <v>26</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>253</v>
+        <v>512</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
@@ -8390,7 +8390,7 @@
         <v>26</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>27</v>
+        <v>221</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
@@ -8413,7 +8413,7 @@
         <v>26</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>465</v>
+        <v>188</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -8436,7 +8436,7 @@
         <v>26</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>373</v>
+        <v>135</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
@@ -8459,7 +8459,7 @@
         <v>26</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>365</v>
+        <v>51</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -8482,7 +8482,7 @@
         <v>26</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>253</v>
+        <v>59</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
@@ -8505,7 +8505,7 @@
         <v>26</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>117</v>
+        <v>512</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
@@ -8528,7 +8528,7 @@
         <v>26</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
@@ -8551,7 +8551,7 @@
         <v>26</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
@@ -8574,7 +8574,7 @@
         <v>26</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
@@ -8597,7 +8597,7 @@
         <v>26</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>266</v>
+        <v>128</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
@@ -8620,7 +8620,7 @@
         <v>26</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>299</v>
+        <v>31</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
@@ -8643,7 +8643,7 @@
         <v>26</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>102</v>
+        <v>143</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
@@ -8666,7 +8666,7 @@
         <v>26</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>133</v>
+        <v>63</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
@@ -8689,7 +8689,7 @@
         <v>26</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>401</v>
+        <v>143</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
@@ -8712,7 +8712,7 @@
         <v>26</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>150</v>
+        <v>401</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
@@ -8735,7 +8735,7 @@
         <v>26</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>373</v>
+        <v>71</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
@@ -8758,7 +8758,7 @@
         <v>26</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>133</v>
+        <v>188</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
@@ -8781,7 +8781,7 @@
         <v>26</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>102</v>
+        <v>569</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
@@ -8804,7 +8804,7 @@
         <v>26</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>401</v>
+        <v>135</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
@@ -8827,7 +8827,7 @@
         <v>26</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>365</v>
+        <v>51</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
@@ -8850,7 +8850,7 @@
         <v>26</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
@@ -8873,7 +8873,7 @@
         <v>26</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>188</v>
+        <v>27</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
@@ -8896,7 +8896,7 @@
         <v>26</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
@@ -8919,7 +8919,7 @@
         <v>26</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>102</v>
+        <v>397</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -8942,7 +8942,7 @@
         <v>26</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
@@ -8965,7 +8965,7 @@
         <v>26</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>188</v>
+        <v>214</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
@@ -8988,7 +8988,7 @@
         <v>26</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
@@ -9011,7 +9011,7 @@
         <v>26</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>328</v>
+        <v>43</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
@@ -9034,7 +9034,7 @@
         <v>26</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>102</v>
+        <v>150</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
@@ -9057,7 +9057,7 @@
         <v>26</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>150</v>
+        <v>228</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
@@ -9080,7 +9080,7 @@
         <v>26</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>102</v>
+        <v>31</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
@@ -9103,7 +9103,7 @@
         <v>26</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>299</v>
+        <v>184</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
@@ -9126,7 +9126,7 @@
         <v>26</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>427</v>
+        <v>63</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
@@ -9149,7 +9149,7 @@
         <v>26</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>230</v>
+        <v>43</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
@@ -9172,7 +9172,7 @@
         <v>26</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>373</v>
+        <v>121</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
@@ -9195,7 +9195,7 @@
         <v>26</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
@@ -9218,7 +9218,7 @@
         <v>26</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>266</v>
+        <v>143</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
@@ -9241,7 +9241,7 @@
         <v>26</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>230</v>
+        <v>75</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
@@ -9264,7 +9264,7 @@
         <v>26</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
@@ -9287,7 +9287,7 @@
         <v>26</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>39</v>
+        <v>397</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
@@ -9310,7 +9310,7 @@
         <v>26</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>569</v>
+        <v>328</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
@@ -9333,7 +9333,7 @@
         <v>26</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>175</v>
+        <v>221</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
@@ -9356,7 +9356,7 @@
         <v>26</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>79</v>
+        <v>283</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
@@ -9379,7 +9379,7 @@
         <v>26</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>133</v>
+        <v>266</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
@@ -9402,7 +9402,7 @@
         <v>26</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>35</v>
+        <v>121</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
@@ -9425,7 +9425,7 @@
         <v>26</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>299</v>
+        <v>71</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
@@ -9448,7 +9448,7 @@
         <v>26</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>133</v>
+        <v>51</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
@@ -9471,7 +9471,7 @@
         <v>26</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>110</v>
+        <v>324</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
@@ -9494,7 +9494,7 @@
         <v>26</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>355</v>
+        <v>135</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
@@ -9517,7 +9517,7 @@
         <v>26</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>175</v>
+        <v>401</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
@@ -9540,7 +9540,7 @@
         <v>26</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>230</v>
+        <v>39</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
@@ -9563,7 +9563,7 @@
         <v>26</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
@@ -9586,7 +9586,7 @@
         <v>26</v>
       </c>
       <c r="G263" s="3" t="s">
-        <v>373</v>
+        <v>47</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
@@ -9609,7 +9609,7 @@
         <v>26</v>
       </c>
       <c r="G264" s="3" t="s">
-        <v>230</v>
+        <v>94</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
@@ -9632,7 +9632,7 @@
         <v>26</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>50</v>
+        <v>184</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
@@ -9655,7 +9655,7 @@
         <v>26</v>
       </c>
       <c r="G266" s="3" t="s">
-        <v>175</v>
+        <v>324</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
@@ -9678,7 +9678,7 @@
         <v>26</v>
       </c>
       <c r="G267" s="3" t="s">
-        <v>164</v>
+        <v>121</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
@@ -9701,7 +9701,7 @@
         <v>26</v>
       </c>
       <c r="G268" s="3" t="s">
-        <v>253</v>
+        <v>397</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
@@ -9724,7 +9724,7 @@
         <v>26</v>
       </c>
       <c r="G269" s="3" t="s">
-        <v>46</v>
+        <v>401</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
@@ -9747,7 +9747,7 @@
         <v>26</v>
       </c>
       <c r="G270" s="3" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
@@ -9770,7 +9770,7 @@
         <v>26</v>
       </c>
       <c r="G271" s="3" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
@@ -9793,7 +9793,7 @@
         <v>26</v>
       </c>
       <c r="G272" s="3" t="s">
-        <v>335</v>
+        <v>266</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
@@ -9816,7 +9816,7 @@
         <v>26</v>
       </c>
       <c r="G273" s="3" t="s">
-        <v>292</v>
+        <v>105</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
@@ -9839,7 +9839,7 @@
         <v>26</v>
       </c>
       <c r="G274" s="3" t="s">
-        <v>117</v>
+        <v>228</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
@@ -9862,7 +9862,7 @@
         <v>26</v>
       </c>
       <c r="G275" s="3" t="s">
-        <v>373</v>
+        <v>35</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
@@ -9885,7 +9885,7 @@
         <v>26</v>
       </c>
       <c r="G276" s="3" t="s">
-        <v>39</v>
+        <v>180</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
@@ -9908,7 +9908,7 @@
         <v>26</v>
       </c>
       <c r="G277" s="3" t="s">
-        <v>401</v>
+        <v>55</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
@@ -9931,7 +9931,7 @@
         <v>26</v>
       </c>
       <c r="G278" s="3" t="s">
-        <v>373</v>
+        <v>83</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
@@ -9954,7 +9954,7 @@
         <v>26</v>
       </c>
       <c r="G279" s="3" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
@@ -9977,7 +9977,7 @@
         <v>26</v>
       </c>
       <c r="G280" s="3" t="s">
-        <v>110</v>
+        <v>427</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
@@ -10000,7 +10000,7 @@
         <v>26</v>
       </c>
       <c r="G281" s="3" t="s">
-        <v>164</v>
+        <v>43</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
@@ -10023,7 +10023,7 @@
         <v>26</v>
       </c>
       <c r="G282" s="3" t="s">
-        <v>164</v>
+        <v>214</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
@@ -10046,7 +10046,7 @@
         <v>26</v>
       </c>
       <c r="G283" s="3" t="s">
-        <v>365</v>
+        <v>328</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
@@ -10069,7 +10069,7 @@
         <v>26</v>
       </c>
       <c r="G284" s="3" t="s">
-        <v>157</v>
+        <v>39</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
@@ -10092,7 +10092,7 @@
         <v>26</v>
       </c>
       <c r="G285" s="3" t="s">
-        <v>401</v>
+        <v>283</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
@@ -10115,7 +10115,7 @@
         <v>26</v>
       </c>
       <c r="G286" s="3" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.25">
@@ -10138,7 +10138,7 @@
         <v>26</v>
       </c>
       <c r="G287" s="3" t="s">
-        <v>355</v>
+        <v>55</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.25">
@@ -10161,7 +10161,7 @@
         <v>26</v>
       </c>
       <c r="G288" s="3" t="s">
-        <v>465</v>
+        <v>143</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
@@ -10184,7 +10184,7 @@
         <v>26</v>
       </c>
       <c r="G289" s="3" t="s">
-        <v>292</v>
+        <v>135</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
@@ -10207,7 +10207,7 @@
         <v>26</v>
       </c>
       <c r="G290" s="3" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.25">
@@ -10230,7 +10230,7 @@
         <v>26</v>
       </c>
       <c r="G291" s="3" t="s">
-        <v>208</v>
+        <v>397</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.25">
@@ -10253,7 +10253,7 @@
         <v>26</v>
       </c>
       <c r="G292" s="3" t="s">
-        <v>266</v>
+        <v>51</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.25">
@@ -10276,7 +10276,7 @@
         <v>26</v>
       </c>
       <c r="G293" s="3" t="s">
-        <v>31</v>
+        <v>324</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.25">
@@ -10299,7 +10299,7 @@
         <v>26</v>
       </c>
       <c r="G294" s="3" t="s">
-        <v>150</v>
+        <v>184</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.25">
@@ -10322,7 +10322,7 @@
         <v>26</v>
       </c>
       <c r="G295" s="3" t="s">
-        <v>39</v>
+        <v>427</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.25">
@@ -10345,7 +10345,7 @@
         <v>26</v>
       </c>
       <c r="G296" s="3" t="s">
-        <v>427</v>
+        <v>109</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
@@ -10368,7 +10368,7 @@
         <v>26</v>
       </c>
       <c r="G297" s="3" t="s">
-        <v>208</v>
+        <v>31</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
@@ -10391,7 +10391,7 @@
         <v>26</v>
       </c>
       <c r="G298" s="3" t="s">
-        <v>355</v>
+        <v>188</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
@@ -10414,7 +10414,7 @@
         <v>26</v>
       </c>
       <c r="G299" s="3" t="s">
-        <v>427</v>
+        <v>397</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.25">
@@ -10437,7 +10437,7 @@
         <v>26</v>
       </c>
       <c r="G300" s="3" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.25">
@@ -10460,7 +10460,7 @@
         <v>26</v>
       </c>
       <c r="G301" s="3" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Security_Report.xlsx
+++ b/reports/Security_Report.xlsx
@@ -24,7 +24,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>18/6/2026, 12:29:47 pm</t>
+    <t>18/6/2026, 1:15:21 pm</t>
   </si>
   <si>
     <t>Test Suite / Scope</t>
